--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.dyrmishi\OneDrive - Kore Systems\Documents\Events\Ascot Networking Day 18.06.2026\Tipping Competition\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{423A6B36-39D3-48DA-B328-9DC5BF3358F3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19215" yWindow="4140" windowWidth="13830" windowHeight="7140" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest List" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="190">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -337,6 +337,285 @@
   <si>
     <t>The Britannia Stakes
 (16:50)</t>
+  </si>
+  <si>
+    <t>Aix La Chapelle</t>
+  </si>
+  <si>
+    <t>Celtic Charioteer</t>
+  </si>
+  <si>
+    <t>Nola Soul</t>
+  </si>
+  <si>
+    <t>On Just Terms</t>
+  </si>
+  <si>
+    <t>Pikachu</t>
+  </si>
+  <si>
+    <t>Revels</t>
+  </si>
+  <si>
+    <t>Romanza</t>
+  </si>
+  <si>
+    <t>South Dakota</t>
+  </si>
+  <si>
+    <t>Sword Salute</t>
+  </si>
+  <si>
+    <t>Sydney Carton</t>
+  </si>
+  <si>
+    <t>Time For The Moon</t>
+  </si>
+  <si>
+    <t>Whispering Moon</t>
+  </si>
+  <si>
+    <t>Aperoll</t>
+  </si>
+  <si>
+    <t>Bayside</t>
+  </si>
+  <si>
+    <t>Sea Venture</t>
+  </si>
+  <si>
+    <t>Guildmaster</t>
+  </si>
+  <si>
+    <t>Tierra Del Toro</t>
+  </si>
+  <si>
+    <t>Cannes</t>
+  </si>
+  <si>
+    <t>Birgham Dub</t>
+  </si>
+  <si>
+    <t>Al Azd</t>
+  </si>
+  <si>
+    <t>Joulany</t>
+  </si>
+  <si>
+    <t>Amora Queen</t>
+  </si>
+  <si>
+    <t>Atomic City</t>
+  </si>
+  <si>
+    <t>Dial Me In</t>
+  </si>
+  <si>
+    <t>Enceladus</t>
+  </si>
+  <si>
+    <t>Believed</t>
+  </si>
+  <si>
+    <t>Into The Light</t>
+  </si>
+  <si>
+    <t>Golden Knight</t>
+  </si>
+  <si>
+    <t>Waterford Castle</t>
+  </si>
+  <si>
+    <t>Genchev</t>
+  </si>
+  <si>
+    <t>Arc Ole Ole</t>
+  </si>
+  <si>
+    <t>Heyzoom</t>
+  </si>
+  <si>
+    <t>Galilean Quality</t>
+  </si>
+  <si>
+    <t>Blue Hercules</t>
+  </si>
+  <si>
+    <t>Who's Lope</t>
+  </si>
+  <si>
+    <t>Charles Darnay</t>
+  </si>
+  <si>
+    <t>Bnaider</t>
+  </si>
+  <si>
+    <t>Brilliant Star</t>
+  </si>
+  <si>
+    <t>Composing</t>
+  </si>
+  <si>
+    <t>Dark Lucinda</t>
+  </si>
+  <si>
+    <t>Earth Shot</t>
+  </si>
+  <si>
+    <t>Gilded Prize</t>
+  </si>
+  <si>
+    <t>Golden Orbit</t>
+  </si>
+  <si>
+    <t>Johanna Walsh</t>
+  </si>
+  <si>
+    <t>Lady Roisia</t>
+  </si>
+  <si>
+    <t>Legacy Link</t>
+  </si>
+  <si>
+    <t>Maldives</t>
+  </si>
+  <si>
+    <t>Venetia</t>
+  </si>
+  <si>
+    <t>Warriors Whisper</t>
+  </si>
+  <si>
+    <t>Al Nayyir</t>
+  </si>
+  <si>
+    <t>Al Riffa</t>
+  </si>
+  <si>
+    <t>Caballo De Mar</t>
+  </si>
+  <si>
+    <t>Dubai Future</t>
+  </si>
+  <si>
+    <t>Sweet William</t>
+  </si>
+  <si>
+    <t>Trawlerman</t>
+  </si>
+  <si>
+    <t>Carmers</t>
+  </si>
+  <si>
+    <t>Furthur</t>
+  </si>
+  <si>
+    <t>Rahiebb</t>
+  </si>
+  <si>
+    <t>Scandinavia</t>
+  </si>
+  <si>
+    <t>Miss Alpilles</t>
+  </si>
+  <si>
+    <t>Pathein</t>
+  </si>
+  <si>
+    <t>Wise Prince</t>
+  </si>
+  <si>
+    <t>Organise</t>
+  </si>
+  <si>
+    <t>Tales Of Wisdom</t>
+  </si>
+  <si>
+    <t>Hilitany</t>
+  </si>
+  <si>
+    <t>Flushing Meadows</t>
+  </si>
+  <si>
+    <t>Laureate Crown</t>
+  </si>
+  <si>
+    <t>Conclave</t>
+  </si>
+  <si>
+    <t>New Connection</t>
+  </si>
+  <si>
+    <t>We're Goosers</t>
+  </si>
+  <si>
+    <t>Wechaad</t>
+  </si>
+  <si>
+    <t>Richie's Rocket</t>
+  </si>
+  <si>
+    <t>Victory Tip</t>
+  </si>
+  <si>
+    <t>Langstone</t>
+  </si>
+  <si>
+    <t>Charly</t>
+  </si>
+  <si>
+    <t>Bobby McGee</t>
+  </si>
+  <si>
+    <t>Blue Courvoisier</t>
+  </si>
+  <si>
+    <t>Noelan Star</t>
+  </si>
+  <si>
+    <t>Intense Vision</t>
+  </si>
+  <si>
+    <t>Outback Heat</t>
+  </si>
+  <si>
+    <t>St Anton</t>
+  </si>
+  <si>
+    <t>Capall Rasa</t>
+  </si>
+  <si>
+    <t>Runman</t>
+  </si>
+  <si>
+    <t>New Monarch</t>
+  </si>
+  <si>
+    <t>Vincenzo Peruggia</t>
+  </si>
+  <si>
+    <t>Crest Of Fire</t>
+  </si>
+  <si>
+    <t>Moonfall</t>
+  </si>
+  <si>
+    <t>Lion Of Alba</t>
+  </si>
+  <si>
+    <t>Jamestown</t>
+  </si>
+  <si>
+    <t>Exclusive Code</t>
+  </si>
+  <si>
+    <t>Winding Stream</t>
+  </si>
+  <si>
+    <t>Synners Kid</t>
+  </si>
+  <si>
+    <t>Wild Thoughts</t>
   </si>
 </sst>
 </file>
@@ -1326,7 +1605,7 @@
   <sheetPr>
     <tabColor rgb="FFC9A84C"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1377,221 +1656,385 @@
       <c r="A4" s="8">
         <v>1</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
+      <c r="B4" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>2</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
+      <c r="B5" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>3</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
+      <c r="B6" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>4</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
+      <c r="B7" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>5</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
+      <c r="B8" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <v>6</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
+      <c r="B9" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>7</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
+      <c r="B10" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>8</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
+      <c r="B11" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>9</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
+      <c r="B12" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>10</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
+      <c r="B13" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>11</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
+      <c r="B14" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <v>12</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
+      <c r="B15" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>145</v>
+      </c>
       <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="F15" s="11" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>13</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
+      <c r="B16" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>124</v>
+      </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
+      <c r="F16" s="9" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <v>14</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
+      <c r="B17" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
+      <c r="F17" s="11" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>15</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="B18" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>126</v>
+      </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
+      <c r="F18" s="9" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
         <v>16</v>
       </c>
       <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
+      <c r="C19" s="11" t="s">
+        <v>127</v>
+      </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
+      <c r="F19" s="11" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>17</v>
       </c>
       <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="C20" s="9" t="s">
+        <v>128</v>
+      </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
+      <c r="F20" s="9" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <v>18</v>
       </c>
       <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
+      <c r="C21" s="11" t="s">
+        <v>129</v>
+      </c>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
+      <c r="F21" s="11" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>19</v>
       </c>
       <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="C22" s="9" t="s">
+        <v>130</v>
+      </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
+      <c r="F22" s="9" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
         <v>20</v>
       </c>
       <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
+      <c r="C23" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
+      <c r="F23" s="11" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>21</v>
       </c>
       <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+      <c r="C24" s="9" t="s">
+        <v>132</v>
+      </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
+      <c r="F24" s="9" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <v>22</v>
       </c>
       <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
+      <c r="C25" s="11" t="s">
+        <v>133</v>
+      </c>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
+      <c r="F25" s="11" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
@@ -1601,7 +2044,9 @@
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
+      <c r="F26" s="9" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
@@ -1611,7 +2056,9 @@
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
+      <c r="F27" s="11" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
@@ -1621,7 +2068,9 @@
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
+      <c r="F28" s="9" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
@@ -1631,7 +2080,9 @@
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
+      <c r="F29" s="11" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
@@ -1641,7 +2092,9 @@
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
+      <c r="F30" s="9" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
@@ -1651,7 +2104,9 @@
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
+      <c r="F31" s="11" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
@@ -1661,17 +2116,57 @@
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
+      <c r="F32" s="9" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="10">
+      <c r="A33" s="8">
         <v>30</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
+        <v>31</v>
+      </c>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
+        <v>32</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="10">
+        <v>33</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11" t="s">
+        <v>189</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1743,7 +2238,9 @@
       <c r="A4" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -1827,7 +2324,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Select from Norfolk Stakes runners" xr:uid="{00000000-0002-0000-0200-000000000000}">
           <x14:formula1>
-            <xm:f>'Race Card'!$B$4:$B$33</xm:f>
+            <xm:f>'Race Card'!$B$4:$B$36</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>0</xm:f>
@@ -1836,7 +2333,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Select from King George V runners" xr:uid="{00000000-0002-0000-0200-000001000000}">
           <x14:formula1>
-            <xm:f>'Race Card'!$C$4:$C$33</xm:f>
+            <xm:f>'Race Card'!$C$4:$C$36</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>0</xm:f>
@@ -1845,7 +2342,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Select from Ribblesdale Stakes runners" xr:uid="{00000000-0002-0000-0200-000002000000}">
           <x14:formula1>
-            <xm:f>'Race Card'!$D$4:$D$33</xm:f>
+            <xm:f>'Race Card'!$D$4:$D$36</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>0</xm:f>
@@ -1854,7 +2351,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Select from Gold Cup runners" xr:uid="{00000000-0002-0000-0200-000003000000}">
           <x14:formula1>
-            <xm:f>'Race Card'!$E$4:$E$33</xm:f>
+            <xm:f>'Race Card'!$E$4:$E$36</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>0</xm:f>
@@ -1863,7 +2360,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Select from Britannia Stakes runners" xr:uid="{00000000-0002-0000-0200-000004000000}">
           <x14:formula1>
-            <xm:f>'Race Card'!$F$4:$F$33</xm:f>
+            <xm:f>'Race Card'!$F$4:$F$36</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>0</xm:f>
@@ -1987,11 +2484,15 @@
       <c r="A4" s="15">
         <v>1</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="17" t="str">
+      <c r="B4" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="17">
         <f>IF(C4="","",IF(UPPER(C4)=UPPER('Race Results'!B4),10,IF(UPPER(C4)=UPPER('Race Results'!C4),6,IF(UPPER(C4)=UPPER('Race Results'!D4),4,IF(UPPER(C4)=UPPER('Race Results'!E4),3,IF(UPPER(C4)=UPPER('Race Results'!F4),2,IF(UPPER(C4)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="17" t="str">
@@ -2014,8 +2515,8 @@
         <v/>
       </c>
       <c r="M4" s="18">
-        <f>IF(COUNTA(D4,F4,H4,J4,L4)=0,"",SUM(D4,F4,H4,J4,L4))</f>
-        <v>0</v>
+        <f t="shared" ref="M4:M33" si="0">IF(COUNTA(D4,F4,H4,J4,L4)=0,"",SUM(D4,F4,H4,J4,L4))</f>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2049,7 +2550,7 @@
         <v/>
       </c>
       <c r="M5" s="18">
-        <f>IF(COUNTA(D5,F5,H5,J5,L5)=0,"",SUM(D5,F5,H5,J5,L5))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2084,7 +2585,7 @@
         <v/>
       </c>
       <c r="M6" s="18">
-        <f>IF(COUNTA(D6,F6,H6,J6,L6)=0,"",SUM(D6,F6,H6,J6,L6))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2119,7 +2620,7 @@
         <v/>
       </c>
       <c r="M7" s="18">
-        <f>IF(COUNTA(D7,F7,H7,J7,L7)=0,"",SUM(D7,F7,H7,J7,L7))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2154,7 +2655,7 @@
         <v/>
       </c>
       <c r="M8" s="18">
-        <f>IF(COUNTA(D8,F8,H8,J8,L8)=0,"",SUM(D8,F8,H8,J8,L8))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2189,7 +2690,7 @@
         <v/>
       </c>
       <c r="M9" s="18">
-        <f>IF(COUNTA(D9,F9,H9,J9,L9)=0,"",SUM(D9,F9,H9,J9,L9))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2224,7 +2725,7 @@
         <v/>
       </c>
       <c r="M10" s="18">
-        <f>IF(COUNTA(D10,F10,H10,J10,L10)=0,"",SUM(D10,F10,H10,J10,L10))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2259,7 +2760,7 @@
         <v/>
       </c>
       <c r="M11" s="18">
-        <f>IF(COUNTA(D11,F11,H11,J11,L11)=0,"",SUM(D11,F11,H11,J11,L11))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2294,7 +2795,7 @@
         <v/>
       </c>
       <c r="M12" s="18">
-        <f>IF(COUNTA(D12,F12,H12,J12,L12)=0,"",SUM(D12,F12,H12,J12,L12))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2329,7 +2830,7 @@
         <v/>
       </c>
       <c r="M13" s="18">
-        <f>IF(COUNTA(D13,F13,H13,J13,L13)=0,"",SUM(D13,F13,H13,J13,L13))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2364,7 +2865,7 @@
         <v/>
       </c>
       <c r="M14" s="18">
-        <f>IF(COUNTA(D14,F14,H14,J14,L14)=0,"",SUM(D14,F14,H14,J14,L14))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2399,7 +2900,7 @@
         <v/>
       </c>
       <c r="M15" s="18">
-        <f>IF(COUNTA(D15,F15,H15,J15,L15)=0,"",SUM(D15,F15,H15,J15,L15))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2434,7 +2935,7 @@
         <v/>
       </c>
       <c r="M16" s="18">
-        <f>IF(COUNTA(D16,F16,H16,J16,L16)=0,"",SUM(D16,F16,H16,J16,L16))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2469,7 +2970,7 @@
         <v/>
       </c>
       <c r="M17" s="18">
-        <f>IF(COUNTA(D17,F17,H17,J17,L17)=0,"",SUM(D17,F17,H17,J17,L17))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2504,7 +3005,7 @@
         <v/>
       </c>
       <c r="M18" s="18">
-        <f>IF(COUNTA(D18,F18,H18,J18,L18)=0,"",SUM(D18,F18,H18,J18,L18))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2539,7 +3040,7 @@
         <v/>
       </c>
       <c r="M19" s="18">
-        <f>IF(COUNTA(D19,F19,H19,J19,L19)=0,"",SUM(D19,F19,H19,J19,L19))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2574,7 +3075,7 @@
         <v/>
       </c>
       <c r="M20" s="18">
-        <f>IF(COUNTA(D20,F20,H20,J20,L20)=0,"",SUM(D20,F20,H20,J20,L20))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2609,7 +3110,7 @@
         <v/>
       </c>
       <c r="M21" s="18">
-        <f>IF(COUNTA(D21,F21,H21,J21,L21)=0,"",SUM(D21,F21,H21,J21,L21))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2644,7 +3145,7 @@
         <v/>
       </c>
       <c r="M22" s="18">
-        <f>IF(COUNTA(D22,F22,H22,J22,L22)=0,"",SUM(D22,F22,H22,J22,L22))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2679,7 +3180,7 @@
         <v/>
       </c>
       <c r="M23" s="18">
-        <f>IF(COUNTA(D23,F23,H23,J23,L23)=0,"",SUM(D23,F23,H23,J23,L23))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2714,7 +3215,7 @@
         <v/>
       </c>
       <c r="M24" s="18">
-        <f>IF(COUNTA(D24,F24,H24,J24,L24)=0,"",SUM(D24,F24,H24,J24,L24))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2749,7 +3250,7 @@
         <v/>
       </c>
       <c r="M25" s="18">
-        <f>IF(COUNTA(D25,F25,H25,J25,L25)=0,"",SUM(D25,F25,H25,J25,L25))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2784,7 +3285,7 @@
         <v/>
       </c>
       <c r="M26" s="18">
-        <f>IF(COUNTA(D26,F26,H26,J26,L26)=0,"",SUM(D26,F26,H26,J26,L26))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2819,7 +3320,7 @@
         <v/>
       </c>
       <c r="M27" s="18">
-        <f>IF(COUNTA(D27,F27,H27,J27,L27)=0,"",SUM(D27,F27,H27,J27,L27))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2854,7 +3355,7 @@
         <v/>
       </c>
       <c r="M28" s="18">
-        <f>IF(COUNTA(D28,F28,H28,J28,L28)=0,"",SUM(D28,F28,H28,J28,L28))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2889,7 +3390,7 @@
         <v/>
       </c>
       <c r="M29" s="18">
-        <f>IF(COUNTA(D29,F29,H29,J29,L29)=0,"",SUM(D29,F29,H29,J29,L29))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2924,7 +3425,7 @@
         <v/>
       </c>
       <c r="M30" s="18">
-        <f>IF(COUNTA(D30,F30,H30,J30,L30)=0,"",SUM(D30,F30,H30,J30,L30))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2959,7 +3460,7 @@
         <v/>
       </c>
       <c r="M31" s="18">
-        <f>IF(COUNTA(D31,F31,H31,J31,L31)=0,"",SUM(D31,F31,H31,J31,L31))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2994,7 +3495,7 @@
         <v/>
       </c>
       <c r="M32" s="18">
-        <f>IF(COUNTA(D32,F32,H32,J32,L32)=0,"",SUM(D32,F32,H32,J32,L32))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3029,7 +3530,7 @@
         <v/>
       </c>
       <c r="M33" s="18">
-        <f>IF(COUNTA(D33,F33,H33,J33,L33)=0,"",SUM(D33,F33,H33,J33,L33))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3054,7 +3555,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Norfolk Stakes" prompt="Select horse for Norfolk Stakes" xr:uid="{00000000-0002-0000-0300-000001000000}">
           <x14:formula1>
-            <xm:f>'Race Card'!$B$4:$B$33</xm:f>
+            <xm:f>'Race Card'!$B$4:$B$36</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>0</xm:f>
@@ -3063,7 +3564,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="King George V" prompt="Select horse for King George V" xr:uid="{00000000-0002-0000-0300-000002000000}">
           <x14:formula1>
-            <xm:f>'Race Card'!$C$4:$C$33</xm:f>
+            <xm:f>'Race Card'!$C$4:$C$36</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>0</xm:f>
@@ -3072,7 +3573,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Ribblesdale Stakes" prompt="Select horse for Ribblesdale Stakes" xr:uid="{00000000-0002-0000-0300-000003000000}">
           <x14:formula1>
-            <xm:f>'Race Card'!$D$4:$D$33</xm:f>
+            <xm:f>'Race Card'!$D$4:$D$36</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>0</xm:f>
@@ -3081,7 +3582,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Gold Cup" prompt="Select horse for Gold Cup" xr:uid="{00000000-0002-0000-0300-000004000000}">
           <x14:formula1>
-            <xm:f>'Race Card'!$E$4:$E$33</xm:f>
+            <xm:f>'Race Card'!$E$4:$E$36</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>0</xm:f>
@@ -3090,7 +3591,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Britannia Stakes" prompt="Select horse for Britannia Stakes" xr:uid="{00000000-0002-0000-0300-000005000000}">
           <x14:formula1>
-            <xm:f>'Race Card'!$F$4:$F$33</xm:f>
+            <xm:f>'Race Card'!$F$4:$F$36</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>0</xm:f>
@@ -3143,17 +3644,17 @@
       <c r="A3" s="19">
         <v>1</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,1),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Mick Hogg</v>
       </c>
       <c r="C3" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,1),"")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D3" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C3,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.3">

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{423A6B36-39D3-48DA-B328-9DC5BF3358F3}"/>
   <bookViews>
-    <workbookView xWindow="-19215" yWindow="4140" windowWidth="13830" windowHeight="7140" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest List" sheetId="1" r:id="rId1"/>
@@ -927,7 +927,10 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -935,13 +938,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1217,16 +1217,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35"/>
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1623,14 +1623,14 @@
       <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -2201,15 +2201,15 @@
       <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
     </row>
     <row r="3" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
@@ -2301,15 +2301,15 @@
       <c r="G9" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2423,21 +2423,21 @@
       <c r="M1" s="33"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
     </row>
     <row r="3" spans="1:13" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -3619,12 +3619,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -4181,14 +4181,14 @@
       <c r="F1" s="33"/>
     </row>
     <row r="3" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="31" t="s">
@@ -4206,14 +4206,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="31" t="s">
@@ -4251,14 +4251,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="31" t="s">
@@ -4301,14 +4301,14 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A27" s="34" t="s">
+      <c r="A27" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="31" t="s">

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{423A6B36-39D3-48DA-B328-9DC5BF3358F3}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8FC39D9-4EF3-4402-BD0E-9D71AED00A04}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="190">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -2241,11 +2241,21 @@
       <c r="B4" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="C4" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8FC39D9-4EF3-4402-BD0E-9D71AED00A04}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A869977-79CE-4ED1-BE84-ED93377F388C}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest List" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="190">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -930,7 +930,6 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -938,6 +937,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1217,16 +1217,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="36"/>
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37"/>
+      <c r="B2" s="36"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1623,14 +1623,14 @@
       <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -2261,12 +2261,24 @@
       <c r="A5" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
@@ -2311,15 +2323,15 @@
       <c r="G9" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2490,7 +2502,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="15">
         <v>1</v>
       </c>
@@ -2504,10 +2516,12 @@
         <f>IF(C4="","",IF(UPPER(C4)=UPPER('Race Results'!B4),10,IF(UPPER(C4)=UPPER('Race Results'!C4),6,IF(UPPER(C4)=UPPER('Race Results'!D4),4,IF(UPPER(C4)=UPPER('Race Results'!E4),3,IF(UPPER(C4)=UPPER('Race Results'!F4),2,IF(UPPER(C4)=UPPER('Race Results'!G4),1,0)))))))</f>
         <v>10</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="17" t="str">
+      <c r="E4" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="17">
         <f>IF(E4="","",IF(UPPER(E4)=UPPER('Race Results'!B5),10,IF(UPPER(E4)=UPPER('Race Results'!C5),6,IF(UPPER(E4)=UPPER('Race Results'!D5),4,IF(UPPER(E4)=UPPER('Race Results'!E5),3,IF(UPPER(E4)=UPPER('Race Results'!F5),2,IF(UPPER(E4)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G4" s="15"/>
       <c r="H4" s="17" t="str">
@@ -2533,16 +2547,20 @@
       <c r="A5" s="4">
         <v>2</v>
       </c>
-      <c r="B5" s="5"/>
+      <c r="B5" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="C5" s="4"/>
       <c r="D5" s="17" t="str">
         <f>IF(C5="","",IF(UPPER(C5)=UPPER('Race Results'!B4),10,IF(UPPER(C5)=UPPER('Race Results'!C4),6,IF(UPPER(C5)=UPPER('Race Results'!D4),4,IF(UPPER(C5)=UPPER('Race Results'!E4),3,IF(UPPER(C5)=UPPER('Race Results'!F4),2,IF(UPPER(C5)=UPPER('Race Results'!G4),1,0)))))))</f>
         <v/>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="17" t="str">
+      <c r="E5" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="17">
         <f>IF(E5="","",IF(UPPER(E5)=UPPER('Race Results'!B5),10,IF(UPPER(E5)=UPPER('Race Results'!C5),6,IF(UPPER(E5)=UPPER('Race Results'!D5),4,IF(UPPER(E5)=UPPER('Race Results'!E5),3,IF(UPPER(E5)=UPPER('Race Results'!F5),2,IF(UPPER(E5)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="17" t="str">
@@ -2561,7 +2579,7 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3553,7 +3571,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="140" yWindow="396" count="6">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Guest Name" prompt="Start typing or pick from guest list" xr:uid="{00000000-0002-0000-0300-000000000000}">
           <x14:formula1>
             <xm:f>'Guest List'!$B$4:$B$53</xm:f>
@@ -3671,13 +3689,13 @@
       <c r="A4" s="19">
         <v>2</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Steve Burfitt</v>
       </c>
       <c r="C4" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),"")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D4" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C4,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A869977-79CE-4ED1-BE84-ED93377F388C}"/>
+  <xr:revisionPtr revIDLastSave="302" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91E79C02-A7FB-4611-AEE7-17C7A578BD6A}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest List" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="190">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -2238,47 +2238,23 @@
       <c r="A4" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>97</v>
-      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>131</v>
-      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
@@ -2502,45 +2478,51 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="15">
         <v>1</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D4" s="17">
         <f>IF(C4="","",IF(UPPER(C4)=UPPER('Race Results'!B4),10,IF(UPPER(C4)=UPPER('Race Results'!C4),6,IF(UPPER(C4)=UPPER('Race Results'!D4),4,IF(UPPER(C4)=UPPER('Race Results'!E4),3,IF(UPPER(C4)=UPPER('Race Results'!F4),2,IF(UPPER(C4)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F4" s="17">
         <f>IF(E4="","",IF(UPPER(E4)=UPPER('Race Results'!B5),10,IF(UPPER(E4)=UPPER('Race Results'!C5),6,IF(UPPER(E4)=UPPER('Race Results'!D5),4,IF(UPPER(E4)=UPPER('Race Results'!E5),3,IF(UPPER(E4)=UPPER('Race Results'!F5),2,IF(UPPER(E4)=UPPER('Race Results'!G5),1,0)))))))</f>
         <v>0</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="17" t="str">
+      <c r="G4" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="H4" s="17">
         <f>IF(G4="","",IF(UPPER(G4)=UPPER('Race Results'!B6),10,IF(UPPER(G4)=UPPER('Race Results'!C6),6,IF(UPPER(G4)=UPPER('Race Results'!D6),4,IF(UPPER(G4)=UPPER('Race Results'!E6),3,IF(UPPER(G4)=UPPER('Race Results'!F6),2,IF(UPPER(G4)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I4" s="15"/>
-      <c r="J4" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="J4" s="17">
         <f>IF(I4="","",IF(UPPER(I4)=UPPER('Race Results'!B7),10,IF(UPPER(I4)=UPPER('Race Results'!C7),6,IF(UPPER(I4)=UPPER('Race Results'!D7),4,IF(UPPER(I4)=UPPER('Race Results'!E7),3,IF(UPPER(I4)=UPPER('Race Results'!F7),2,IF(UPPER(I4)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K4" s="15"/>
-      <c r="L4" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="L4" s="17">
         <f>IF(K4="","",IF(UPPER(K4)=UPPER('Race Results'!B8),10,IF(UPPER(K4)=UPPER('Race Results'!C8),6,IF(UPPER(K4)=UPPER('Race Results'!D8),4,IF(UPPER(K4)=UPPER('Race Results'!E8),3,IF(UPPER(K4)=UPPER('Race Results'!F8),2,IF(UPPER(K4)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M4" s="18">
         <f t="shared" ref="M4:M33" si="0">IF(COUNTA(D4,F4,H4,J4,L4)=0,"",SUM(D4,F4,H4,J4,L4))</f>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2548,69 +2530,89 @@
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="17" t="str">
+        <v>65</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="17">
         <f>IF(C5="","",IF(UPPER(C5)=UPPER('Race Results'!B4),10,IF(UPPER(C5)=UPPER('Race Results'!C4),6,IF(UPPER(C5)=UPPER('Race Results'!D4),4,IF(UPPER(C5)=UPPER('Race Results'!E4),3,IF(UPPER(C5)=UPPER('Race Results'!F4),2,IF(UPPER(C5)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="F5" s="17">
         <f>IF(E5="","",IF(UPPER(E5)=UPPER('Race Results'!B5),10,IF(UPPER(E5)=UPPER('Race Results'!C5),6,IF(UPPER(E5)=UPPER('Race Results'!D5),4,IF(UPPER(E5)=UPPER('Race Results'!E5),3,IF(UPPER(E5)=UPPER('Race Results'!F5),2,IF(UPPER(E5)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="H5" s="17">
         <f>IF(G5="","",IF(UPPER(G5)=UPPER('Race Results'!B6),10,IF(UPPER(G5)=UPPER('Race Results'!C6),6,IF(UPPER(G5)=UPPER('Race Results'!D6),4,IF(UPPER(G5)=UPPER('Race Results'!E6),3,IF(UPPER(G5)=UPPER('Race Results'!F6),2,IF(UPPER(G5)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J5" s="17">
         <f>IF(I5="","",IF(UPPER(I5)=UPPER('Race Results'!B7),10,IF(UPPER(I5)=UPPER('Race Results'!C7),6,IF(UPPER(I5)=UPPER('Race Results'!D7),4,IF(UPPER(I5)=UPPER('Race Results'!E7),3,IF(UPPER(I5)=UPPER('Race Results'!F7),2,IF(UPPER(I5)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="L5" s="17">
         <f>IF(K5="","",IF(UPPER(K5)=UPPER('Race Results'!B8),10,IF(UPPER(K5)=UPPER('Race Results'!C8),6,IF(UPPER(K5)=UPPER('Race Results'!D8),4,IF(UPPER(K5)=UPPER('Race Results'!E8),3,IF(UPPER(K5)=UPPER('Race Results'!F8),2,IF(UPPER(K5)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M5" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="15">
         <v>3</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="17" t="str">
+      <c r="B6" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="17">
         <f>IF(C6="","",IF(UPPER(C6)=UPPER('Race Results'!B4),10,IF(UPPER(C6)=UPPER('Race Results'!C4),6,IF(UPPER(C6)=UPPER('Race Results'!D4),4,IF(UPPER(C6)=UPPER('Race Results'!E4),3,IF(UPPER(C6)=UPPER('Race Results'!F4),2,IF(UPPER(C6)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" s="17">
         <f>IF(E6="","",IF(UPPER(E6)=UPPER('Race Results'!B5),10,IF(UPPER(E6)=UPPER('Race Results'!C5),6,IF(UPPER(E6)=UPPER('Race Results'!D5),4,IF(UPPER(E6)=UPPER('Race Results'!E5),3,IF(UPPER(E6)=UPPER('Race Results'!F5),2,IF(UPPER(E6)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="H6" s="17">
         <f>IF(G6="","",IF(UPPER(G6)=UPPER('Race Results'!B6),10,IF(UPPER(G6)=UPPER('Race Results'!C6),6,IF(UPPER(G6)=UPPER('Race Results'!D6),4,IF(UPPER(G6)=UPPER('Race Results'!E6),3,IF(UPPER(G6)=UPPER('Race Results'!F6),2,IF(UPPER(G6)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="J6" s="17">
         <f>IF(I6="","",IF(UPPER(I6)=UPPER('Race Results'!B7),10,IF(UPPER(I6)=UPPER('Race Results'!C7),6,IF(UPPER(I6)=UPPER('Race Results'!D7),4,IF(UPPER(I6)=UPPER('Race Results'!E7),3,IF(UPPER(I6)=UPPER('Race Results'!F7),2,IF(UPPER(I6)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K6" s="15"/>
-      <c r="L6" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L6" s="17">
         <f>IF(K6="","",IF(UPPER(K6)=UPPER('Race Results'!B8),10,IF(UPPER(K6)=UPPER('Race Results'!C8),6,IF(UPPER(K6)=UPPER('Race Results'!D8),4,IF(UPPER(K6)=UPPER('Race Results'!E8),3,IF(UPPER(K6)=UPPER('Race Results'!F8),2,IF(UPPER(K6)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M6" s="18">
         <f t="shared" si="0"/>
@@ -2621,31 +2623,43 @@
       <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="17" t="str">
+      <c r="B7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="17">
         <f>IF(C7="","",IF(UPPER(C7)=UPPER('Race Results'!B4),10,IF(UPPER(C7)=UPPER('Race Results'!C4),6,IF(UPPER(C7)=UPPER('Race Results'!D4),4,IF(UPPER(C7)=UPPER('Race Results'!E4),3,IF(UPPER(C7)=UPPER('Race Results'!F4),2,IF(UPPER(C7)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F7" s="17">
         <f>IF(E7="","",IF(UPPER(E7)=UPPER('Race Results'!B5),10,IF(UPPER(E7)=UPPER('Race Results'!C5),6,IF(UPPER(E7)=UPPER('Race Results'!D5),4,IF(UPPER(E7)=UPPER('Race Results'!E5),3,IF(UPPER(E7)=UPPER('Race Results'!F5),2,IF(UPPER(E7)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H7" s="17">
         <f>IF(G7="","",IF(UPPER(G7)=UPPER('Race Results'!B6),10,IF(UPPER(G7)=UPPER('Race Results'!C6),6,IF(UPPER(G7)=UPPER('Race Results'!D6),4,IF(UPPER(G7)=UPPER('Race Results'!E6),3,IF(UPPER(G7)=UPPER('Race Results'!F6),2,IF(UPPER(G7)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="J7" s="17">
         <f>IF(I7="","",IF(UPPER(I7)=UPPER('Race Results'!B7),10,IF(UPPER(I7)=UPPER('Race Results'!C7),6,IF(UPPER(I7)=UPPER('Race Results'!D7),4,IF(UPPER(I7)=UPPER('Race Results'!E7),3,IF(UPPER(I7)=UPPER('Race Results'!F7),2,IF(UPPER(I7)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L7" s="17">
         <f>IF(K7="","",IF(UPPER(K7)=UPPER('Race Results'!B8),10,IF(UPPER(K7)=UPPER('Race Results'!C8),6,IF(UPPER(K7)=UPPER('Race Results'!D8),4,IF(UPPER(K7)=UPPER('Race Results'!E8),3,IF(UPPER(K7)=UPPER('Race Results'!F8),2,IF(UPPER(K7)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M7" s="18">
         <f t="shared" si="0"/>
@@ -2656,31 +2670,43 @@
       <c r="A8" s="15">
         <v>5</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="17" t="str">
+      <c r="B8" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="17">
         <f>IF(C8="","",IF(UPPER(C8)=UPPER('Race Results'!B4),10,IF(UPPER(C8)=UPPER('Race Results'!C4),6,IF(UPPER(C8)=UPPER('Race Results'!D4),4,IF(UPPER(C8)=UPPER('Race Results'!E4),3,IF(UPPER(C8)=UPPER('Race Results'!F4),2,IF(UPPER(C8)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="17">
         <f>IF(E8="","",IF(UPPER(E8)=UPPER('Race Results'!B5),10,IF(UPPER(E8)=UPPER('Race Results'!C5),6,IF(UPPER(E8)=UPPER('Race Results'!D5),4,IF(UPPER(E8)=UPPER('Race Results'!E5),3,IF(UPPER(E8)=UPPER('Race Results'!F5),2,IF(UPPER(E8)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="H8" s="17">
         <f>IF(G8="","",IF(UPPER(G8)=UPPER('Race Results'!B6),10,IF(UPPER(G8)=UPPER('Race Results'!C6),6,IF(UPPER(G8)=UPPER('Race Results'!D6),4,IF(UPPER(G8)=UPPER('Race Results'!E6),3,IF(UPPER(G8)=UPPER('Race Results'!F6),2,IF(UPPER(G8)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J8" s="17">
         <f>IF(I8="","",IF(UPPER(I8)=UPPER('Race Results'!B7),10,IF(UPPER(I8)=UPPER('Race Results'!C7),6,IF(UPPER(I8)=UPPER('Race Results'!D7),4,IF(UPPER(I8)=UPPER('Race Results'!E7),3,IF(UPPER(I8)=UPPER('Race Results'!F7),2,IF(UPPER(I8)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="L8" s="17">
         <f>IF(K8="","",IF(UPPER(K8)=UPPER('Race Results'!B8),10,IF(UPPER(K8)=UPPER('Race Results'!C8),6,IF(UPPER(K8)=UPPER('Race Results'!D8),4,IF(UPPER(K8)=UPPER('Race Results'!E8),3,IF(UPPER(K8)=UPPER('Race Results'!F8),2,IF(UPPER(K8)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M8" s="18">
         <f t="shared" si="0"/>
@@ -2691,31 +2717,43 @@
       <c r="A9" s="4">
         <v>6</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="17" t="str">
+      <c r="B9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="17">
         <f>IF(C9="","",IF(UPPER(C9)=UPPER('Race Results'!B4),10,IF(UPPER(C9)=UPPER('Race Results'!C4),6,IF(UPPER(C9)=UPPER('Race Results'!D4),4,IF(UPPER(C9)=UPPER('Race Results'!E4),3,IF(UPPER(C9)=UPPER('Race Results'!F4),2,IF(UPPER(C9)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F9" s="17">
         <f>IF(E9="","",IF(UPPER(E9)=UPPER('Race Results'!B5),10,IF(UPPER(E9)=UPPER('Race Results'!C5),6,IF(UPPER(E9)=UPPER('Race Results'!D5),4,IF(UPPER(E9)=UPPER('Race Results'!E5),3,IF(UPPER(E9)=UPPER('Race Results'!F5),2,IF(UPPER(E9)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H9" s="17">
         <f>IF(G9="","",IF(UPPER(G9)=UPPER('Race Results'!B6),10,IF(UPPER(G9)=UPPER('Race Results'!C6),6,IF(UPPER(G9)=UPPER('Race Results'!D6),4,IF(UPPER(G9)=UPPER('Race Results'!E6),3,IF(UPPER(G9)=UPPER('Race Results'!F6),2,IF(UPPER(G9)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J9" s="17">
         <f>IF(I9="","",IF(UPPER(I9)=UPPER('Race Results'!B7),10,IF(UPPER(I9)=UPPER('Race Results'!C7),6,IF(UPPER(I9)=UPPER('Race Results'!D7),4,IF(UPPER(I9)=UPPER('Race Results'!E7),3,IF(UPPER(I9)=UPPER('Race Results'!F7),2,IF(UPPER(I9)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="L9" s="17">
         <f>IF(K9="","",IF(UPPER(K9)=UPPER('Race Results'!B8),10,IF(UPPER(K9)=UPPER('Race Results'!C8),6,IF(UPPER(K9)=UPPER('Race Results'!D8),4,IF(UPPER(K9)=UPPER('Race Results'!E8),3,IF(UPPER(K9)=UPPER('Race Results'!F8),2,IF(UPPER(K9)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M9" s="18">
         <f t="shared" si="0"/>
@@ -2726,31 +2764,43 @@
       <c r="A10" s="15">
         <v>7</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="17" t="str">
+      <c r="B10" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="17">
         <f>IF(C10="","",IF(UPPER(C10)=UPPER('Race Results'!B4),10,IF(UPPER(C10)=UPPER('Race Results'!C4),6,IF(UPPER(C10)=UPPER('Race Results'!D4),4,IF(UPPER(C10)=UPPER('Race Results'!E4),3,IF(UPPER(C10)=UPPER('Race Results'!F4),2,IF(UPPER(C10)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10" s="17">
         <f>IF(E10="","",IF(UPPER(E10)=UPPER('Race Results'!B5),10,IF(UPPER(E10)=UPPER('Race Results'!C5),6,IF(UPPER(E10)=UPPER('Race Results'!D5),4,IF(UPPER(E10)=UPPER('Race Results'!E5),3,IF(UPPER(E10)=UPPER('Race Results'!F5),2,IF(UPPER(E10)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G10" s="15"/>
-      <c r="H10" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H10" s="17">
         <f>IF(G10="","",IF(UPPER(G10)=UPPER('Race Results'!B6),10,IF(UPPER(G10)=UPPER('Race Results'!C6),6,IF(UPPER(G10)=UPPER('Race Results'!D6),4,IF(UPPER(G10)=UPPER('Race Results'!E6),3,IF(UPPER(G10)=UPPER('Race Results'!F6),2,IF(UPPER(G10)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="J10" s="17">
         <f>IF(I10="","",IF(UPPER(I10)=UPPER('Race Results'!B7),10,IF(UPPER(I10)=UPPER('Race Results'!C7),6,IF(UPPER(I10)=UPPER('Race Results'!D7),4,IF(UPPER(I10)=UPPER('Race Results'!E7),3,IF(UPPER(I10)=UPPER('Race Results'!F7),2,IF(UPPER(I10)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K10" s="15"/>
-      <c r="L10" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="L10" s="17">
         <f>IF(K10="","",IF(UPPER(K10)=UPPER('Race Results'!B8),10,IF(UPPER(K10)=UPPER('Race Results'!C8),6,IF(UPPER(K10)=UPPER('Race Results'!D8),4,IF(UPPER(K10)=UPPER('Race Results'!E8),3,IF(UPPER(K10)=UPPER('Race Results'!F8),2,IF(UPPER(K10)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M10" s="18">
         <f t="shared" si="0"/>
@@ -2761,31 +2811,43 @@
       <c r="A11" s="4">
         <v>8</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="17" t="str">
+      <c r="B11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="17">
         <f>IF(C11="","",IF(UPPER(C11)=UPPER('Race Results'!B4),10,IF(UPPER(C11)=UPPER('Race Results'!C4),6,IF(UPPER(C11)=UPPER('Race Results'!D4),4,IF(UPPER(C11)=UPPER('Race Results'!E4),3,IF(UPPER(C11)=UPPER('Race Results'!F4),2,IF(UPPER(C11)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" s="17">
         <f>IF(E11="","",IF(UPPER(E11)=UPPER('Race Results'!B5),10,IF(UPPER(E11)=UPPER('Race Results'!C5),6,IF(UPPER(E11)=UPPER('Race Results'!D5),4,IF(UPPER(E11)=UPPER('Race Results'!E5),3,IF(UPPER(E11)=UPPER('Race Results'!F5),2,IF(UPPER(E11)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="H11" s="17">
         <f>IF(G11="","",IF(UPPER(G11)=UPPER('Race Results'!B6),10,IF(UPPER(G11)=UPPER('Race Results'!C6),6,IF(UPPER(G11)=UPPER('Race Results'!D6),4,IF(UPPER(G11)=UPPER('Race Results'!E6),3,IF(UPPER(G11)=UPPER('Race Results'!F6),2,IF(UPPER(G11)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="J11" s="17">
         <f>IF(I11="","",IF(UPPER(I11)=UPPER('Race Results'!B7),10,IF(UPPER(I11)=UPPER('Race Results'!C7),6,IF(UPPER(I11)=UPPER('Race Results'!D7),4,IF(UPPER(I11)=UPPER('Race Results'!E7),3,IF(UPPER(I11)=UPPER('Race Results'!F7),2,IF(UPPER(I11)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="L11" s="17">
         <f>IF(K11="","",IF(UPPER(K11)=UPPER('Race Results'!B8),10,IF(UPPER(K11)=UPPER('Race Results'!C8),6,IF(UPPER(K11)=UPPER('Race Results'!D8),4,IF(UPPER(K11)=UPPER('Race Results'!E8),3,IF(UPPER(K11)=UPPER('Race Results'!F8),2,IF(UPPER(K11)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M11" s="18">
         <f t="shared" si="0"/>
@@ -2796,31 +2858,43 @@
       <c r="A12" s="15">
         <v>9</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="17" t="str">
+      <c r="B12" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="17">
         <f>IF(C12="","",IF(UPPER(C12)=UPPER('Race Results'!B4),10,IF(UPPER(C12)=UPPER('Race Results'!C4),6,IF(UPPER(C12)=UPPER('Race Results'!D4),4,IF(UPPER(C12)=UPPER('Race Results'!E4),3,IF(UPPER(C12)=UPPER('Race Results'!F4),2,IF(UPPER(C12)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="17">
         <f>IF(E12="","",IF(UPPER(E12)=UPPER('Race Results'!B5),10,IF(UPPER(E12)=UPPER('Race Results'!C5),6,IF(UPPER(E12)=UPPER('Race Results'!D5),4,IF(UPPER(E12)=UPPER('Race Results'!E5),3,IF(UPPER(E12)=UPPER('Race Results'!F5),2,IF(UPPER(E12)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="H12" s="17">
         <f>IF(G12="","",IF(UPPER(G12)=UPPER('Race Results'!B6),10,IF(UPPER(G12)=UPPER('Race Results'!C6),6,IF(UPPER(G12)=UPPER('Race Results'!D6),4,IF(UPPER(G12)=UPPER('Race Results'!E6),3,IF(UPPER(G12)=UPPER('Race Results'!F6),2,IF(UPPER(G12)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="J12" s="17">
         <f>IF(I12="","",IF(UPPER(I12)=UPPER('Race Results'!B7),10,IF(UPPER(I12)=UPPER('Race Results'!C7),6,IF(UPPER(I12)=UPPER('Race Results'!D7),4,IF(UPPER(I12)=UPPER('Race Results'!E7),3,IF(UPPER(I12)=UPPER('Race Results'!F7),2,IF(UPPER(I12)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L12" s="17">
         <f>IF(K12="","",IF(UPPER(K12)=UPPER('Race Results'!B8),10,IF(UPPER(K12)=UPPER('Race Results'!C8),6,IF(UPPER(K12)=UPPER('Race Results'!D8),4,IF(UPPER(K12)=UPPER('Race Results'!E8),3,IF(UPPER(K12)=UPPER('Race Results'!F8),2,IF(UPPER(K12)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M12" s="18">
         <f t="shared" si="0"/>
@@ -2831,66 +2905,90 @@
       <c r="A13" s="4">
         <v>10</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="17" t="str">
+      <c r="B13" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="17">
         <f>IF(C13="","",IF(UPPER(C13)=UPPER('Race Results'!B4),10,IF(UPPER(C13)=UPPER('Race Results'!C4),6,IF(UPPER(C13)=UPPER('Race Results'!D4),4,IF(UPPER(C13)=UPPER('Race Results'!E4),3,IF(UPPER(C13)=UPPER('Race Results'!F4),2,IF(UPPER(C13)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13" s="17">
         <f>IF(E13="","",IF(UPPER(E13)=UPPER('Race Results'!B5),10,IF(UPPER(E13)=UPPER('Race Results'!C5),6,IF(UPPER(E13)=UPPER('Race Results'!D5),4,IF(UPPER(E13)=UPPER('Race Results'!E5),3,IF(UPPER(E13)=UPPER('Race Results'!F5),2,IF(UPPER(E13)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H13" s="17">
         <f>IF(G13="","",IF(UPPER(G13)=UPPER('Race Results'!B6),10,IF(UPPER(G13)=UPPER('Race Results'!C6),6,IF(UPPER(G13)=UPPER('Race Results'!D6),4,IF(UPPER(G13)=UPPER('Race Results'!E6),3,IF(UPPER(G13)=UPPER('Race Results'!F6),2,IF(UPPER(G13)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J13" s="17">
         <f>IF(I13="","",IF(UPPER(I13)=UPPER('Race Results'!B7),10,IF(UPPER(I13)=UPPER('Race Results'!C7),6,IF(UPPER(I13)=UPPER('Race Results'!D7),4,IF(UPPER(I13)=UPPER('Race Results'!E7),3,IF(UPPER(I13)=UPPER('Race Results'!F7),2,IF(UPPER(I13)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="L13" s="17">
         <f>IF(K13="","",IF(UPPER(K13)=UPPER('Race Results'!B8),10,IF(UPPER(K13)=UPPER('Race Results'!C8),6,IF(UPPER(K13)=UPPER('Race Results'!D8),4,IF(UPPER(K13)=UPPER('Race Results'!E8),3,IF(UPPER(K13)=UPPER('Race Results'!F8),2,IF(UPPER(K13)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M13" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A14" s="15">
         <v>11</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="17" t="str">
+      <c r="B14" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="17">
         <f>IF(C14="","",IF(UPPER(C14)=UPPER('Race Results'!B4),10,IF(UPPER(C14)=UPPER('Race Results'!C4),6,IF(UPPER(C14)=UPPER('Race Results'!D4),4,IF(UPPER(C14)=UPPER('Race Results'!E4),3,IF(UPPER(C14)=UPPER('Race Results'!F4),2,IF(UPPER(C14)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="F14" s="17">
         <f>IF(E14="","",IF(UPPER(E14)=UPPER('Race Results'!B5),10,IF(UPPER(E14)=UPPER('Race Results'!C5),6,IF(UPPER(E14)=UPPER('Race Results'!D5),4,IF(UPPER(E14)=UPPER('Race Results'!E5),3,IF(UPPER(E14)=UPPER('Race Results'!F5),2,IF(UPPER(E14)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="H14" s="17">
         <f>IF(G14="","",IF(UPPER(G14)=UPPER('Race Results'!B6),10,IF(UPPER(G14)=UPPER('Race Results'!C6),6,IF(UPPER(G14)=UPPER('Race Results'!D6),4,IF(UPPER(G14)=UPPER('Race Results'!E6),3,IF(UPPER(G14)=UPPER('Race Results'!F6),2,IF(UPPER(G14)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="J14" s="17">
         <f>IF(I14="","",IF(UPPER(I14)=UPPER('Race Results'!B7),10,IF(UPPER(I14)=UPPER('Race Results'!C7),6,IF(UPPER(I14)=UPPER('Race Results'!D7),4,IF(UPPER(I14)=UPPER('Race Results'!E7),3,IF(UPPER(I14)=UPPER('Race Results'!F7),2,IF(UPPER(I14)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K14" s="15"/>
-      <c r="L14" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="L14" s="17">
         <f>IF(K14="","",IF(UPPER(K14)=UPPER('Race Results'!B8),10,IF(UPPER(K14)=UPPER('Race Results'!C8),6,IF(UPPER(K14)=UPPER('Race Results'!D8),4,IF(UPPER(K14)=UPPER('Race Results'!E8),3,IF(UPPER(K14)=UPPER('Race Results'!F8),2,IF(UPPER(K14)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M14" s="18">
         <f t="shared" si="0"/>
@@ -2901,31 +2999,43 @@
       <c r="A15" s="4">
         <v>12</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="17" t="str">
+      <c r="B15" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="17">
         <f>IF(C15="","",IF(UPPER(C15)=UPPER('Race Results'!B4),10,IF(UPPER(C15)=UPPER('Race Results'!C4),6,IF(UPPER(C15)=UPPER('Race Results'!D4),4,IF(UPPER(C15)=UPPER('Race Results'!E4),3,IF(UPPER(C15)=UPPER('Race Results'!F4),2,IF(UPPER(C15)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F15" s="17">
         <f>IF(E15="","",IF(UPPER(E15)=UPPER('Race Results'!B5),10,IF(UPPER(E15)=UPPER('Race Results'!C5),6,IF(UPPER(E15)=UPPER('Race Results'!D5),4,IF(UPPER(E15)=UPPER('Race Results'!E5),3,IF(UPPER(E15)=UPPER('Race Results'!F5),2,IF(UPPER(E15)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H15" s="17">
         <f>IF(G15="","",IF(UPPER(G15)=UPPER('Race Results'!B6),10,IF(UPPER(G15)=UPPER('Race Results'!C6),6,IF(UPPER(G15)=UPPER('Race Results'!D6),4,IF(UPPER(G15)=UPPER('Race Results'!E6),3,IF(UPPER(G15)=UPPER('Race Results'!F6),2,IF(UPPER(G15)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="J15" s="17">
         <f>IF(I15="","",IF(UPPER(I15)=UPPER('Race Results'!B7),10,IF(UPPER(I15)=UPPER('Race Results'!C7),6,IF(UPPER(I15)=UPPER('Race Results'!D7),4,IF(UPPER(I15)=UPPER('Race Results'!E7),3,IF(UPPER(I15)=UPPER('Race Results'!F7),2,IF(UPPER(I15)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K15" s="4"/>
-      <c r="L15" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L15" s="17">
         <f>IF(K15="","",IF(UPPER(K15)=UPPER('Race Results'!B8),10,IF(UPPER(K15)=UPPER('Race Results'!C8),6,IF(UPPER(K15)=UPPER('Race Results'!D8),4,IF(UPPER(K15)=UPPER('Race Results'!E8),3,IF(UPPER(K15)=UPPER('Race Results'!F8),2,IF(UPPER(K15)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M15" s="18">
         <f t="shared" si="0"/>
@@ -2936,31 +3046,43 @@
       <c r="A16" s="15">
         <v>13</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="17" t="str">
+      <c r="B16" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="17">
         <f>IF(C16="","",IF(UPPER(C16)=UPPER('Race Results'!B4),10,IF(UPPER(C16)=UPPER('Race Results'!C4),6,IF(UPPER(C16)=UPPER('Race Results'!D4),4,IF(UPPER(C16)=UPPER('Race Results'!E4),3,IF(UPPER(C16)=UPPER('Race Results'!F4),2,IF(UPPER(C16)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E16" s="15"/>
-      <c r="F16" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="17">
         <f>IF(E16="","",IF(UPPER(E16)=UPPER('Race Results'!B5),10,IF(UPPER(E16)=UPPER('Race Results'!C5),6,IF(UPPER(E16)=UPPER('Race Results'!D5),4,IF(UPPER(E16)=UPPER('Race Results'!E5),3,IF(UPPER(E16)=UPPER('Race Results'!F5),2,IF(UPPER(E16)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="H16" s="17">
         <f>IF(G16="","",IF(UPPER(G16)=UPPER('Race Results'!B6),10,IF(UPPER(G16)=UPPER('Race Results'!C6),6,IF(UPPER(G16)=UPPER('Race Results'!D6),4,IF(UPPER(G16)=UPPER('Race Results'!E6),3,IF(UPPER(G16)=UPPER('Race Results'!F6),2,IF(UPPER(G16)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I16" s="15"/>
-      <c r="J16" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="J16" s="17">
         <f>IF(I16="","",IF(UPPER(I16)=UPPER('Race Results'!B7),10,IF(UPPER(I16)=UPPER('Race Results'!C7),6,IF(UPPER(I16)=UPPER('Race Results'!D7),4,IF(UPPER(I16)=UPPER('Race Results'!E7),3,IF(UPPER(I16)=UPPER('Race Results'!F7),2,IF(UPPER(I16)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K16" s="15"/>
-      <c r="L16" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="L16" s="17">
         <f>IF(K16="","",IF(UPPER(K16)=UPPER('Race Results'!B8),10,IF(UPPER(K16)=UPPER('Race Results'!C8),6,IF(UPPER(K16)=UPPER('Race Results'!D8),4,IF(UPPER(K16)=UPPER('Race Results'!E8),3,IF(UPPER(K16)=UPPER('Race Results'!F8),2,IF(UPPER(K16)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M16" s="18">
         <f t="shared" si="0"/>
@@ -2971,31 +3093,43 @@
       <c r="A17" s="4">
         <v>14</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="17" t="str">
+      <c r="B17" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="17">
         <f>IF(C17="","",IF(UPPER(C17)=UPPER('Race Results'!B4),10,IF(UPPER(C17)=UPPER('Race Results'!C4),6,IF(UPPER(C17)=UPPER('Race Results'!D4),4,IF(UPPER(C17)=UPPER('Race Results'!E4),3,IF(UPPER(C17)=UPPER('Race Results'!F4),2,IF(UPPER(C17)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="17">
         <f>IF(E17="","",IF(UPPER(E17)=UPPER('Race Results'!B5),10,IF(UPPER(E17)=UPPER('Race Results'!C5),6,IF(UPPER(E17)=UPPER('Race Results'!D5),4,IF(UPPER(E17)=UPPER('Race Results'!E5),3,IF(UPPER(E17)=UPPER('Race Results'!F5),2,IF(UPPER(E17)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H17" s="17">
         <f>IF(G17="","",IF(UPPER(G17)=UPPER('Race Results'!B6),10,IF(UPPER(G17)=UPPER('Race Results'!C6),6,IF(UPPER(G17)=UPPER('Race Results'!D6),4,IF(UPPER(G17)=UPPER('Race Results'!E6),3,IF(UPPER(G17)=UPPER('Race Results'!F6),2,IF(UPPER(G17)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J17" s="17">
         <f>IF(I17="","",IF(UPPER(I17)=UPPER('Race Results'!B7),10,IF(UPPER(I17)=UPPER('Race Results'!C7),6,IF(UPPER(I17)=UPPER('Race Results'!D7),4,IF(UPPER(I17)=UPPER('Race Results'!E7),3,IF(UPPER(I17)=UPPER('Race Results'!F7),2,IF(UPPER(I17)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K17" s="4"/>
-      <c r="L17" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="L17" s="17">
         <f>IF(K17="","",IF(UPPER(K17)=UPPER('Race Results'!B8),10,IF(UPPER(K17)=UPPER('Race Results'!C8),6,IF(UPPER(K17)=UPPER('Race Results'!D8),4,IF(UPPER(K17)=UPPER('Race Results'!E8),3,IF(UPPER(K17)=UPPER('Race Results'!F8),2,IF(UPPER(K17)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M17" s="18">
         <f t="shared" si="0"/>
@@ -3006,31 +3140,43 @@
       <c r="A18" s="15">
         <v>15</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="17" t="str">
+      <c r="B18" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="17">
         <f>IF(C18="","",IF(UPPER(C18)=UPPER('Race Results'!B4),10,IF(UPPER(C18)=UPPER('Race Results'!C4),6,IF(UPPER(C18)=UPPER('Race Results'!D4),4,IF(UPPER(C18)=UPPER('Race Results'!E4),3,IF(UPPER(C18)=UPPER('Race Results'!F4),2,IF(UPPER(C18)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="F18" s="17">
         <f>IF(E18="","",IF(UPPER(E18)=UPPER('Race Results'!B5),10,IF(UPPER(E18)=UPPER('Race Results'!C5),6,IF(UPPER(E18)=UPPER('Race Results'!D5),4,IF(UPPER(E18)=UPPER('Race Results'!E5),3,IF(UPPER(E18)=UPPER('Race Results'!F5),2,IF(UPPER(E18)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="H18" s="17">
         <f>IF(G18="","",IF(UPPER(G18)=UPPER('Race Results'!B6),10,IF(UPPER(G18)=UPPER('Race Results'!C6),6,IF(UPPER(G18)=UPPER('Race Results'!D6),4,IF(UPPER(G18)=UPPER('Race Results'!E6),3,IF(UPPER(G18)=UPPER('Race Results'!F6),2,IF(UPPER(G18)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I18" s="15"/>
-      <c r="J18" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="J18" s="17">
         <f>IF(I18="","",IF(UPPER(I18)=UPPER('Race Results'!B7),10,IF(UPPER(I18)=UPPER('Race Results'!C7),6,IF(UPPER(I18)=UPPER('Race Results'!D7),4,IF(UPPER(I18)=UPPER('Race Results'!E7),3,IF(UPPER(I18)=UPPER('Race Results'!F7),2,IF(UPPER(I18)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K18" s="15"/>
-      <c r="L18" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L18" s="17">
         <f>IF(K18="","",IF(UPPER(K18)=UPPER('Race Results'!B8),10,IF(UPPER(K18)=UPPER('Race Results'!C8),6,IF(UPPER(K18)=UPPER('Race Results'!D8),4,IF(UPPER(K18)=UPPER('Race Results'!E8),3,IF(UPPER(K18)=UPPER('Race Results'!F8),2,IF(UPPER(K18)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M18" s="18">
         <f t="shared" si="0"/>
@@ -3041,31 +3187,43 @@
       <c r="A19" s="4">
         <v>16</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="17" t="str">
+      <c r="B19" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="17">
         <f>IF(C19="","",IF(UPPER(C19)=UPPER('Race Results'!B4),10,IF(UPPER(C19)=UPPER('Race Results'!C4),6,IF(UPPER(C19)=UPPER('Race Results'!D4),4,IF(UPPER(C19)=UPPER('Race Results'!E4),3,IF(UPPER(C19)=UPPER('Race Results'!F4),2,IF(UPPER(C19)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" s="17">
         <f>IF(E19="","",IF(UPPER(E19)=UPPER('Race Results'!B5),10,IF(UPPER(E19)=UPPER('Race Results'!C5),6,IF(UPPER(E19)=UPPER('Race Results'!D5),4,IF(UPPER(E19)=UPPER('Race Results'!E5),3,IF(UPPER(E19)=UPPER('Race Results'!F5),2,IF(UPPER(E19)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="17">
         <f>IF(G19="","",IF(UPPER(G19)=UPPER('Race Results'!B6),10,IF(UPPER(G19)=UPPER('Race Results'!C6),6,IF(UPPER(G19)=UPPER('Race Results'!D6),4,IF(UPPER(G19)=UPPER('Race Results'!E6),3,IF(UPPER(G19)=UPPER('Race Results'!F6),2,IF(UPPER(G19)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I19" s="4"/>
-      <c r="J19" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J19" s="17">
         <f>IF(I19="","",IF(UPPER(I19)=UPPER('Race Results'!B7),10,IF(UPPER(I19)=UPPER('Race Results'!C7),6,IF(UPPER(I19)=UPPER('Race Results'!D7),4,IF(UPPER(I19)=UPPER('Race Results'!E7),3,IF(UPPER(I19)=UPPER('Race Results'!F7),2,IF(UPPER(I19)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K19" s="4"/>
-      <c r="L19" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="L19" s="17">
         <f>IF(K19="","",IF(UPPER(K19)=UPPER('Race Results'!B8),10,IF(UPPER(K19)=UPPER('Race Results'!C8),6,IF(UPPER(K19)=UPPER('Race Results'!D8),4,IF(UPPER(K19)=UPPER('Race Results'!E8),3,IF(UPPER(K19)=UPPER('Race Results'!F8),2,IF(UPPER(K19)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M19" s="18">
         <f t="shared" si="0"/>
@@ -3076,31 +3234,43 @@
       <c r="A20" s="15">
         <v>17</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="17" t="str">
+      <c r="B20" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" s="17">
         <f>IF(C20="","",IF(UPPER(C20)=UPPER('Race Results'!B4),10,IF(UPPER(C20)=UPPER('Race Results'!C4),6,IF(UPPER(C20)=UPPER('Race Results'!D4),4,IF(UPPER(C20)=UPPER('Race Results'!E4),3,IF(UPPER(C20)=UPPER('Race Results'!F4),2,IF(UPPER(C20)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E20" s="15"/>
-      <c r="F20" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" s="17">
         <f>IF(E20="","",IF(UPPER(E20)=UPPER('Race Results'!B5),10,IF(UPPER(E20)=UPPER('Race Results'!C5),6,IF(UPPER(E20)=UPPER('Race Results'!D5),4,IF(UPPER(E20)=UPPER('Race Results'!E5),3,IF(UPPER(E20)=UPPER('Race Results'!F5),2,IF(UPPER(E20)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G20" s="15"/>
-      <c r="H20" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="H20" s="17">
         <f>IF(G20="","",IF(UPPER(G20)=UPPER('Race Results'!B6),10,IF(UPPER(G20)=UPPER('Race Results'!C6),6,IF(UPPER(G20)=UPPER('Race Results'!D6),4,IF(UPPER(G20)=UPPER('Race Results'!E6),3,IF(UPPER(G20)=UPPER('Race Results'!F6),2,IF(UPPER(G20)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I20" s="15"/>
-      <c r="J20" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="J20" s="17">
         <f>IF(I20="","",IF(UPPER(I20)=UPPER('Race Results'!B7),10,IF(UPPER(I20)=UPPER('Race Results'!C7),6,IF(UPPER(I20)=UPPER('Race Results'!D7),4,IF(UPPER(I20)=UPPER('Race Results'!E7),3,IF(UPPER(I20)=UPPER('Race Results'!F7),2,IF(UPPER(I20)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K20" s="15"/>
-      <c r="L20" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="L20" s="17">
         <f>IF(K20="","",IF(UPPER(K20)=UPPER('Race Results'!B8),10,IF(UPPER(K20)=UPPER('Race Results'!C8),6,IF(UPPER(K20)=UPPER('Race Results'!D8),4,IF(UPPER(K20)=UPPER('Race Results'!E8),3,IF(UPPER(K20)=UPPER('Race Results'!F8),2,IF(UPPER(K20)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M20" s="18">
         <f t="shared" si="0"/>
@@ -3111,31 +3281,43 @@
       <c r="A21" s="4">
         <v>18</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="17" t="str">
+      <c r="B21" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="17">
         <f>IF(C21="","",IF(UPPER(C21)=UPPER('Race Results'!B4),10,IF(UPPER(C21)=UPPER('Race Results'!C4),6,IF(UPPER(C21)=UPPER('Race Results'!D4),4,IF(UPPER(C21)=UPPER('Race Results'!E4),3,IF(UPPER(C21)=UPPER('Race Results'!F4),2,IF(UPPER(C21)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="17">
         <f>IF(E21="","",IF(UPPER(E21)=UPPER('Race Results'!B5),10,IF(UPPER(E21)=UPPER('Race Results'!C5),6,IF(UPPER(E21)=UPPER('Race Results'!D5),4,IF(UPPER(E21)=UPPER('Race Results'!E5),3,IF(UPPER(E21)=UPPER('Race Results'!F5),2,IF(UPPER(E21)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="H21" s="17">
         <f>IF(G21="","",IF(UPPER(G21)=UPPER('Race Results'!B6),10,IF(UPPER(G21)=UPPER('Race Results'!C6),6,IF(UPPER(G21)=UPPER('Race Results'!D6),4,IF(UPPER(G21)=UPPER('Race Results'!E6),3,IF(UPPER(G21)=UPPER('Race Results'!F6),2,IF(UPPER(G21)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I21" s="4"/>
-      <c r="J21" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J21" s="17">
         <f>IF(I21="","",IF(UPPER(I21)=UPPER('Race Results'!B7),10,IF(UPPER(I21)=UPPER('Race Results'!C7),6,IF(UPPER(I21)=UPPER('Race Results'!D7),4,IF(UPPER(I21)=UPPER('Race Results'!E7),3,IF(UPPER(I21)=UPPER('Race Results'!F7),2,IF(UPPER(I21)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K21" s="4"/>
-      <c r="L21" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="L21" s="17">
         <f>IF(K21="","",IF(UPPER(K21)=UPPER('Race Results'!B8),10,IF(UPPER(K21)=UPPER('Race Results'!C8),6,IF(UPPER(K21)=UPPER('Race Results'!D8),4,IF(UPPER(K21)=UPPER('Race Results'!E8),3,IF(UPPER(K21)=UPPER('Race Results'!F8),2,IF(UPPER(K21)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M21" s="18">
         <f t="shared" si="0"/>
@@ -3146,31 +3328,43 @@
       <c r="A22" s="15">
         <v>19</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="17" t="str">
+      <c r="B22" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" s="17">
         <f>IF(C22="","",IF(UPPER(C22)=UPPER('Race Results'!B4),10,IF(UPPER(C22)=UPPER('Race Results'!C4),6,IF(UPPER(C22)=UPPER('Race Results'!D4),4,IF(UPPER(C22)=UPPER('Race Results'!E4),3,IF(UPPER(C22)=UPPER('Race Results'!F4),2,IF(UPPER(C22)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E22" s="15"/>
-      <c r="F22" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="F22" s="17">
         <f>IF(E22="","",IF(UPPER(E22)=UPPER('Race Results'!B5),10,IF(UPPER(E22)=UPPER('Race Results'!C5),6,IF(UPPER(E22)=UPPER('Race Results'!D5),4,IF(UPPER(E22)=UPPER('Race Results'!E5),3,IF(UPPER(E22)=UPPER('Race Results'!F5),2,IF(UPPER(E22)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G22" s="15"/>
-      <c r="H22" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="H22" s="17">
         <f>IF(G22="","",IF(UPPER(G22)=UPPER('Race Results'!B6),10,IF(UPPER(G22)=UPPER('Race Results'!C6),6,IF(UPPER(G22)=UPPER('Race Results'!D6),4,IF(UPPER(G22)=UPPER('Race Results'!E6),3,IF(UPPER(G22)=UPPER('Race Results'!F6),2,IF(UPPER(G22)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I22" s="15"/>
-      <c r="J22" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J22" s="17">
         <f>IF(I22="","",IF(UPPER(I22)=UPPER('Race Results'!B7),10,IF(UPPER(I22)=UPPER('Race Results'!C7),6,IF(UPPER(I22)=UPPER('Race Results'!D7),4,IF(UPPER(I22)=UPPER('Race Results'!E7),3,IF(UPPER(I22)=UPPER('Race Results'!F7),2,IF(UPPER(I22)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K22" s="15"/>
-      <c r="L22" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="L22" s="17">
         <f>IF(K22="","",IF(UPPER(K22)=UPPER('Race Results'!B8),10,IF(UPPER(K22)=UPPER('Race Results'!C8),6,IF(UPPER(K22)=UPPER('Race Results'!D8),4,IF(UPPER(K22)=UPPER('Race Results'!E8),3,IF(UPPER(K22)=UPPER('Race Results'!F8),2,IF(UPPER(K22)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M22" s="18">
         <f t="shared" si="0"/>
@@ -3181,31 +3375,43 @@
       <c r="A23" s="4">
         <v>20</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="17" t="str">
+      <c r="B23" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="17">
         <f>IF(C23="","",IF(UPPER(C23)=UPPER('Race Results'!B4),10,IF(UPPER(C23)=UPPER('Race Results'!C4),6,IF(UPPER(C23)=UPPER('Race Results'!D4),4,IF(UPPER(C23)=UPPER('Race Results'!E4),3,IF(UPPER(C23)=UPPER('Race Results'!F4),2,IF(UPPER(C23)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23" s="17">
         <f>IF(E23="","",IF(UPPER(E23)=UPPER('Race Results'!B5),10,IF(UPPER(E23)=UPPER('Race Results'!C5),6,IF(UPPER(E23)=UPPER('Race Results'!D5),4,IF(UPPER(E23)=UPPER('Race Results'!E5),3,IF(UPPER(E23)=UPPER('Race Results'!F5),2,IF(UPPER(E23)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H23" s="17">
         <f>IF(G23="","",IF(UPPER(G23)=UPPER('Race Results'!B6),10,IF(UPPER(G23)=UPPER('Race Results'!C6),6,IF(UPPER(G23)=UPPER('Race Results'!D6),4,IF(UPPER(G23)=UPPER('Race Results'!E6),3,IF(UPPER(G23)=UPPER('Race Results'!F6),2,IF(UPPER(G23)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I23" s="4"/>
-      <c r="J23" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J23" s="17">
         <f>IF(I23="","",IF(UPPER(I23)=UPPER('Race Results'!B7),10,IF(UPPER(I23)=UPPER('Race Results'!C7),6,IF(UPPER(I23)=UPPER('Race Results'!D7),4,IF(UPPER(I23)=UPPER('Race Results'!E7),3,IF(UPPER(I23)=UPPER('Race Results'!F7),2,IF(UPPER(I23)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K23" s="4"/>
-      <c r="L23" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L23" s="17">
         <f>IF(K23="","",IF(UPPER(K23)=UPPER('Race Results'!B8),10,IF(UPPER(K23)=UPPER('Race Results'!C8),6,IF(UPPER(K23)=UPPER('Race Results'!D8),4,IF(UPPER(K23)=UPPER('Race Results'!E8),3,IF(UPPER(K23)=UPPER('Race Results'!F8),2,IF(UPPER(K23)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M23" s="18">
         <f t="shared" si="0"/>
@@ -3216,31 +3422,43 @@
       <c r="A24" s="15">
         <v>21</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="17" t="str">
+      <c r="B24" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="17">
         <f>IF(C24="","",IF(UPPER(C24)=UPPER('Race Results'!B4),10,IF(UPPER(C24)=UPPER('Race Results'!C4),6,IF(UPPER(C24)=UPPER('Race Results'!D4),4,IF(UPPER(C24)=UPPER('Race Results'!E4),3,IF(UPPER(C24)=UPPER('Race Results'!F4),2,IF(UPPER(C24)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="F24" s="17">
         <f>IF(E24="","",IF(UPPER(E24)=UPPER('Race Results'!B5),10,IF(UPPER(E24)=UPPER('Race Results'!C5),6,IF(UPPER(E24)=UPPER('Race Results'!D5),4,IF(UPPER(E24)=UPPER('Race Results'!E5),3,IF(UPPER(E24)=UPPER('Race Results'!F5),2,IF(UPPER(E24)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G24" s="15"/>
-      <c r="H24" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="H24" s="17">
         <f>IF(G24="","",IF(UPPER(G24)=UPPER('Race Results'!B6),10,IF(UPPER(G24)=UPPER('Race Results'!C6),6,IF(UPPER(G24)=UPPER('Race Results'!D6),4,IF(UPPER(G24)=UPPER('Race Results'!E6),3,IF(UPPER(G24)=UPPER('Race Results'!F6),2,IF(UPPER(G24)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I24" s="15"/>
-      <c r="J24" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="J24" s="17">
         <f>IF(I24="","",IF(UPPER(I24)=UPPER('Race Results'!B7),10,IF(UPPER(I24)=UPPER('Race Results'!C7),6,IF(UPPER(I24)=UPPER('Race Results'!D7),4,IF(UPPER(I24)=UPPER('Race Results'!E7),3,IF(UPPER(I24)=UPPER('Race Results'!F7),2,IF(UPPER(I24)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K24" s="15"/>
-      <c r="L24" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L24" s="17">
         <f>IF(K24="","",IF(UPPER(K24)=UPPER('Race Results'!B8),10,IF(UPPER(K24)=UPPER('Race Results'!C8),6,IF(UPPER(K24)=UPPER('Race Results'!D8),4,IF(UPPER(K24)=UPPER('Race Results'!E8),3,IF(UPPER(K24)=UPPER('Race Results'!F8),2,IF(UPPER(K24)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M24" s="18">
         <f t="shared" si="0"/>
@@ -3251,31 +3469,43 @@
       <c r="A25" s="4">
         <v>22</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="17" t="str">
+      <c r="B25" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25" s="17">
         <f>IF(C25="","",IF(UPPER(C25)=UPPER('Race Results'!B4),10,IF(UPPER(C25)=UPPER('Race Results'!C4),6,IF(UPPER(C25)=UPPER('Race Results'!D4),4,IF(UPPER(C25)=UPPER('Race Results'!E4),3,IF(UPPER(C25)=UPPER('Race Results'!F4),2,IF(UPPER(C25)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F25" s="17">
         <f>IF(E25="","",IF(UPPER(E25)=UPPER('Race Results'!B5),10,IF(UPPER(E25)=UPPER('Race Results'!C5),6,IF(UPPER(E25)=UPPER('Race Results'!D5),4,IF(UPPER(E25)=UPPER('Race Results'!E5),3,IF(UPPER(E25)=UPPER('Race Results'!F5),2,IF(UPPER(E25)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H25" s="17">
         <f>IF(G25="","",IF(UPPER(G25)=UPPER('Race Results'!B6),10,IF(UPPER(G25)=UPPER('Race Results'!C6),6,IF(UPPER(G25)=UPPER('Race Results'!D6),4,IF(UPPER(G25)=UPPER('Race Results'!E6),3,IF(UPPER(G25)=UPPER('Race Results'!F6),2,IF(UPPER(G25)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I25" s="4"/>
-      <c r="J25" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="J25" s="17">
         <f>IF(I25="","",IF(UPPER(I25)=UPPER('Race Results'!B7),10,IF(UPPER(I25)=UPPER('Race Results'!C7),6,IF(UPPER(I25)=UPPER('Race Results'!D7),4,IF(UPPER(I25)=UPPER('Race Results'!E7),3,IF(UPPER(I25)=UPPER('Race Results'!F7),2,IF(UPPER(I25)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K25" s="4"/>
-      <c r="L25" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="L25" s="17">
         <f>IF(K25="","",IF(UPPER(K25)=UPPER('Race Results'!B8),10,IF(UPPER(K25)=UPPER('Race Results'!C8),6,IF(UPPER(K25)=UPPER('Race Results'!D8),4,IF(UPPER(K25)=UPPER('Race Results'!E8),3,IF(UPPER(K25)=UPPER('Race Results'!F8),2,IF(UPPER(K25)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M25" s="18">
         <f t="shared" si="0"/>
@@ -3286,66 +3516,90 @@
       <c r="A26" s="15">
         <v>23</v>
       </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="17" t="str">
+      <c r="B26" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" s="17">
         <f>IF(C26="","",IF(UPPER(C26)=UPPER('Race Results'!B4),10,IF(UPPER(C26)=UPPER('Race Results'!C4),6,IF(UPPER(C26)=UPPER('Race Results'!D4),4,IF(UPPER(C26)=UPPER('Race Results'!E4),3,IF(UPPER(C26)=UPPER('Race Results'!F4),2,IF(UPPER(C26)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" s="17">
         <f>IF(E26="","",IF(UPPER(E26)=UPPER('Race Results'!B5),10,IF(UPPER(E26)=UPPER('Race Results'!C5),6,IF(UPPER(E26)=UPPER('Race Results'!D5),4,IF(UPPER(E26)=UPPER('Race Results'!E5),3,IF(UPPER(E26)=UPPER('Race Results'!F5),2,IF(UPPER(E26)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G26" s="15"/>
-      <c r="H26" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="H26" s="17">
         <f>IF(G26="","",IF(UPPER(G26)=UPPER('Race Results'!B6),10,IF(UPPER(G26)=UPPER('Race Results'!C6),6,IF(UPPER(G26)=UPPER('Race Results'!D6),4,IF(UPPER(G26)=UPPER('Race Results'!E6),3,IF(UPPER(G26)=UPPER('Race Results'!F6),2,IF(UPPER(G26)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I26" s="15"/>
-      <c r="J26" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="J26" s="17">
         <f>IF(I26="","",IF(UPPER(I26)=UPPER('Race Results'!B7),10,IF(UPPER(I26)=UPPER('Race Results'!C7),6,IF(UPPER(I26)=UPPER('Race Results'!D7),4,IF(UPPER(I26)=UPPER('Race Results'!E7),3,IF(UPPER(I26)=UPPER('Race Results'!F7),2,IF(UPPER(I26)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K26" s="15"/>
-      <c r="L26" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="L26" s="17">
         <f>IF(K26="","",IF(UPPER(K26)=UPPER('Race Results'!B8),10,IF(UPPER(K26)=UPPER('Race Results'!C8),6,IF(UPPER(K26)=UPPER('Race Results'!D8),4,IF(UPPER(K26)=UPPER('Race Results'!E8),3,IF(UPPER(K26)=UPPER('Race Results'!F8),2,IF(UPPER(K26)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M26" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>24</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="17" t="str">
+      <c r="B27" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" s="17">
         <f>IF(C27="","",IF(UPPER(C27)=UPPER('Race Results'!B4),10,IF(UPPER(C27)=UPPER('Race Results'!C4),6,IF(UPPER(C27)=UPPER('Race Results'!D4),4,IF(UPPER(C27)=UPPER('Race Results'!E4),3,IF(UPPER(C27)=UPPER('Race Results'!F4),2,IF(UPPER(C27)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F27" s="17">
         <f>IF(E27="","",IF(UPPER(E27)=UPPER('Race Results'!B5),10,IF(UPPER(E27)=UPPER('Race Results'!C5),6,IF(UPPER(E27)=UPPER('Race Results'!D5),4,IF(UPPER(E27)=UPPER('Race Results'!E5),3,IF(UPPER(E27)=UPPER('Race Results'!F5),2,IF(UPPER(E27)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H27" s="17">
         <f>IF(G27="","",IF(UPPER(G27)=UPPER('Race Results'!B6),10,IF(UPPER(G27)=UPPER('Race Results'!C6),6,IF(UPPER(G27)=UPPER('Race Results'!D6),4,IF(UPPER(G27)=UPPER('Race Results'!E6),3,IF(UPPER(G27)=UPPER('Race Results'!F6),2,IF(UPPER(G27)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I27" s="4"/>
-      <c r="J27" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J27" s="17">
         <f>IF(I27="","",IF(UPPER(I27)=UPPER('Race Results'!B7),10,IF(UPPER(I27)=UPPER('Race Results'!C7),6,IF(UPPER(I27)=UPPER('Race Results'!D7),4,IF(UPPER(I27)=UPPER('Race Results'!E7),3,IF(UPPER(I27)=UPPER('Race Results'!F7),2,IF(UPPER(I27)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K27" s="4"/>
-      <c r="L27" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="L27" s="17">
         <f>IF(K27="","",IF(UPPER(K27)=UPPER('Race Results'!B8),10,IF(UPPER(K27)=UPPER('Race Results'!C8),6,IF(UPPER(K27)=UPPER('Race Results'!D8),4,IF(UPPER(K27)=UPPER('Race Results'!E8),3,IF(UPPER(K27)=UPPER('Race Results'!F8),2,IF(UPPER(K27)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M27" s="18">
         <f t="shared" si="0"/>
@@ -3356,31 +3610,43 @@
       <c r="A28" s="15">
         <v>25</v>
       </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="17" t="str">
+      <c r="B28" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="17">
         <f>IF(C28="","",IF(UPPER(C28)=UPPER('Race Results'!B4),10,IF(UPPER(C28)=UPPER('Race Results'!C4),6,IF(UPPER(C28)=UPPER('Race Results'!D4),4,IF(UPPER(C28)=UPPER('Race Results'!E4),3,IF(UPPER(C28)=UPPER('Race Results'!F4),2,IF(UPPER(C28)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E28" s="15"/>
-      <c r="F28" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="F28" s="17">
         <f>IF(E28="","",IF(UPPER(E28)=UPPER('Race Results'!B5),10,IF(UPPER(E28)=UPPER('Race Results'!C5),6,IF(UPPER(E28)=UPPER('Race Results'!D5),4,IF(UPPER(E28)=UPPER('Race Results'!E5),3,IF(UPPER(E28)=UPPER('Race Results'!F5),2,IF(UPPER(E28)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G28" s="15"/>
-      <c r="H28" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="H28" s="17">
         <f>IF(G28="","",IF(UPPER(G28)=UPPER('Race Results'!B6),10,IF(UPPER(G28)=UPPER('Race Results'!C6),6,IF(UPPER(G28)=UPPER('Race Results'!D6),4,IF(UPPER(G28)=UPPER('Race Results'!E6),3,IF(UPPER(G28)=UPPER('Race Results'!F6),2,IF(UPPER(G28)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I28" s="15"/>
-      <c r="J28" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="J28" s="17">
         <f>IF(I28="","",IF(UPPER(I28)=UPPER('Race Results'!B7),10,IF(UPPER(I28)=UPPER('Race Results'!C7),6,IF(UPPER(I28)=UPPER('Race Results'!D7),4,IF(UPPER(I28)=UPPER('Race Results'!E7),3,IF(UPPER(I28)=UPPER('Race Results'!F7),2,IF(UPPER(I28)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K28" s="15"/>
-      <c r="L28" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="L28" s="17">
         <f>IF(K28="","",IF(UPPER(K28)=UPPER('Race Results'!B8),10,IF(UPPER(K28)=UPPER('Race Results'!C8),6,IF(UPPER(K28)=UPPER('Race Results'!D8),4,IF(UPPER(K28)=UPPER('Race Results'!E8),3,IF(UPPER(K28)=UPPER('Race Results'!F8),2,IF(UPPER(K28)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M28" s="18">
         <f t="shared" si="0"/>
@@ -3391,31 +3657,43 @@
       <c r="A29" s="4">
         <v>26</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="17" t="str">
+      <c r="B29" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D29" s="17">
         <f>IF(C29="","",IF(UPPER(C29)=UPPER('Race Results'!B4),10,IF(UPPER(C29)=UPPER('Race Results'!C4),6,IF(UPPER(C29)=UPPER('Race Results'!D4),4,IF(UPPER(C29)=UPPER('Race Results'!E4),3,IF(UPPER(C29)=UPPER('Race Results'!F4),2,IF(UPPER(C29)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F29" s="17">
         <f>IF(E29="","",IF(UPPER(E29)=UPPER('Race Results'!B5),10,IF(UPPER(E29)=UPPER('Race Results'!C5),6,IF(UPPER(E29)=UPPER('Race Results'!D5),4,IF(UPPER(E29)=UPPER('Race Results'!E5),3,IF(UPPER(E29)=UPPER('Race Results'!F5),2,IF(UPPER(E29)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G29" s="4"/>
-      <c r="H29" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H29" s="17">
         <f>IF(G29="","",IF(UPPER(G29)=UPPER('Race Results'!B6),10,IF(UPPER(G29)=UPPER('Race Results'!C6),6,IF(UPPER(G29)=UPPER('Race Results'!D6),4,IF(UPPER(G29)=UPPER('Race Results'!E6),3,IF(UPPER(G29)=UPPER('Race Results'!F6),2,IF(UPPER(G29)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I29" s="4"/>
-      <c r="J29" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J29" s="17">
         <f>IF(I29="","",IF(UPPER(I29)=UPPER('Race Results'!B7),10,IF(UPPER(I29)=UPPER('Race Results'!C7),6,IF(UPPER(I29)=UPPER('Race Results'!D7),4,IF(UPPER(I29)=UPPER('Race Results'!E7),3,IF(UPPER(I29)=UPPER('Race Results'!F7),2,IF(UPPER(I29)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K29" s="4"/>
-      <c r="L29" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="L29" s="17">
         <f>IF(K29="","",IF(UPPER(K29)=UPPER('Race Results'!B8),10,IF(UPPER(K29)=UPPER('Race Results'!C8),6,IF(UPPER(K29)=UPPER('Race Results'!D8),4,IF(UPPER(K29)=UPPER('Race Results'!E8),3,IF(UPPER(K29)=UPPER('Race Results'!F8),2,IF(UPPER(K29)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M29" s="18">
         <f t="shared" si="0"/>
@@ -3426,31 +3704,43 @@
       <c r="A30" s="15">
         <v>27</v>
       </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="17" t="str">
+      <c r="B30" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" s="17">
         <f>IF(C30="","",IF(UPPER(C30)=UPPER('Race Results'!B4),10,IF(UPPER(C30)=UPPER('Race Results'!C4),6,IF(UPPER(C30)=UPPER('Race Results'!D4),4,IF(UPPER(C30)=UPPER('Race Results'!E4),3,IF(UPPER(C30)=UPPER('Race Results'!F4),2,IF(UPPER(C30)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="F30" s="17">
         <f>IF(E30="","",IF(UPPER(E30)=UPPER('Race Results'!B5),10,IF(UPPER(E30)=UPPER('Race Results'!C5),6,IF(UPPER(E30)=UPPER('Race Results'!D5),4,IF(UPPER(E30)=UPPER('Race Results'!E5),3,IF(UPPER(E30)=UPPER('Race Results'!F5),2,IF(UPPER(E30)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G30" s="15"/>
-      <c r="H30" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H30" s="17">
         <f>IF(G30="","",IF(UPPER(G30)=UPPER('Race Results'!B6),10,IF(UPPER(G30)=UPPER('Race Results'!C6),6,IF(UPPER(G30)=UPPER('Race Results'!D6),4,IF(UPPER(G30)=UPPER('Race Results'!E6),3,IF(UPPER(G30)=UPPER('Race Results'!F6),2,IF(UPPER(G30)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I30" s="15"/>
-      <c r="J30" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J30" s="17">
         <f>IF(I30="","",IF(UPPER(I30)=UPPER('Race Results'!B7),10,IF(UPPER(I30)=UPPER('Race Results'!C7),6,IF(UPPER(I30)=UPPER('Race Results'!D7),4,IF(UPPER(I30)=UPPER('Race Results'!E7),3,IF(UPPER(I30)=UPPER('Race Results'!F7),2,IF(UPPER(I30)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K30" s="15"/>
-      <c r="L30" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L30" s="17">
         <f>IF(K30="","",IF(UPPER(K30)=UPPER('Race Results'!B8),10,IF(UPPER(K30)=UPPER('Race Results'!C8),6,IF(UPPER(K30)=UPPER('Race Results'!D8),4,IF(UPPER(K30)=UPPER('Race Results'!E8),3,IF(UPPER(K30)=UPPER('Race Results'!F8),2,IF(UPPER(K30)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M30" s="18">
         <f t="shared" si="0"/>
@@ -3571,7 +3861,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="140" yWindow="396" count="6">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="752" yWindow="747" count="6">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Guest Name" prompt="Start typing or pick from guest list" xr:uid="{00000000-0002-0000-0300-000000000000}">
           <x14:formula1>
             <xm:f>'Guest List'!$B$4:$B$53</xm:f>
@@ -3674,15 +3964,15 @@
       </c>
       <c r="B3" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,1),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Mick Hogg</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C3" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,1),"")</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D3" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C3,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -3691,11 +3981,11 @@
       </c>
       <c r="B4" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Steve Burfitt</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C4" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),"")</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D4" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C4,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -3706,9 +3996,9 @@
       <c r="A5" s="19">
         <v>3</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,3),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C5" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,3),"")</f>
@@ -3723,9 +4013,9 @@
       <c r="A6" s="23">
         <v>4</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,4),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C6" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,4),"")</f>
@@ -3740,9 +4030,9 @@
       <c r="A7" s="27">
         <v>5</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,5),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C7" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,5),"")</f>
@@ -3757,9 +4047,9 @@
       <c r="A8" s="23">
         <v>6</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,6),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C8" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,6),"")</f>
@@ -3774,9 +4064,9 @@
       <c r="A9" s="27">
         <v>7</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,7),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C9" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,7),"")</f>
@@ -3791,9 +4081,9 @@
       <c r="A10" s="23">
         <v>8</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,8),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C10" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,8),"")</f>
@@ -3808,9 +4098,9 @@
       <c r="A11" s="27">
         <v>9</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,9),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C11" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,9),"")</f>
@@ -3825,9 +4115,9 @@
       <c r="A12" s="23">
         <v>10</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,10),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C12" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,10),"")</f>
@@ -3842,9 +4132,9 @@
       <c r="A13" s="27">
         <v>11</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,11),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C13" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,11),"")</f>
@@ -3859,9 +4149,9 @@
       <c r="A14" s="23">
         <v>12</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,12),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C14" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,12),"")</f>
@@ -3876,9 +4166,9 @@
       <c r="A15" s="27">
         <v>13</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,13),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C15" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,13),"")</f>
@@ -3893,9 +4183,9 @@
       <c r="A16" s="23">
         <v>14</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,14),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C16" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,14),"")</f>
@@ -3910,9 +4200,9 @@
       <c r="A17" s="27">
         <v>15</v>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,15),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C17" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,15),"")</f>
@@ -3927,9 +4217,9 @@
       <c r="A18" s="23">
         <v>16</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,16),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C18" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,16),"")</f>
@@ -3944,9 +4234,9 @@
       <c r="A19" s="27">
         <v>17</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,17),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C19" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,17),"")</f>
@@ -3961,9 +4251,9 @@
       <c r="A20" s="23">
         <v>18</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,18),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C20" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,18),"")</f>
@@ -3978,9 +4268,9 @@
       <c r="A21" s="27">
         <v>19</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,19),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C21" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,19),"")</f>
@@ -3995,9 +4285,9 @@
       <c r="A22" s="23">
         <v>20</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B22" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,20),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C22" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,20),"")</f>
@@ -4012,9 +4302,9 @@
       <c r="A23" s="27">
         <v>21</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,21),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C23" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,21),"")</f>
@@ -4029,9 +4319,9 @@
       <c r="A24" s="23">
         <v>22</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,22),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C24" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,22),"")</f>
@@ -4046,9 +4336,9 @@
       <c r="A25" s="27">
         <v>23</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,23),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C25" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,23),"")</f>
@@ -4063,9 +4353,9 @@
       <c r="A26" s="23">
         <v>24</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,24),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C26" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,24),"")</f>
@@ -4080,9 +4370,9 @@
       <c r="A27" s="27">
         <v>25</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,25),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C27" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,25),"")</f>
@@ -4097,9 +4387,9 @@
       <c r="A28" s="23">
         <v>26</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,26),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C28" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,26),"")</f>
@@ -4114,9 +4404,9 @@
       <c r="A29" s="27">
         <v>27</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,27),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C29" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,27),"")</f>
@@ -4131,9 +4421,9 @@
       <c r="A30" s="23">
         <v>28</v>
       </c>
-      <c r="B30" s="24">
+      <c r="B30" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,28),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C30" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,28),"")</f>
@@ -4148,9 +4438,9 @@
       <c r="A31" s="27">
         <v>29</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,29),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C31" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,29),"")</f>
@@ -4165,9 +4455,9 @@
       <c r="A32" s="23">
         <v>30</v>
       </c>
-      <c r="B32" s="24">
+      <c r="B32" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,30),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C32" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,30),"")</f>

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="302" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91E79C02-A7FB-4611-AEE7-17C7A578BD6A}"/>
+  <xr:revisionPtr revIDLastSave="309" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3EA124D-577F-4807-BD7B-F18BFDF53BC2}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="190">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -930,6 +930,7 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -937,7 +938,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1217,16 +1217,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35"/>
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1623,14 +1623,14 @@
       <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -2238,12 +2238,24 @@
       <c r="A4" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
@@ -2299,15 +2311,15 @@
       <c r="G9" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2490,7 +2502,7 @@
       </c>
       <c r="D4" s="17">
         <f>IF(C4="","",IF(UPPER(C4)=UPPER('Race Results'!B4),10,IF(UPPER(C4)=UPPER('Race Results'!C4),6,IF(UPPER(C4)=UPPER('Race Results'!D4),4,IF(UPPER(C4)=UPPER('Race Results'!E4),3,IF(UPPER(C4)=UPPER('Race Results'!F4),2,IF(UPPER(C4)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>119</v>
@@ -2522,7 +2534,7 @@
       </c>
       <c r="M4" s="18">
         <f t="shared" ref="M4:M33" si="0">IF(COUNTA(D4,F4,H4,J4,L4)=0,"",SUM(D4,F4,H4,J4,L4))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2537,7 +2549,7 @@
       </c>
       <c r="D5" s="17">
         <f>IF(C5="","",IF(UPPER(C5)=UPPER('Race Results'!B4),10,IF(UPPER(C5)=UPPER('Race Results'!C4),6,IF(UPPER(C5)=UPPER('Race Results'!D4),4,IF(UPPER(C5)=UPPER('Race Results'!E4),3,IF(UPPER(C5)=UPPER('Race Results'!F4),2,IF(UPPER(C5)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>112</v>
@@ -2569,7 +2581,7 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2584,7 +2596,7 @@
       </c>
       <c r="D6" s="17">
         <f>IF(C6="","",IF(UPPER(C6)=UPPER('Race Results'!B4),10,IF(UPPER(C6)=UPPER('Race Results'!C4),6,IF(UPPER(C6)=UPPER('Race Results'!D4),4,IF(UPPER(C6)=UPPER('Race Results'!E4),3,IF(UPPER(C6)=UPPER('Race Results'!F4),2,IF(UPPER(C6)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>114</v>
@@ -2616,7 +2628,7 @@
       </c>
       <c r="M6" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2631,7 +2643,7 @@
       </c>
       <c r="D7" s="17">
         <f>IF(C7="","",IF(UPPER(C7)=UPPER('Race Results'!B4),10,IF(UPPER(C7)=UPPER('Race Results'!C4),6,IF(UPPER(C7)=UPPER('Race Results'!D4),4,IF(UPPER(C7)=UPPER('Race Results'!E4),3,IF(UPPER(C7)=UPPER('Race Results'!F4),2,IF(UPPER(C7)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>122</v>
@@ -2663,7 +2675,7 @@
       </c>
       <c r="M7" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2678,7 +2690,7 @@
       </c>
       <c r="D8" s="17">
         <f>IF(C8="","",IF(UPPER(C8)=UPPER('Race Results'!B4),10,IF(UPPER(C8)=UPPER('Race Results'!C4),6,IF(UPPER(C8)=UPPER('Race Results'!D4),4,IF(UPPER(C8)=UPPER('Race Results'!E4),3,IF(UPPER(C8)=UPPER('Race Results'!F4),2,IF(UPPER(C8)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>119</v>
@@ -2710,7 +2722,7 @@
       </c>
       <c r="M8" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2725,7 +2737,7 @@
       </c>
       <c r="D9" s="17">
         <f>IF(C9="","",IF(UPPER(C9)=UPPER('Race Results'!B4),10,IF(UPPER(C9)=UPPER('Race Results'!C4),6,IF(UPPER(C9)=UPPER('Race Results'!D4),4,IF(UPPER(C9)=UPPER('Race Results'!E4),3,IF(UPPER(C9)=UPPER('Race Results'!F4),2,IF(UPPER(C9)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>128</v>
@@ -2757,7 +2769,7 @@
       </c>
       <c r="M9" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2772,7 +2784,7 @@
       </c>
       <c r="D10" s="17">
         <f>IF(C10="","",IF(UPPER(C10)=UPPER('Race Results'!B4),10,IF(UPPER(C10)=UPPER('Race Results'!C4),6,IF(UPPER(C10)=UPPER('Race Results'!D4),4,IF(UPPER(C10)=UPPER('Race Results'!E4),3,IF(UPPER(C10)=UPPER('Race Results'!F4),2,IF(UPPER(C10)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>112</v>
@@ -2804,7 +2816,7 @@
       </c>
       <c r="M10" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2866,7 +2878,7 @@
       </c>
       <c r="D12" s="17">
         <f>IF(C12="","",IF(UPPER(C12)=UPPER('Race Results'!B4),10,IF(UPPER(C12)=UPPER('Race Results'!C4),6,IF(UPPER(C12)=UPPER('Race Results'!D4),4,IF(UPPER(C12)=UPPER('Race Results'!E4),3,IF(UPPER(C12)=UPPER('Race Results'!F4),2,IF(UPPER(C12)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>119</v>
@@ -2898,7 +2910,7 @@
       </c>
       <c r="M12" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2913,7 +2925,7 @@
       </c>
       <c r="D13" s="17">
         <f>IF(C13="","",IF(UPPER(C13)=UPPER('Race Results'!B4),10,IF(UPPER(C13)=UPPER('Race Results'!C4),6,IF(UPPER(C13)=UPPER('Race Results'!D4),4,IF(UPPER(C13)=UPPER('Race Results'!E4),3,IF(UPPER(C13)=UPPER('Race Results'!F4),2,IF(UPPER(C13)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>114</v>
@@ -2945,7 +2957,7 @@
       </c>
       <c r="M13" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
@@ -3007,7 +3019,7 @@
       </c>
       <c r="D15" s="17">
         <f>IF(C15="","",IF(UPPER(C15)=UPPER('Race Results'!B4),10,IF(UPPER(C15)=UPPER('Race Results'!C4),6,IF(UPPER(C15)=UPPER('Race Results'!D4),4,IF(UPPER(C15)=UPPER('Race Results'!E4),3,IF(UPPER(C15)=UPPER('Race Results'!F4),2,IF(UPPER(C15)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>112</v>
@@ -3039,7 +3051,7 @@
       </c>
       <c r="M15" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3054,7 +3066,7 @@
       </c>
       <c r="D16" s="17">
         <f>IF(C16="","",IF(UPPER(C16)=UPPER('Race Results'!B4),10,IF(UPPER(C16)=UPPER('Race Results'!C4),6,IF(UPPER(C16)=UPPER('Race Results'!D4),4,IF(UPPER(C16)=UPPER('Race Results'!E4),3,IF(UPPER(C16)=UPPER('Race Results'!F4),2,IF(UPPER(C16)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>119</v>
@@ -3086,7 +3098,7 @@
       </c>
       <c r="M16" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3101,7 +3113,7 @@
       </c>
       <c r="D17" s="17">
         <f>IF(C17="","",IF(UPPER(C17)=UPPER('Race Results'!B4),10,IF(UPPER(C17)=UPPER('Race Results'!C4),6,IF(UPPER(C17)=UPPER('Race Results'!D4),4,IF(UPPER(C17)=UPPER('Race Results'!E4),3,IF(UPPER(C17)=UPPER('Race Results'!F4),2,IF(UPPER(C17)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>128</v>
@@ -3133,7 +3145,7 @@
       </c>
       <c r="M17" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3148,7 +3160,7 @@
       </c>
       <c r="D18" s="17">
         <f>IF(C18="","",IF(UPPER(C18)=UPPER('Race Results'!B4),10,IF(UPPER(C18)=UPPER('Race Results'!C4),6,IF(UPPER(C18)=UPPER('Race Results'!D4),4,IF(UPPER(C18)=UPPER('Race Results'!E4),3,IF(UPPER(C18)=UPPER('Race Results'!F4),2,IF(UPPER(C18)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>133</v>
@@ -3180,7 +3192,7 @@
       </c>
       <c r="M18" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3195,7 +3207,7 @@
       </c>
       <c r="D19" s="17">
         <f>IF(C19="","",IF(UPPER(C19)=UPPER('Race Results'!B4),10,IF(UPPER(C19)=UPPER('Race Results'!C4),6,IF(UPPER(C19)=UPPER('Race Results'!D4),4,IF(UPPER(C19)=UPPER('Race Results'!E4),3,IF(UPPER(C19)=UPPER('Race Results'!F4),2,IF(UPPER(C19)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>114</v>
@@ -3227,7 +3239,7 @@
       </c>
       <c r="M19" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3242,7 +3254,7 @@
       </c>
       <c r="D20" s="17">
         <f>IF(C20="","",IF(UPPER(C20)=UPPER('Race Results'!B4),10,IF(UPPER(C20)=UPPER('Race Results'!C4),6,IF(UPPER(C20)=UPPER('Race Results'!D4),4,IF(UPPER(C20)=UPPER('Race Results'!E4),3,IF(UPPER(C20)=UPPER('Race Results'!F4),2,IF(UPPER(C20)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>112</v>
@@ -3274,7 +3286,7 @@
       </c>
       <c r="M20" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3336,7 +3348,7 @@
       </c>
       <c r="D22" s="17">
         <f>IF(C22="","",IF(UPPER(C22)=UPPER('Race Results'!B4),10,IF(UPPER(C22)=UPPER('Race Results'!C4),6,IF(UPPER(C22)=UPPER('Race Results'!D4),4,IF(UPPER(C22)=UPPER('Race Results'!E4),3,IF(UPPER(C22)=UPPER('Race Results'!F4),2,IF(UPPER(C22)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>122</v>
@@ -3368,7 +3380,7 @@
       </c>
       <c r="M22" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3383,7 +3395,7 @@
       </c>
       <c r="D23" s="17">
         <f>IF(C23="","",IF(UPPER(C23)=UPPER('Race Results'!B4),10,IF(UPPER(C23)=UPPER('Race Results'!C4),6,IF(UPPER(C23)=UPPER('Race Results'!D4),4,IF(UPPER(C23)=UPPER('Race Results'!E4),3,IF(UPPER(C23)=UPPER('Race Results'!F4),2,IF(UPPER(C23)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>128</v>
@@ -3415,7 +3427,7 @@
       </c>
       <c r="M23" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3430,7 +3442,7 @@
       </c>
       <c r="D24" s="17">
         <f>IF(C24="","",IF(UPPER(C24)=UPPER('Race Results'!B4),10,IF(UPPER(C24)=UPPER('Race Results'!C4),6,IF(UPPER(C24)=UPPER('Race Results'!D4),4,IF(UPPER(C24)=UPPER('Race Results'!E4),3,IF(UPPER(C24)=UPPER('Race Results'!F4),2,IF(UPPER(C24)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>114</v>
@@ -3462,7 +3474,7 @@
       </c>
       <c r="M24" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3477,7 +3489,7 @@
       </c>
       <c r="D25" s="17">
         <f>IF(C25="","",IF(UPPER(C25)=UPPER('Race Results'!B4),10,IF(UPPER(C25)=UPPER('Race Results'!C4),6,IF(UPPER(C25)=UPPER('Race Results'!D4),4,IF(UPPER(C25)=UPPER('Race Results'!E4),3,IF(UPPER(C25)=UPPER('Race Results'!F4),2,IF(UPPER(C25)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>112</v>
@@ -3509,7 +3521,7 @@
       </c>
       <c r="M25" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3524,7 +3536,7 @@
       </c>
       <c r="D26" s="17">
         <f>IF(C26="","",IF(UPPER(C26)=UPPER('Race Results'!B4),10,IF(UPPER(C26)=UPPER('Race Results'!C4),6,IF(UPPER(C26)=UPPER('Race Results'!D4),4,IF(UPPER(C26)=UPPER('Race Results'!E4),3,IF(UPPER(C26)=UPPER('Race Results'!F4),2,IF(UPPER(C26)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>119</v>
@@ -3556,7 +3568,7 @@
       </c>
       <c r="M26" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
@@ -3665,7 +3677,7 @@
       </c>
       <c r="D29" s="17">
         <f>IF(C29="","",IF(UPPER(C29)=UPPER('Race Results'!B4),10,IF(UPPER(C29)=UPPER('Race Results'!C4),6,IF(UPPER(C29)=UPPER('Race Results'!D4),4,IF(UPPER(C29)=UPPER('Race Results'!E4),3,IF(UPPER(C29)=UPPER('Race Results'!F4),2,IF(UPPER(C29)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>112</v>
@@ -3697,7 +3709,7 @@
       </c>
       <c r="M29" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3712,7 +3724,7 @@
       </c>
       <c r="D30" s="17">
         <f>IF(C30="","",IF(UPPER(C30)=UPPER('Race Results'!B4),10,IF(UPPER(C30)=UPPER('Race Results'!C4),6,IF(UPPER(C30)=UPPER('Race Results'!D4),4,IF(UPPER(C30)=UPPER('Race Results'!E4),3,IF(UPPER(C30)=UPPER('Race Results'!F4),2,IF(UPPER(C30)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>122</v>
@@ -3744,7 +3756,7 @@
       </c>
       <c r="M30" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3968,11 +3980,11 @@
       </c>
       <c r="C3" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,1),"")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D3" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C3,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -3985,11 +3997,11 @@
       </c>
       <c r="C4" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),"")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D4" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C4,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4002,11 +4014,11 @@
       </c>
       <c r="C5" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,3),"")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D5" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C5,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4019,11 +4031,11 @@
       </c>
       <c r="C6" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,4),"")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D6" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C6,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4036,11 +4048,11 @@
       </c>
       <c r="C7" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,5),"")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D7" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C7,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4053,11 +4065,11 @@
       </c>
       <c r="C8" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,6),"")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D8" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C8,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4070,11 +4082,11 @@
       </c>
       <c r="C9" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,7),"")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D9" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C9,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4083,11 +4095,11 @@
       </c>
       <c r="B10" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,8),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Marianne Chardon</v>
       </c>
       <c r="C10" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,8),"")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D10" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C10,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4100,11 +4112,11 @@
       </c>
       <c r="B11" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,9),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Marianne Chardon</v>
       </c>
       <c r="C11" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,9),"")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D11" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C11,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4117,11 +4129,11 @@
       </c>
       <c r="B12" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,10),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Marianne Chardon</v>
       </c>
       <c r="C12" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,10),"")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D12" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C12,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4134,11 +4146,11 @@
       </c>
       <c r="B13" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,11),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Marianne Chardon</v>
       </c>
       <c r="C13" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,11),"")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D13" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C13,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4151,11 +4163,11 @@
       </c>
       <c r="B14" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,12),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Marianne Chardon</v>
       </c>
       <c r="C14" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,12),"")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D14" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C14,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4168,11 +4180,11 @@
       </c>
       <c r="B15" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,13),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Ronan Keohane</v>
       </c>
       <c r="C15" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,13),"")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D15" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C15,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4185,11 +4197,11 @@
       </c>
       <c r="B16" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,14),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Ronan Keohane</v>
       </c>
       <c r="C16" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,14),"")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D16" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C16,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4202,11 +4214,11 @@
       </c>
       <c r="B17" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,15),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Ronan Keohane</v>
       </c>
       <c r="C17" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,15),"")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D17" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C17,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4219,11 +4231,11 @@
       </c>
       <c r="B18" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,16),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Anthony Burke</v>
       </c>
       <c r="C18" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,16),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D18" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C18,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4236,11 +4248,11 @@
       </c>
       <c r="B19" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,17),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Anthony Burke</v>
       </c>
       <c r="C19" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,17),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D19" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C19,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4253,11 +4265,11 @@
       </c>
       <c r="B20" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,18),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Anthony Burke</v>
       </c>
       <c r="C20" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,18),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D20" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C20,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4270,11 +4282,11 @@
       </c>
       <c r="B21" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,19),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Denise White</v>
       </c>
       <c r="C21" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,19),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C21,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4287,11 +4299,11 @@
       </c>
       <c r="B22" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,20),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Denise White</v>
       </c>
       <c r="C22" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,20),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C22,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4304,11 +4316,11 @@
       </c>
       <c r="B23" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,21),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Denise White</v>
       </c>
       <c r="C23" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,21),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C23,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4321,11 +4333,11 @@
       </c>
       <c r="B24" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,22),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Liz Bugler</v>
       </c>
       <c r="C24" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,22),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C24,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4338,7 +4350,7 @@
       </c>
       <c r="B25" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,23),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Ryan Crowley</v>
       </c>
       <c r="C25" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,23),"")</f>
@@ -4355,7 +4367,7 @@
       </c>
       <c r="B26" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,24),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Ryan Crowley</v>
       </c>
       <c r="C26" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,24),"")</f>
@@ -4372,7 +4384,7 @@
       </c>
       <c r="B27" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,25),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Ryan Crowley</v>
       </c>
       <c r="C27" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,25),"")</f>
@@ -4389,7 +4401,7 @@
       </c>
       <c r="B28" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,26),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Ryan Crowley</v>
       </c>
       <c r="C28" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,26),"")</f>
@@ -4406,7 +4418,7 @@
       </c>
       <c r="B29" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,27),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Ryan Crowley</v>
       </c>
       <c r="C29" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,27),"")</f>
@@ -4423,7 +4435,7 @@
       </c>
       <c r="B30" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,28),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Ryan Crowley</v>
       </c>
       <c r="C30" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,28),"")</f>
@@ -4440,7 +4452,7 @@
       </c>
       <c r="B31" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,29),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Ryan Crowley</v>
       </c>
       <c r="C31" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,29),"")</f>
@@ -4457,7 +4469,7 @@
       </c>
       <c r="B32" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,30),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Ryan Crowley</v>
       </c>
       <c r="C32" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,30),"")</f>

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="309" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3EA124D-577F-4807-BD7B-F18BFDF53BC2}"/>
+  <xr:revisionPtr revIDLastSave="319" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFC0DEFC-8DEB-481B-AC2E-387E5DB83C1C}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest List" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="190">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -924,23 +924,23 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1217,16 +1217,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="36"/>
+      <c r="A1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="34"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37"/>
+      <c r="B2" s="35"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1613,24 +1613,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -1906,7 +1906,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <v>14</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>15</v>
       </c>
@@ -2190,26 +2190,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
     </row>
     <row r="3" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
@@ -2261,12 +2261,24 @@
       <c r="A5" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
@@ -2311,15 +2323,15 @@
       <c r="G9" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2416,38 +2428,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
     </row>
     <row r="3" spans="1:13" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -2509,7 +2521,7 @@
       </c>
       <c r="F4" s="17">
         <f>IF(E4="","",IF(UPPER(E4)=UPPER('Race Results'!B5),10,IF(UPPER(E4)=UPPER('Race Results'!C5),6,IF(UPPER(E4)=UPPER('Race Results'!D5),4,IF(UPPER(E4)=UPPER('Race Results'!E5),3,IF(UPPER(E4)=UPPER('Race Results'!F5),2,IF(UPPER(E4)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G4" s="15" t="s">
         <v>143</v>
@@ -2534,7 +2546,7 @@
       </c>
       <c r="M4" s="18">
         <f t="shared" ref="M4:M33" si="0">IF(COUNTA(D4,F4,H4,J4,L4)=0,"",SUM(D4,F4,H4,J4,L4))</f>
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2556,7 +2568,7 @@
       </c>
       <c r="F5" s="17">
         <f>IF(E5="","",IF(UPPER(E5)=UPPER('Race Results'!B5),10,IF(UPPER(E5)=UPPER('Race Results'!C5),6,IF(UPPER(E5)=UPPER('Race Results'!D5),4,IF(UPPER(E5)=UPPER('Race Results'!E5),3,IF(UPPER(E5)=UPPER('Race Results'!F5),2,IF(UPPER(E5)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>137</v>
@@ -2581,7 +2593,7 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2697,7 +2709,7 @@
       </c>
       <c r="F8" s="17">
         <f>IF(E8="","",IF(UPPER(E8)=UPPER('Race Results'!B5),10,IF(UPPER(E8)=UPPER('Race Results'!C5),6,IF(UPPER(E8)=UPPER('Race Results'!D5),4,IF(UPPER(E8)=UPPER('Race Results'!E5),3,IF(UPPER(E8)=UPPER('Race Results'!F5),2,IF(UPPER(E8)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G8" s="15" t="s">
         <v>143</v>
@@ -2722,7 +2734,7 @@
       </c>
       <c r="M8" s="18">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2791,7 +2803,7 @@
       </c>
       <c r="F10" s="17">
         <f>IF(E10="","",IF(UPPER(E10)=UPPER('Race Results'!B5),10,IF(UPPER(E10)=UPPER('Race Results'!C5),6,IF(UPPER(E10)=UPPER('Race Results'!D5),4,IF(UPPER(E10)=UPPER('Race Results'!E5),3,IF(UPPER(E10)=UPPER('Race Results'!F5),2,IF(UPPER(E10)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G10" s="15" t="s">
         <v>139</v>
@@ -2816,7 +2828,7 @@
       </c>
       <c r="M10" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2885,7 +2897,7 @@
       </c>
       <c r="F12" s="17">
         <f>IF(E12="","",IF(UPPER(E12)=UPPER('Race Results'!B5),10,IF(UPPER(E12)=UPPER('Race Results'!C5),6,IF(UPPER(E12)=UPPER('Race Results'!D5),4,IF(UPPER(E12)=UPPER('Race Results'!E5),3,IF(UPPER(E12)=UPPER('Race Results'!F5),2,IF(UPPER(E12)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G12" s="15" t="s">
         <v>134</v>
@@ -2910,7 +2922,7 @@
       </c>
       <c r="M12" s="18">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3026,7 +3038,7 @@
       </c>
       <c r="F15" s="17">
         <f>IF(E15="","",IF(UPPER(E15)=UPPER('Race Results'!B5),10,IF(UPPER(E15)=UPPER('Race Results'!C5),6,IF(UPPER(E15)=UPPER('Race Results'!D5),4,IF(UPPER(E15)=UPPER('Race Results'!E5),3,IF(UPPER(E15)=UPPER('Race Results'!F5),2,IF(UPPER(E15)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>141</v>
@@ -3051,7 +3063,7 @@
       </c>
       <c r="M15" s="18">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3073,7 +3085,7 @@
       </c>
       <c r="F16" s="17">
         <f>IF(E16="","",IF(UPPER(E16)=UPPER('Race Results'!B5),10,IF(UPPER(E16)=UPPER('Race Results'!C5),6,IF(UPPER(E16)=UPPER('Race Results'!D5),4,IF(UPPER(E16)=UPPER('Race Results'!E5),3,IF(UPPER(E16)=UPPER('Race Results'!F5),2,IF(UPPER(E16)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15" t="s">
         <v>144</v>
@@ -3098,7 +3110,7 @@
       </c>
       <c r="M16" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3261,7 +3273,7 @@
       </c>
       <c r="F20" s="17">
         <f>IF(E20="","",IF(UPPER(E20)=UPPER('Race Results'!B5),10,IF(UPPER(E20)=UPPER('Race Results'!C5),6,IF(UPPER(E20)=UPPER('Race Results'!D5),4,IF(UPPER(E20)=UPPER('Race Results'!E5),3,IF(UPPER(E20)=UPPER('Race Results'!F5),2,IF(UPPER(E20)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G20" s="15" t="s">
         <v>143</v>
@@ -3286,7 +3298,7 @@
       </c>
       <c r="M20" s="18">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3308,7 +3320,7 @@
       </c>
       <c r="F21" s="17">
         <f>IF(E21="","",IF(UPPER(E21)=UPPER('Race Results'!B5),10,IF(UPPER(E21)=UPPER('Race Results'!C5),6,IF(UPPER(E21)=UPPER('Race Results'!D5),4,IF(UPPER(E21)=UPPER('Race Results'!E5),3,IF(UPPER(E21)=UPPER('Race Results'!F5),2,IF(UPPER(E21)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>137</v>
@@ -3333,7 +3345,7 @@
       </c>
       <c r="M21" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3496,7 +3508,7 @@
       </c>
       <c r="F25" s="17">
         <f>IF(E25="","",IF(UPPER(E25)=UPPER('Race Results'!B5),10,IF(UPPER(E25)=UPPER('Race Results'!C5),6,IF(UPPER(E25)=UPPER('Race Results'!D5),4,IF(UPPER(E25)=UPPER('Race Results'!E5),3,IF(UPPER(E25)=UPPER('Race Results'!F5),2,IF(UPPER(E25)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>134</v>
@@ -3521,7 +3533,7 @@
       </c>
       <c r="M25" s="18">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3543,7 +3555,7 @@
       </c>
       <c r="F26" s="17">
         <f>IF(E26="","",IF(UPPER(E26)=UPPER('Race Results'!B5),10,IF(UPPER(E26)=UPPER('Race Results'!C5),6,IF(UPPER(E26)=UPPER('Race Results'!D5),4,IF(UPPER(E26)=UPPER('Race Results'!E5),3,IF(UPPER(E26)=UPPER('Race Results'!F5),2,IF(UPPER(E26)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G26" s="15" t="s">
         <v>137</v>
@@ -3568,7 +3580,7 @@
       </c>
       <c r="M26" s="18">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
@@ -3684,7 +3696,7 @@
       </c>
       <c r="F29" s="17">
         <f>IF(E29="","",IF(UPPER(E29)=UPPER('Race Results'!B5),10,IF(UPPER(E29)=UPPER('Race Results'!C5),6,IF(UPPER(E29)=UPPER('Race Results'!D5),4,IF(UPPER(E29)=UPPER('Race Results'!E5),3,IF(UPPER(E29)=UPPER('Race Results'!F5),2,IF(UPPER(E29)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>144</v>
@@ -3709,7 +3721,7 @@
       </c>
       <c r="M29" s="18">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3949,12 +3961,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -3976,11 +3988,11 @@
       </c>
       <c r="B3" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,1),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Emily Sardo</v>
       </c>
       <c r="C3" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,1),"")</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D3" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C3,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -3993,11 +4005,11 @@
       </c>
       <c r="B4" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Emily Sardo</v>
       </c>
       <c r="C4" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),"")</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D4" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C4,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4014,11 +4026,11 @@
       </c>
       <c r="C5" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,3),"")</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D5" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C5,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4031,11 +4043,11 @@
       </c>
       <c r="C6" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,4),"")</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D6" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C6,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4048,11 +4060,11 @@
       </c>
       <c r="C7" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,5),"")</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D7" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C7,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4065,11 +4077,11 @@
       </c>
       <c r="C8" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,6),"")</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D8" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C8,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4078,15 +4090,15 @@
       </c>
       <c r="B9" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,7),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Stephen Hughes</v>
       </c>
       <c r="C9" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,7),"")</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D9" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C9,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4095,15 +4107,15 @@
       </c>
       <c r="B10" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,8),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Marianne Chardon</v>
+        <v>Stephen Hughes</v>
       </c>
       <c r="C10" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,8),"")</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D10" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C10,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4112,11 +4124,11 @@
       </c>
       <c r="B11" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,9),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Marianne Chardon</v>
+        <v>David Hughes</v>
       </c>
       <c r="C11" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,9),"")</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D11" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C11,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4129,15 +4141,15 @@
       </c>
       <c r="B12" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,10),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Marianne Chardon</v>
+        <v>Sean Horan</v>
       </c>
       <c r="C12" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,10),"")</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D12" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C12,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4146,15 +4158,15 @@
       </c>
       <c r="B13" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,11),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Marianne Chardon</v>
+        <v>Sean Horan</v>
       </c>
       <c r="C13" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,11),"")</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D13" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C13,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4163,15 +4175,15 @@
       </c>
       <c r="B14" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,12),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Marianne Chardon</v>
+        <v>Sean Horan</v>
       </c>
       <c r="C14" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,12),"")</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D14" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C14,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4180,11 +4192,11 @@
       </c>
       <c r="B15" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,13),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ronan Keohane</v>
+        <v>Anthony Burke</v>
       </c>
       <c r="C15" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,13),"")</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D15" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C15,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4197,11 +4209,11 @@
       </c>
       <c r="B16" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,14),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ronan Keohane</v>
+        <v>Liam Bridgeman</v>
       </c>
       <c r="C16" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,14),"")</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D16" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C16,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4214,11 +4226,11 @@
       </c>
       <c r="B17" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,15),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ronan Keohane</v>
+        <v>Darren Gill</v>
       </c>
       <c r="C17" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,15),"")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C17,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4231,11 +4243,11 @@
       </c>
       <c r="B18" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,16),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Anthony Burke</v>
+        <v>Darren Gill</v>
       </c>
       <c r="C18" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,16),"")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D18" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C18,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4248,11 +4260,11 @@
       </c>
       <c r="B19" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,17),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Anthony Burke</v>
+        <v>Darren Gill</v>
       </c>
       <c r="C19" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,17),"")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D19" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C19,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4265,11 +4277,11 @@
       </c>
       <c r="B20" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,18),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Anthony Burke</v>
+        <v>Ronan Keohane</v>
       </c>
       <c r="C20" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,18),"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C20,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4282,11 +4294,11 @@
       </c>
       <c r="B21" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,19),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Denise White</v>
+        <v>Ronan Keohane</v>
       </c>
       <c r="C21" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,19),"")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C21,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4299,11 +4311,11 @@
       </c>
       <c r="B22" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,20),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Denise White</v>
+        <v>Ronan Keohane</v>
       </c>
       <c r="C22" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,20),"")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C22,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4333,11 +4345,11 @@
       </c>
       <c r="B24" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,22),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Denise White</v>
       </c>
       <c r="C24" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,22),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C24,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4350,11 +4362,11 @@
       </c>
       <c r="B25" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,23),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ryan Crowley</v>
+        <v>Liz Bugler</v>
       </c>
       <c r="C25" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,23),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C25,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4501,14 +4513,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="3" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A3" s="40" t="s">

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="319" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFC0DEFC-8DEB-481B-AC2E-387E5DB83C1C}"/>
+  <xr:revisionPtr revIDLastSave="327" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{199CACA1-DBB5-45A8-8B96-4F015C0848B0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest List" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="190">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -924,23 +924,23 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1204,6 +1204,28 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="2">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{6967CB7C-1FFA-404F-AB60-D09A002544AE}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;0ea980b1-2da0-4ef4-84a6-2e30376f1cf5&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
@@ -1217,16 +1239,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="34"/>
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35"/>
+      <c r="B2" s="36"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1613,14 +1635,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="37" t="s">
@@ -2190,26 +2212,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
     </row>
     <row r="3" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
@@ -2284,12 +2306,24 @@
       <c r="A6" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
+      <c r="B6" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
@@ -2323,15 +2357,15 @@
       <c r="G9" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2428,38 +2462,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
     </row>
     <row r="3" spans="1:13" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -2528,7 +2562,7 @@
       </c>
       <c r="H4" s="17">
         <f>IF(G4="","",IF(UPPER(G4)=UPPER('Race Results'!B6),10,IF(UPPER(G4)=UPPER('Race Results'!C6),6,IF(UPPER(G4)=UPPER('Race Results'!D6),4,IF(UPPER(G4)=UPPER('Race Results'!E6),3,IF(UPPER(G4)=UPPER('Race Results'!F6),2,IF(UPPER(G4)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I4" s="15" t="s">
         <v>150</v>
@@ -2546,7 +2580,7 @@
       </c>
       <c r="M4" s="18">
         <f t="shared" ref="M4:M33" si="0">IF(COUNTA(D4,F4,H4,J4,L4)=0,"",SUM(D4,F4,H4,J4,L4))</f>
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2575,7 +2609,7 @@
       </c>
       <c r="H5" s="17">
         <f>IF(G5="","",IF(UPPER(G5)=UPPER('Race Results'!B6),10,IF(UPPER(G5)=UPPER('Race Results'!C6),6,IF(UPPER(G5)=UPPER('Race Results'!D6),4,IF(UPPER(G5)=UPPER('Race Results'!E6),3,IF(UPPER(G5)=UPPER('Race Results'!F6),2,IF(UPPER(G5)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>151</v>
@@ -2593,7 +2627,7 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2622,7 +2656,7 @@
       </c>
       <c r="H6" s="17">
         <f>IF(G6="","",IF(UPPER(G6)=UPPER('Race Results'!B6),10,IF(UPPER(G6)=UPPER('Race Results'!C6),6,IF(UPPER(G6)=UPPER('Race Results'!D6),4,IF(UPPER(G6)=UPPER('Race Results'!E6),3,IF(UPPER(G6)=UPPER('Race Results'!F6),2,IF(UPPER(G6)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>147</v>
@@ -2640,7 +2674,7 @@
       </c>
       <c r="M6" s="18">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2669,7 +2703,7 @@
       </c>
       <c r="H7" s="17">
         <f>IF(G7="","",IF(UPPER(G7)=UPPER('Race Results'!B6),10,IF(UPPER(G7)=UPPER('Race Results'!C6),6,IF(UPPER(G7)=UPPER('Race Results'!D6),4,IF(UPPER(G7)=UPPER('Race Results'!E6),3,IF(UPPER(G7)=UPPER('Race Results'!F6),2,IF(UPPER(G7)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>150</v>
@@ -2687,7 +2721,7 @@
       </c>
       <c r="M7" s="18">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2716,7 +2750,7 @@
       </c>
       <c r="H8" s="17">
         <f>IF(G8="","",IF(UPPER(G8)=UPPER('Race Results'!B6),10,IF(UPPER(G8)=UPPER('Race Results'!C6),6,IF(UPPER(G8)=UPPER('Race Results'!D6),4,IF(UPPER(G8)=UPPER('Race Results'!E6),3,IF(UPPER(G8)=UPPER('Race Results'!F6),2,IF(UPPER(G8)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>155</v>
@@ -2734,7 +2768,7 @@
       </c>
       <c r="M8" s="18">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2763,7 +2797,7 @@
       </c>
       <c r="H9" s="17">
         <f>IF(G9="","",IF(UPPER(G9)=UPPER('Race Results'!B6),10,IF(UPPER(G9)=UPPER('Race Results'!C6),6,IF(UPPER(G9)=UPPER('Race Results'!D6),4,IF(UPPER(G9)=UPPER('Race Results'!E6),3,IF(UPPER(G9)=UPPER('Race Results'!F6),2,IF(UPPER(G9)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>148</v>
@@ -2781,7 +2815,7 @@
       </c>
       <c r="M9" s="18">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2810,7 +2844,7 @@
       </c>
       <c r="H10" s="17">
         <f>IF(G10="","",IF(UPPER(G10)=UPPER('Race Results'!B6),10,IF(UPPER(G10)=UPPER('Race Results'!C6),6,IF(UPPER(G10)=UPPER('Race Results'!D6),4,IF(UPPER(G10)=UPPER('Race Results'!E6),3,IF(UPPER(G10)=UPPER('Race Results'!F6),2,IF(UPPER(G10)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>153</v>
@@ -2828,7 +2862,7 @@
       </c>
       <c r="M10" s="18">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2857,7 +2891,7 @@
       </c>
       <c r="H11" s="17">
         <f>IF(G11="","",IF(UPPER(G11)=UPPER('Race Results'!B6),10,IF(UPPER(G11)=UPPER('Race Results'!C6),6,IF(UPPER(G11)=UPPER('Race Results'!D6),4,IF(UPPER(G11)=UPPER('Race Results'!E6),3,IF(UPPER(G11)=UPPER('Race Results'!F6),2,IF(UPPER(G11)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>150</v>
@@ -2875,7 +2909,7 @@
       </c>
       <c r="M11" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2904,7 +2938,7 @@
       </c>
       <c r="H12" s="17">
         <f>IF(G12="","",IF(UPPER(G12)=UPPER('Race Results'!B6),10,IF(UPPER(G12)=UPPER('Race Results'!C6),6,IF(UPPER(G12)=UPPER('Race Results'!D6),4,IF(UPPER(G12)=UPPER('Race Results'!E6),3,IF(UPPER(G12)=UPPER('Race Results'!F6),2,IF(UPPER(G12)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>146</v>
@@ -2922,7 +2956,7 @@
       </c>
       <c r="M12" s="18">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2951,7 +2985,7 @@
       </c>
       <c r="H13" s="17">
         <f>IF(G13="","",IF(UPPER(G13)=UPPER('Race Results'!B6),10,IF(UPPER(G13)=UPPER('Race Results'!C6),6,IF(UPPER(G13)=UPPER('Race Results'!D6),4,IF(UPPER(G13)=UPPER('Race Results'!E6),3,IF(UPPER(G13)=UPPER('Race Results'!F6),2,IF(UPPER(G13)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>151</v>
@@ -2969,7 +3003,7 @@
       </c>
       <c r="M13" s="18">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
@@ -2998,7 +3032,7 @@
       </c>
       <c r="H14" s="17">
         <f>IF(G14="","",IF(UPPER(G14)=UPPER('Race Results'!B6),10,IF(UPPER(G14)=UPPER('Race Results'!C6),6,IF(UPPER(G14)=UPPER('Race Results'!D6),4,IF(UPPER(G14)=UPPER('Race Results'!E6),3,IF(UPPER(G14)=UPPER('Race Results'!F6),2,IF(UPPER(G14)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>150</v>
@@ -3016,7 +3050,7 @@
       </c>
       <c r="M14" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3045,7 +3079,7 @@
       </c>
       <c r="H15" s="17">
         <f>IF(G15="","",IF(UPPER(G15)=UPPER('Race Results'!B6),10,IF(UPPER(G15)=UPPER('Race Results'!C6),6,IF(UPPER(G15)=UPPER('Race Results'!D6),4,IF(UPPER(G15)=UPPER('Race Results'!E6),3,IF(UPPER(G15)=UPPER('Race Results'!F6),2,IF(UPPER(G15)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>155</v>
@@ -3063,7 +3097,7 @@
       </c>
       <c r="M15" s="18">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3092,7 +3126,7 @@
       </c>
       <c r="H16" s="17">
         <f>IF(G16="","",IF(UPPER(G16)=UPPER('Race Results'!B6),10,IF(UPPER(G16)=UPPER('Race Results'!C6),6,IF(UPPER(G16)=UPPER('Race Results'!D6),4,IF(UPPER(G16)=UPPER('Race Results'!E6),3,IF(UPPER(G16)=UPPER('Race Results'!F6),2,IF(UPPER(G16)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>148</v>
@@ -3110,7 +3144,7 @@
       </c>
       <c r="M16" s="18">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3139,7 +3173,7 @@
       </c>
       <c r="H17" s="17">
         <f>IF(G17="","",IF(UPPER(G17)=UPPER('Race Results'!B6),10,IF(UPPER(G17)=UPPER('Race Results'!C6),6,IF(UPPER(G17)=UPPER('Race Results'!D6),4,IF(UPPER(G17)=UPPER('Race Results'!E6),3,IF(UPPER(G17)=UPPER('Race Results'!F6),2,IF(UPPER(G17)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>153</v>
@@ -3157,7 +3191,7 @@
       </c>
       <c r="M17" s="18">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3186,7 +3220,7 @@
       </c>
       <c r="H18" s="17">
         <f>IF(G18="","",IF(UPPER(G18)=UPPER('Race Results'!B6),10,IF(UPPER(G18)=UPPER('Race Results'!C6),6,IF(UPPER(G18)=UPPER('Race Results'!D6),4,IF(UPPER(G18)=UPPER('Race Results'!E6),3,IF(UPPER(G18)=UPPER('Race Results'!F6),2,IF(UPPER(G18)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>150</v>
@@ -3204,7 +3238,7 @@
       </c>
       <c r="M18" s="18">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3233,7 +3267,7 @@
       </c>
       <c r="H19" s="17">
         <f>IF(G19="","",IF(UPPER(G19)=UPPER('Race Results'!B6),10,IF(UPPER(G19)=UPPER('Race Results'!C6),6,IF(UPPER(G19)=UPPER('Race Results'!D6),4,IF(UPPER(G19)=UPPER('Race Results'!E6),3,IF(UPPER(G19)=UPPER('Race Results'!F6),2,IF(UPPER(G19)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>147</v>
@@ -3251,7 +3285,7 @@
       </c>
       <c r="M19" s="18">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3280,7 +3314,7 @@
       </c>
       <c r="H20" s="17">
         <f>IF(G20="","",IF(UPPER(G20)=UPPER('Race Results'!B6),10,IF(UPPER(G20)=UPPER('Race Results'!C6),6,IF(UPPER(G20)=UPPER('Race Results'!D6),4,IF(UPPER(G20)=UPPER('Race Results'!E6),3,IF(UPPER(G20)=UPPER('Race Results'!F6),2,IF(UPPER(G20)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>150</v>
@@ -3298,7 +3332,7 @@
       </c>
       <c r="M20" s="18">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3327,7 +3361,7 @@
       </c>
       <c r="H21" s="17">
         <f>IF(G21="","",IF(UPPER(G21)=UPPER('Race Results'!B6),10,IF(UPPER(G21)=UPPER('Race Results'!C6),6,IF(UPPER(G21)=UPPER('Race Results'!D6),4,IF(UPPER(G21)=UPPER('Race Results'!E6),3,IF(UPPER(G21)=UPPER('Race Results'!F6),2,IF(UPPER(G21)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>151</v>
@@ -3345,7 +3379,7 @@
       </c>
       <c r="M21" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3374,7 +3408,7 @@
       </c>
       <c r="H22" s="17">
         <f>IF(G22="","",IF(UPPER(G22)=UPPER('Race Results'!B6),10,IF(UPPER(G22)=UPPER('Race Results'!C6),6,IF(UPPER(G22)=UPPER('Race Results'!D6),4,IF(UPPER(G22)=UPPER('Race Results'!E6),3,IF(UPPER(G22)=UPPER('Race Results'!F6),2,IF(UPPER(G22)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>155</v>
@@ -3392,7 +3426,7 @@
       </c>
       <c r="M22" s="18">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3421,7 +3455,7 @@
       </c>
       <c r="H23" s="17">
         <f>IF(G23="","",IF(UPPER(G23)=UPPER('Race Results'!B6),10,IF(UPPER(G23)=UPPER('Race Results'!C6),6,IF(UPPER(G23)=UPPER('Race Results'!D6),4,IF(UPPER(G23)=UPPER('Race Results'!E6),3,IF(UPPER(G23)=UPPER('Race Results'!F6),2,IF(UPPER(G23)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>148</v>
@@ -3439,7 +3473,7 @@
       </c>
       <c r="M23" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3468,7 +3502,7 @@
       </c>
       <c r="H24" s="17">
         <f>IF(G24="","",IF(UPPER(G24)=UPPER('Race Results'!B6),10,IF(UPPER(G24)=UPPER('Race Results'!C6),6,IF(UPPER(G24)=UPPER('Race Results'!D6),4,IF(UPPER(G24)=UPPER('Race Results'!E6),3,IF(UPPER(G24)=UPPER('Race Results'!F6),2,IF(UPPER(G24)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>147</v>
@@ -3486,7 +3520,7 @@
       </c>
       <c r="M24" s="18">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3515,7 +3549,7 @@
       </c>
       <c r="H25" s="17">
         <f>IF(G25="","",IF(UPPER(G25)=UPPER('Race Results'!B6),10,IF(UPPER(G25)=UPPER('Race Results'!C6),6,IF(UPPER(G25)=UPPER('Race Results'!D6),4,IF(UPPER(G25)=UPPER('Race Results'!E6),3,IF(UPPER(G25)=UPPER('Race Results'!F6),2,IF(UPPER(G25)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>150</v>
@@ -3533,7 +3567,7 @@
       </c>
       <c r="M25" s="18">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3562,7 +3596,7 @@
       </c>
       <c r="H26" s="17">
         <f>IF(G26="","",IF(UPPER(G26)=UPPER('Race Results'!B6),10,IF(UPPER(G26)=UPPER('Race Results'!C6),6,IF(UPPER(G26)=UPPER('Race Results'!D6),4,IF(UPPER(G26)=UPPER('Race Results'!E6),3,IF(UPPER(G26)=UPPER('Race Results'!F6),2,IF(UPPER(G26)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>153</v>
@@ -3580,7 +3614,7 @@
       </c>
       <c r="M26" s="18">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
@@ -3609,7 +3643,7 @@
       </c>
       <c r="H27" s="17">
         <f>IF(G27="","",IF(UPPER(G27)=UPPER('Race Results'!B6),10,IF(UPPER(G27)=UPPER('Race Results'!C6),6,IF(UPPER(G27)=UPPER('Race Results'!D6),4,IF(UPPER(G27)=UPPER('Race Results'!E6),3,IF(UPPER(G27)=UPPER('Race Results'!F6),2,IF(UPPER(G27)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>151</v>
@@ -3627,7 +3661,7 @@
       </c>
       <c r="M27" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3656,7 +3690,7 @@
       </c>
       <c r="H28" s="17">
         <f>IF(G28="","",IF(UPPER(G28)=UPPER('Race Results'!B6),10,IF(UPPER(G28)=UPPER('Race Results'!C6),6,IF(UPPER(G28)=UPPER('Race Results'!D6),4,IF(UPPER(G28)=UPPER('Race Results'!E6),3,IF(UPPER(G28)=UPPER('Race Results'!F6),2,IF(UPPER(G28)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>150</v>
@@ -3674,7 +3708,7 @@
       </c>
       <c r="M28" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3703,7 +3737,7 @@
       </c>
       <c r="H29" s="17">
         <f>IF(G29="","",IF(UPPER(G29)=UPPER('Race Results'!B6),10,IF(UPPER(G29)=UPPER('Race Results'!C6),6,IF(UPPER(G29)=UPPER('Race Results'!D6),4,IF(UPPER(G29)=UPPER('Race Results'!E6),3,IF(UPPER(G29)=UPPER('Race Results'!F6),2,IF(UPPER(G29)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>146</v>
@@ -3721,7 +3755,7 @@
       </c>
       <c r="M29" s="18">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3750,7 +3784,7 @@
       </c>
       <c r="H30" s="17">
         <f>IF(G30="","",IF(UPPER(G30)=UPPER('Race Results'!B6),10,IF(UPPER(G30)=UPPER('Race Results'!C6),6,IF(UPPER(G30)=UPPER('Race Results'!D6),4,IF(UPPER(G30)=UPPER('Race Results'!E6),3,IF(UPPER(G30)=UPPER('Race Results'!F6),2,IF(UPPER(G30)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>155</v>
@@ -3768,7 +3802,7 @@
       </c>
       <c r="M30" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3961,12 +3995,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -3992,11 +4026,11 @@
       </c>
       <c r="C3" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,1),"")</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D3" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C3,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4005,11 +4039,11 @@
       </c>
       <c r="B4" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Emily Sardo</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C4" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),"")</f>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D4" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C4,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4022,11 +4056,11 @@
       </c>
       <c r="B5" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,3),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Marianne Chardon</v>
       </c>
       <c r="C5" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,3),"")</f>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D5" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C5,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4039,11 +4073,11 @@
       </c>
       <c r="B6" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,4),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Marianne Chardon</v>
       </c>
       <c r="C6" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,4),"")</f>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D6" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C6,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4056,11 +4090,11 @@
       </c>
       <c r="B7" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,5),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Vahi Crowley</v>
       </c>
       <c r="C7" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,5),"")</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D7" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C7,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4073,11 +4107,11 @@
       </c>
       <c r="B8" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,6),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Vahi Crowley</v>
       </c>
       <c r="C8" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,6),"")</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D8" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C8,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4090,11 +4124,11 @@
       </c>
       <c r="B9" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,7),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Stephen Hughes</v>
+        <v>Vahi Crowley</v>
       </c>
       <c r="C9" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,7),"")</f>
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D9" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C9,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4107,11 +4141,11 @@
       </c>
       <c r="B10" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,8),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Stephen Hughes</v>
+        <v>Anthony Burke</v>
       </c>
       <c r="C10" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,8),"")</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D10" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C10,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4124,15 +4158,15 @@
       </c>
       <c r="B11" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,9),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>David Hughes</v>
+        <v>Bryan White</v>
       </c>
       <c r="C11" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,9),"")</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D11" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C11,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4141,15 +4175,15 @@
       </c>
       <c r="B12" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,10),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Sean Horan</v>
+        <v>Bryan White</v>
       </c>
       <c r="C12" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,10),"")</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D12" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C12,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4158,15 +4192,15 @@
       </c>
       <c r="B13" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,11),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Sean Horan</v>
+        <v>Stephen Hughes</v>
       </c>
       <c r="C13" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,11),"")</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D13" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C13,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4175,15 +4209,15 @@
       </c>
       <c r="B14" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,12),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Sean Horan</v>
+        <v>David Owens</v>
       </c>
       <c r="C14" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,12),"")</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D14" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C14,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4192,15 +4226,15 @@
       </c>
       <c r="B15" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,13),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Anthony Burke</v>
+        <v>David Owens</v>
       </c>
       <c r="C15" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,13),"")</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D15" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C15,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4209,15 +4243,15 @@
       </c>
       <c r="B16" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,14),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Liam Bridgeman</v>
+        <v>David Owens</v>
       </c>
       <c r="C16" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,14),"")</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D16" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C16,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4226,15 +4260,15 @@
       </c>
       <c r="B17" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,15),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Darren Gill</v>
+        <v>Sean Horan</v>
       </c>
       <c r="C17" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,15),"")</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D17" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C17,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4247,7 +4281,7 @@
       </c>
       <c r="C18" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,16),"")</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D18" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C18,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4260,15 +4294,15 @@
       </c>
       <c r="B19" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,17),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Darren Gill</v>
+        <v>Jack Webb</v>
       </c>
       <c r="C19" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,17),"")</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D19" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C19,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4281,7 +4315,7 @@
       </c>
       <c r="C20" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,18),"")</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D20" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C20,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4298,7 +4332,7 @@
       </c>
       <c r="C21" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,19),"")</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D21" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C21,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4311,11 +4345,11 @@
       </c>
       <c r="B22" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,20),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ronan Keohane</v>
+        <v>Lynn Forsyth</v>
       </c>
       <c r="C22" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,20),"")</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D22" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C22,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4328,11 +4362,11 @@
       </c>
       <c r="B23" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,21),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Denise White</v>
+        <v>Lynn Forsyth</v>
       </c>
       <c r="C23" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,21),"")</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D23" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C23,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4345,11 +4379,11 @@
       </c>
       <c r="B24" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,22),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Denise White</v>
+        <v>Ryan Crowley</v>
       </c>
       <c r="C24" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,22),"")</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D24" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C24,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4362,11 +4396,11 @@
       </c>
       <c r="B25" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,23),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Ryan Crowley</v>
       </c>
       <c r="C25" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,23),"")</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D25" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C25,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4383,7 +4417,7 @@
       </c>
       <c r="C26" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,24),"")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D26" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C26,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4396,11 +4430,11 @@
       </c>
       <c r="B27" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,25),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ryan Crowley</v>
+        <v>Denise White</v>
       </c>
       <c r="C27" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,25),"")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D27" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C27,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4413,11 +4447,11 @@
       </c>
       <c r="B28" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,26),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ryan Crowley</v>
+        <v>Steve Hunt</v>
       </c>
       <c r="C28" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,26),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D28" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C28,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4430,11 +4464,11 @@
       </c>
       <c r="B29" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,27),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ryan Crowley</v>
+        <v>Liz Bugler</v>
       </c>
       <c r="C29" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,27),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C29,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4445,9 +4479,9 @@
       <c r="A30" s="23">
         <v>28</v>
       </c>
-      <c r="B30" s="24" t="str">
+      <c r="B30" s="24">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,28),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ryan Crowley</v>
+        <v>0</v>
       </c>
       <c r="C30" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,28),"")</f>
@@ -4462,9 +4496,9 @@
       <c r="A31" s="27">
         <v>29</v>
       </c>
-      <c r="B31" s="28" t="str">
+      <c r="B31" s="28">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,29),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ryan Crowley</v>
+        <v>0</v>
       </c>
       <c r="C31" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,29),"")</f>
@@ -4479,9 +4513,9 @@
       <c r="A32" s="23">
         <v>30</v>
       </c>
-      <c r="B32" s="24" t="str">
+      <c r="B32" s="24">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,30),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ryan Crowley</v>
+        <v>0</v>
       </c>
       <c r="C32" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,30),"")</f>
@@ -4513,14 +4547,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="3" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A3" s="40" t="s">

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="327" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{199CACA1-DBB5-45A8-8B96-4F015C0848B0}"/>
+  <xr:revisionPtr revIDLastSave="333" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD0D3C16-F6A3-4039-9D54-FD42E9FF78D1}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest List" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="190">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -2329,12 +2329,24 @@
       <c r="A7" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
+      <c r="B7" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
@@ -2569,7 +2581,7 @@
       </c>
       <c r="J4" s="17">
         <f>IF(I4="","",IF(UPPER(I4)=UPPER('Race Results'!B7),10,IF(UPPER(I4)=UPPER('Race Results'!C7),6,IF(UPPER(I4)=UPPER('Race Results'!D7),4,IF(UPPER(I4)=UPPER('Race Results'!E7),3,IF(UPPER(I4)=UPPER('Race Results'!F7),2,IF(UPPER(I4)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>183</v>
@@ -2580,7 +2592,7 @@
       </c>
       <c r="M4" s="18">
         <f t="shared" ref="M4:M33" si="0">IF(COUNTA(D4,F4,H4,J4,L4)=0,"",SUM(D4,F4,H4,J4,L4))</f>
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2616,7 +2628,7 @@
       </c>
       <c r="J5" s="17">
         <f>IF(I5="","",IF(UPPER(I5)=UPPER('Race Results'!B7),10,IF(UPPER(I5)=UPPER('Race Results'!C7),6,IF(UPPER(I5)=UPPER('Race Results'!D7),4,IF(UPPER(I5)=UPPER('Race Results'!E7),3,IF(UPPER(I5)=UPPER('Race Results'!F7),2,IF(UPPER(I5)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>170</v>
@@ -2627,7 +2639,7 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2663,7 +2675,7 @@
       </c>
       <c r="J6" s="17">
         <f>IF(I6="","",IF(UPPER(I6)=UPPER('Race Results'!B7),10,IF(UPPER(I6)=UPPER('Race Results'!C7),6,IF(UPPER(I6)=UPPER('Race Results'!D7),4,IF(UPPER(I6)=UPPER('Race Results'!E7),3,IF(UPPER(I6)=UPPER('Race Results'!F7),2,IF(UPPER(I6)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K6" s="15" t="s">
         <v>171</v>
@@ -2674,7 +2686,7 @@
       </c>
       <c r="M6" s="18">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2710,7 +2722,7 @@
       </c>
       <c r="J7" s="17">
         <f>IF(I7="","",IF(UPPER(I7)=UPPER('Race Results'!B7),10,IF(UPPER(I7)=UPPER('Race Results'!C7),6,IF(UPPER(I7)=UPPER('Race Results'!D7),4,IF(UPPER(I7)=UPPER('Race Results'!E7),3,IF(UPPER(I7)=UPPER('Race Results'!F7),2,IF(UPPER(I7)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>180</v>
@@ -2721,7 +2733,7 @@
       </c>
       <c r="M7" s="18">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2757,7 +2769,7 @@
       </c>
       <c r="J8" s="17">
         <f>IF(I8="","",IF(UPPER(I8)=UPPER('Race Results'!B7),10,IF(UPPER(I8)=UPPER('Race Results'!C7),6,IF(UPPER(I8)=UPPER('Race Results'!D7),4,IF(UPPER(I8)=UPPER('Race Results'!E7),3,IF(UPPER(I8)=UPPER('Race Results'!F7),2,IF(UPPER(I8)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" s="15" t="s">
         <v>158</v>
@@ -2768,7 +2780,7 @@
       </c>
       <c r="M8" s="18">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2804,7 +2816,7 @@
       </c>
       <c r="J9" s="17">
         <f>IF(I9="","",IF(UPPER(I9)=UPPER('Race Results'!B7),10,IF(UPPER(I9)=UPPER('Race Results'!C7),6,IF(UPPER(I9)=UPPER('Race Results'!D7),4,IF(UPPER(I9)=UPPER('Race Results'!E7),3,IF(UPPER(I9)=UPPER('Race Results'!F7),2,IF(UPPER(I9)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>164</v>
@@ -2815,7 +2827,7 @@
       </c>
       <c r="M9" s="18">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2851,7 +2863,7 @@
       </c>
       <c r="J10" s="17">
         <f>IF(I10="","",IF(UPPER(I10)=UPPER('Race Results'!B7),10,IF(UPPER(I10)=UPPER('Race Results'!C7),6,IF(UPPER(I10)=UPPER('Race Results'!D7),4,IF(UPPER(I10)=UPPER('Race Results'!E7),3,IF(UPPER(I10)=UPPER('Race Results'!F7),2,IF(UPPER(I10)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>183</v>
@@ -2862,7 +2874,7 @@
       </c>
       <c r="M10" s="18">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2898,7 +2910,7 @@
       </c>
       <c r="J11" s="17">
         <f>IF(I11="","",IF(UPPER(I11)=UPPER('Race Results'!B7),10,IF(UPPER(I11)=UPPER('Race Results'!C7),6,IF(UPPER(I11)=UPPER('Race Results'!D7),4,IF(UPPER(I11)=UPPER('Race Results'!E7),3,IF(UPPER(I11)=UPPER('Race Results'!F7),2,IF(UPPER(I11)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>170</v>
@@ -2909,7 +2921,7 @@
       </c>
       <c r="M11" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2992,7 +3004,7 @@
       </c>
       <c r="J13" s="17">
         <f>IF(I13="","",IF(UPPER(I13)=UPPER('Race Results'!B7),10,IF(UPPER(I13)=UPPER('Race Results'!C7),6,IF(UPPER(I13)=UPPER('Race Results'!D7),4,IF(UPPER(I13)=UPPER('Race Results'!E7),3,IF(UPPER(I13)=UPPER('Race Results'!F7),2,IF(UPPER(I13)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>189</v>
@@ -3003,7 +3015,7 @@
       </c>
       <c r="M13" s="18">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
@@ -3039,7 +3051,7 @@
       </c>
       <c r="J14" s="17">
         <f>IF(I14="","",IF(UPPER(I14)=UPPER('Race Results'!B7),10,IF(UPPER(I14)=UPPER('Race Results'!C7),6,IF(UPPER(I14)=UPPER('Race Results'!D7),4,IF(UPPER(I14)=UPPER('Race Results'!E7),3,IF(UPPER(I14)=UPPER('Race Results'!F7),2,IF(UPPER(I14)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K14" s="15" t="s">
         <v>183</v>
@@ -3050,7 +3062,7 @@
       </c>
       <c r="M14" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3086,7 +3098,7 @@
       </c>
       <c r="J15" s="17">
         <f>IF(I15="","",IF(UPPER(I15)=UPPER('Race Results'!B7),10,IF(UPPER(I15)=UPPER('Race Results'!C7),6,IF(UPPER(I15)=UPPER('Race Results'!D7),4,IF(UPPER(I15)=UPPER('Race Results'!E7),3,IF(UPPER(I15)=UPPER('Race Results'!F7),2,IF(UPPER(I15)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>180</v>
@@ -3097,7 +3109,7 @@
       </c>
       <c r="M15" s="18">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3133,7 +3145,7 @@
       </c>
       <c r="J16" s="17">
         <f>IF(I16="","",IF(UPPER(I16)=UPPER('Race Results'!B7),10,IF(UPPER(I16)=UPPER('Race Results'!C7),6,IF(UPPER(I16)=UPPER('Race Results'!D7),4,IF(UPPER(I16)=UPPER('Race Results'!E7),3,IF(UPPER(I16)=UPPER('Race Results'!F7),2,IF(UPPER(I16)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>170</v>
@@ -3144,7 +3156,7 @@
       </c>
       <c r="M16" s="18">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3180,7 +3192,7 @@
       </c>
       <c r="J17" s="17">
         <f>IF(I17="","",IF(UPPER(I17)=UPPER('Race Results'!B7),10,IF(UPPER(I17)=UPPER('Race Results'!C7),6,IF(UPPER(I17)=UPPER('Race Results'!D7),4,IF(UPPER(I17)=UPPER('Race Results'!E7),3,IF(UPPER(I17)=UPPER('Race Results'!F7),2,IF(UPPER(I17)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>158</v>
@@ -3191,7 +3203,7 @@
       </c>
       <c r="M17" s="18">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3227,7 +3239,7 @@
       </c>
       <c r="J18" s="17">
         <f>IF(I18="","",IF(UPPER(I18)=UPPER('Race Results'!B7),10,IF(UPPER(I18)=UPPER('Race Results'!C7),6,IF(UPPER(I18)=UPPER('Race Results'!D7),4,IF(UPPER(I18)=UPPER('Race Results'!E7),3,IF(UPPER(I18)=UPPER('Race Results'!F7),2,IF(UPPER(I18)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>171</v>
@@ -3238,7 +3250,7 @@
       </c>
       <c r="M18" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3274,7 +3286,7 @@
       </c>
       <c r="J19" s="17">
         <f>IF(I19="","",IF(UPPER(I19)=UPPER('Race Results'!B7),10,IF(UPPER(I19)=UPPER('Race Results'!C7),6,IF(UPPER(I19)=UPPER('Race Results'!D7),4,IF(UPPER(I19)=UPPER('Race Results'!E7),3,IF(UPPER(I19)=UPPER('Race Results'!F7),2,IF(UPPER(I19)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>164</v>
@@ -3285,7 +3297,7 @@
       </c>
       <c r="M19" s="18">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3321,7 +3333,7 @@
       </c>
       <c r="J20" s="17">
         <f>IF(I20="","",IF(UPPER(I20)=UPPER('Race Results'!B7),10,IF(UPPER(I20)=UPPER('Race Results'!C7),6,IF(UPPER(I20)=UPPER('Race Results'!D7),4,IF(UPPER(I20)=UPPER('Race Results'!E7),3,IF(UPPER(I20)=UPPER('Race Results'!F7),2,IF(UPPER(I20)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K20" s="15" t="s">
         <v>183</v>
@@ -3332,7 +3344,7 @@
       </c>
       <c r="M20" s="18">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3368,7 +3380,7 @@
       </c>
       <c r="J21" s="17">
         <f>IF(I21="","",IF(UPPER(I21)=UPPER('Race Results'!B7),10,IF(UPPER(I21)=UPPER('Race Results'!C7),6,IF(UPPER(I21)=UPPER('Race Results'!D7),4,IF(UPPER(I21)=UPPER('Race Results'!E7),3,IF(UPPER(I21)=UPPER('Race Results'!F7),2,IF(UPPER(I21)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>157</v>
@@ -3379,7 +3391,7 @@
       </c>
       <c r="M21" s="18">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3415,7 +3427,7 @@
       </c>
       <c r="J22" s="17">
         <f>IF(I22="","",IF(UPPER(I22)=UPPER('Race Results'!B7),10,IF(UPPER(I22)=UPPER('Race Results'!C7),6,IF(UPPER(I22)=UPPER('Race Results'!D7),4,IF(UPPER(I22)=UPPER('Race Results'!E7),3,IF(UPPER(I22)=UPPER('Race Results'!F7),2,IF(UPPER(I22)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K22" s="15" t="s">
         <v>170</v>
@@ -3426,7 +3438,7 @@
       </c>
       <c r="M22" s="18">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3462,7 +3474,7 @@
       </c>
       <c r="J23" s="17">
         <f>IF(I23="","",IF(UPPER(I23)=UPPER('Race Results'!B7),10,IF(UPPER(I23)=UPPER('Race Results'!C7),6,IF(UPPER(I23)=UPPER('Race Results'!D7),4,IF(UPPER(I23)=UPPER('Race Results'!E7),3,IF(UPPER(I23)=UPPER('Race Results'!F7),2,IF(UPPER(I23)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>180</v>
@@ -3473,7 +3485,7 @@
       </c>
       <c r="M23" s="18">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3509,7 +3521,7 @@
       </c>
       <c r="J24" s="17">
         <f>IF(I24="","",IF(UPPER(I24)=UPPER('Race Results'!B7),10,IF(UPPER(I24)=UPPER('Race Results'!C7),6,IF(UPPER(I24)=UPPER('Race Results'!D7),4,IF(UPPER(I24)=UPPER('Race Results'!E7),3,IF(UPPER(I24)=UPPER('Race Results'!F7),2,IF(UPPER(I24)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K24" s="15" t="s">
         <v>171</v>
@@ -3520,7 +3532,7 @@
       </c>
       <c r="M24" s="18">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3556,7 +3568,7 @@
       </c>
       <c r="J25" s="17">
         <f>IF(I25="","",IF(UPPER(I25)=UPPER('Race Results'!B7),10,IF(UPPER(I25)=UPPER('Race Results'!C7),6,IF(UPPER(I25)=UPPER('Race Results'!D7),4,IF(UPPER(I25)=UPPER('Race Results'!E7),3,IF(UPPER(I25)=UPPER('Race Results'!F7),2,IF(UPPER(I25)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>183</v>
@@ -3567,7 +3579,7 @@
       </c>
       <c r="M25" s="18">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3603,7 +3615,7 @@
       </c>
       <c r="J26" s="17">
         <f>IF(I26="","",IF(UPPER(I26)=UPPER('Race Results'!B7),10,IF(UPPER(I26)=UPPER('Race Results'!C7),6,IF(UPPER(I26)=UPPER('Race Results'!D7),4,IF(UPPER(I26)=UPPER('Race Results'!E7),3,IF(UPPER(I26)=UPPER('Race Results'!F7),2,IF(UPPER(I26)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="15" t="s">
         <v>170</v>
@@ -3614,7 +3626,7 @@
       </c>
       <c r="M26" s="18">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
@@ -3650,7 +3662,7 @@
       </c>
       <c r="J27" s="17">
         <f>IF(I27="","",IF(UPPER(I27)=UPPER('Race Results'!B7),10,IF(UPPER(I27)=UPPER('Race Results'!C7),6,IF(UPPER(I27)=UPPER('Race Results'!D7),4,IF(UPPER(I27)=UPPER('Race Results'!E7),3,IF(UPPER(I27)=UPPER('Race Results'!F7),2,IF(UPPER(I27)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>158</v>
@@ -3661,7 +3673,7 @@
       </c>
       <c r="M27" s="18">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3697,7 +3709,7 @@
       </c>
       <c r="J28" s="17">
         <f>IF(I28="","",IF(UPPER(I28)=UPPER('Race Results'!B7),10,IF(UPPER(I28)=UPPER('Race Results'!C7),6,IF(UPPER(I28)=UPPER('Race Results'!D7),4,IF(UPPER(I28)=UPPER('Race Results'!E7),3,IF(UPPER(I28)=UPPER('Race Results'!F7),2,IF(UPPER(I28)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15" t="s">
         <v>164</v>
@@ -3708,7 +3720,7 @@
       </c>
       <c r="M28" s="18">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3791,7 +3803,7 @@
       </c>
       <c r="J30" s="17">
         <f>IF(I30="","",IF(UPPER(I30)=UPPER('Race Results'!B7),10,IF(UPPER(I30)=UPPER('Race Results'!C7),6,IF(UPPER(I30)=UPPER('Race Results'!D7),4,IF(UPPER(I30)=UPPER('Race Results'!E7),3,IF(UPPER(I30)=UPPER('Race Results'!F7),2,IF(UPPER(I30)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K30" s="15" t="s">
         <v>171</v>
@@ -3802,7 +3814,7 @@
       </c>
       <c r="M30" s="18">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -4026,11 +4038,11 @@
       </c>
       <c r="C3" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,1),"")</f>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D3" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C3,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4043,11 +4055,11 @@
       </c>
       <c r="C4" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),"")</f>
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D4" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C4,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4060,7 +4072,7 @@
       </c>
       <c r="C5" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,3),"")</f>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D5" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C5,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4073,15 +4085,15 @@
       </c>
       <c r="B6" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,4),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Marianne Chardon</v>
+        <v>Mick Hogg</v>
       </c>
       <c r="C6" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,4),"")</f>
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D6" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C6,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4090,15 +4102,15 @@
       </c>
       <c r="B7" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,5),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Vahi Crowley</v>
+        <v>Steve Burfitt</v>
       </c>
       <c r="C7" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,5),"")</f>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D7" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C7,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4107,15 +4119,15 @@
       </c>
       <c r="B8" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,6),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Vahi Crowley</v>
+        <v>Sean Horan</v>
       </c>
       <c r="C8" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,6),"")</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D8" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C8,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4124,11 +4136,11 @@
       </c>
       <c r="B9" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,7),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Vahi Crowley</v>
+        <v>Anthony Burke</v>
       </c>
       <c r="C9" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,7),"")</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C9,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4145,7 +4157,7 @@
       </c>
       <c r="C10" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,8),"")</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D10" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C10,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4158,15 +4170,15 @@
       </c>
       <c r="B11" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,9),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Bryan White</v>
+        <v>Gemma Forsyth</v>
       </c>
       <c r="C11" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,9),"")</f>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D11" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C11,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4175,11 +4187,11 @@
       </c>
       <c r="B12" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,10),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Bryan White</v>
+        <v>Vahi Crowley</v>
       </c>
       <c r="C12" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,10),"")</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D12" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C12,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4192,11 +4204,11 @@
       </c>
       <c r="B13" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,11),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Stephen Hughes</v>
+        <v>Vahi Crowley</v>
       </c>
       <c r="C13" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,11),"")</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D13" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C13,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4209,11 +4221,11 @@
       </c>
       <c r="B14" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,12),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>David Owens</v>
+        <v>Vahi Crowley</v>
       </c>
       <c r="C14" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,12),"")</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D14" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C14,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4226,11 +4238,11 @@
       </c>
       <c r="B15" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,13),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>David Owens</v>
+        <v>Stephen Hughes</v>
       </c>
       <c r="C15" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,13),"")</f>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D15" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C15,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4243,11 +4255,11 @@
       </c>
       <c r="B16" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,14),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>David Owens</v>
+        <v>Bryan White</v>
       </c>
       <c r="C16" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,14),"")</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D16" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C16,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4260,11 +4272,11 @@
       </c>
       <c r="B17" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,15),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Sean Horan</v>
+        <v>Bryan White</v>
       </c>
       <c r="C17" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,15),"")</f>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D17" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C17,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4277,15 +4289,15 @@
       </c>
       <c r="B18" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,16),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Darren Gill</v>
+        <v>Ryan Crowley</v>
       </c>
       <c r="C18" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,16),"")</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D18" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C18,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4294,15 +4306,15 @@
       </c>
       <c r="B19" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,17),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Jack Webb</v>
+        <v>Ryan Crowley</v>
       </c>
       <c r="C19" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,17),"")</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D19" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C19,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4311,15 +4323,15 @@
       </c>
       <c r="B20" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,18),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ronan Keohane</v>
+        <v>Ryan Crowley</v>
       </c>
       <c r="C20" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,18),"")</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D20" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C20,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4328,15 +4340,15 @@
       </c>
       <c r="B21" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,19),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ronan Keohane</v>
+        <v>Ryan Crowley</v>
       </c>
       <c r="C21" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,19),"")</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D21" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C21,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4345,11 +4357,11 @@
       </c>
       <c r="B22" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,20),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Lynn Forsyth</v>
+        <v>Liam Bridgeman</v>
       </c>
       <c r="C22" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,20),"")</f>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D22" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C22,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4362,11 +4374,11 @@
       </c>
       <c r="B23" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,21),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Lynn Forsyth</v>
+        <v>Ronan Keohane</v>
       </c>
       <c r="C23" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,21),"")</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D23" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C23,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4379,15 +4391,15 @@
       </c>
       <c r="B24" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,22),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ryan Crowley</v>
+        <v>Lynn Forsyth</v>
       </c>
       <c r="C24" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,22),"")</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D24" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C24,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4396,15 +4408,15 @@
       </c>
       <c r="B25" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,23),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ryan Crowley</v>
+        <v>Lynn Forsyth</v>
       </c>
       <c r="C25" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,23),"")</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D25" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C25,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4413,15 +4425,15 @@
       </c>
       <c r="B26" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,24),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ryan Crowley</v>
+        <v>Lynn Forsyth</v>
       </c>
       <c r="C26" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,24),"")</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D26" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C26,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4430,11 +4442,11 @@
       </c>
       <c r="B27" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,25),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Denise White</v>
+        <v>Steve Hunt</v>
       </c>
       <c r="C27" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,25),"")</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D27" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C27,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4447,11 +4459,11 @@
       </c>
       <c r="B28" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,26),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Steve Hunt</v>
+        <v>Denise White</v>
       </c>
       <c r="C28" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,26),"")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D28" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C28,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4464,11 +4476,11 @@
       </c>
       <c r="B29" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,27),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Denise White</v>
       </c>
       <c r="C29" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,27),"")</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D29" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C29,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="333" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD0D3C16-F6A3-4039-9D54-FD42E9FF78D1}"/>
+  <xr:revisionPtr revIDLastSave="381" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41923381-1E13-455E-A6BA-A2C27A04891D}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest List" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="183">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -239,9 +239,6 @@
   </si>
   <si>
     <t>Marianne Chardon</t>
-  </si>
-  <si>
-    <t>Ronan Keohane</t>
   </si>
   <si>
     <t>Sean Horan</t>
@@ -441,15 +438,6 @@
     <t>Blue Hercules</t>
   </si>
   <si>
-    <t>Who's Lope</t>
-  </si>
-  <si>
-    <t>Charles Darnay</t>
-  </si>
-  <si>
-    <t>Bnaider</t>
-  </si>
-  <si>
     <t>Brilliant Star</t>
   </si>
   <si>
@@ -564,9 +552,6 @@
     <t>Charly</t>
   </si>
   <si>
-    <t>Bobby McGee</t>
-  </si>
-  <si>
     <t>Blue Courvoisier</t>
   </si>
   <si>
@@ -610,12 +595,6 @@
   </si>
   <si>
     <t>Winding Stream</t>
-  </si>
-  <si>
-    <t>Synners Kid</t>
-  </si>
-  <si>
-    <t>Wild Thoughts</t>
   </si>
 </sst>
 </file>
@@ -930,6 +909,7 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -937,7 +917,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1239,16 +1218,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35"/>
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1278,7 +1257,7 @@
       <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1286,7 +1265,7 @@
       <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1294,7 +1273,7 @@
       <c r="A8" s="2">
         <v>5</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1302,7 +1281,7 @@
       <c r="A9" s="4">
         <v>6</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1310,7 +1289,7 @@
       <c r="A10" s="2">
         <v>7</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1318,7 +1297,7 @@
       <c r="A11" s="4">
         <v>8</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1326,7 +1305,7 @@
       <c r="A12" s="2">
         <v>9</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1334,7 +1313,7 @@
       <c r="A13" s="4">
         <v>10</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1342,7 +1321,7 @@
       <c r="A14" s="2">
         <v>11</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1350,7 +1329,7 @@
       <c r="A15" s="4">
         <v>12</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1358,7 +1337,7 @@
       <c r="A16" s="2">
         <v>13</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1366,7 +1345,7 @@
       <c r="A17" s="4">
         <v>14</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1374,7 +1353,7 @@
       <c r="A18" s="2">
         <v>15</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1382,7 +1361,7 @@
       <c r="A19" s="4">
         <v>16</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1390,7 +1369,7 @@
       <c r="A20" s="2">
         <v>17</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1398,7 +1377,7 @@
       <c r="A21" s="4">
         <v>18</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1406,7 +1385,7 @@
       <c r="A22" s="2">
         <v>19</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1414,7 +1393,7 @@
       <c r="A23" s="4">
         <v>20</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1422,7 +1401,7 @@
       <c r="A24" s="2">
         <v>21</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1430,7 +1409,7 @@
       <c r="A25" s="4">
         <v>22</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1446,7 +1425,7 @@
       <c r="A27" s="4">
         <v>24</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1454,7 +1433,7 @@
       <c r="A28" s="2">
         <v>25</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>88</v>
       </c>
     </row>
@@ -1462,7 +1441,7 @@
       <c r="A29" s="4">
         <v>26</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1470,9 +1449,7 @@
       <c r="A30" s="2">
         <v>27</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>90</v>
-      </c>
+      <c r="B30" s="5"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
@@ -1645,33 +1622,33 @@
       <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1679,19 +1656,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1699,19 +1676,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1719,19 +1696,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1739,19 +1716,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1759,19 +1736,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1779,19 +1756,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1799,19 +1776,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1819,19 +1796,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1839,19 +1816,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1859,19 +1836,19 @@
         <v>10</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1879,19 +1856,19 @@
         <v>11</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1899,17 +1876,17 @@
         <v>12</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E15" s="11"/>
       <c r="F15" s="11" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1917,15 +1894,15 @@
         <v>13</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1933,15 +1910,15 @@
         <v>14</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1949,15 +1926,15 @@
         <v>15</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1966,12 +1943,12 @@
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
-      <c r="F19" s="11" t="s">
-        <v>172</v>
+      <c r="F19" s="9" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1980,12 +1957,12 @@
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
-      <c r="F20" s="9" t="s">
-        <v>173</v>
+      <c r="F20" s="11" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1994,12 +1971,12 @@
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
-      <c r="F21" s="11" t="s">
-        <v>174</v>
+      <c r="F21" s="9" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2008,12 +1985,12 @@
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
-      <c r="F22" s="9" t="s">
-        <v>175</v>
+      <c r="F22" s="11" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -2021,13 +1998,11 @@
         <v>20</v>
       </c>
       <c r="B23" s="11"/>
-      <c r="C23" s="11" t="s">
-        <v>131</v>
-      </c>
+      <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
-      <c r="F23" s="11" t="s">
-        <v>176</v>
+      <c r="F23" s="9" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2035,13 +2010,11 @@
         <v>21</v>
       </c>
       <c r="B24" s="9"/>
-      <c r="C24" s="9" t="s">
-        <v>132</v>
-      </c>
+      <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
-      <c r="F24" s="9" t="s">
-        <v>177</v>
+      <c r="F24" s="11" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2049,13 +2022,11 @@
         <v>22</v>
       </c>
       <c r="B25" s="11"/>
-      <c r="C25" s="11" t="s">
-        <v>133</v>
-      </c>
+      <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
-      <c r="F25" s="11" t="s">
-        <v>178</v>
+      <c r="F25" s="9" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -2066,8 +2037,8 @@
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
-      <c r="F26" s="9" t="s">
-        <v>179</v>
+      <c r="F26" s="11" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2078,8 +2049,8 @@
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
-      <c r="F27" s="11" t="s">
-        <v>180</v>
+      <c r="F27" s="9" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -2090,8 +2061,8 @@
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="9" t="s">
-        <v>181</v>
+      <c r="F28" s="11" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2102,8 +2073,8 @@
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
-      <c r="F29" s="11" t="s">
-        <v>182</v>
+      <c r="F29" s="9" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -2114,8 +2085,8 @@
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
-      <c r="F30" s="9" t="s">
-        <v>183</v>
+      <c r="F30" s="11" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2126,8 +2097,8 @@
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="11" t="s">
-        <v>184</v>
+      <c r="F31" s="9" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2139,7 +2110,7 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -2151,7 +2122,7 @@
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2162,9 +2133,7 @@
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
-      <c r="F34" s="9" t="s">
-        <v>187</v>
-      </c>
+      <c r="F34" s="9"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
@@ -2174,9 +2143,7 @@
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
-      <c r="F35" s="9" t="s">
-        <v>188</v>
-      </c>
+      <c r="F35" s="9"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
@@ -2186,9 +2153,7 @@
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="11" t="s">
-        <v>189</v>
-      </c>
+      <c r="F36" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2258,99 +2223,51 @@
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>110</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>132</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>139</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>153</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -2369,15 +2286,15 @@
       <c r="G9" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2515,7 +2432,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>18</v>
@@ -2552,1269 +2469,945 @@
       <c r="A4" s="15">
         <v>1</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" s="17">
+      <c r="B4" s="16"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="17" t="str">
         <f>IF(C4="","",IF(UPPER(C4)=UPPER('Race Results'!B4),10,IF(UPPER(C4)=UPPER('Race Results'!C4),6,IF(UPPER(C4)=UPPER('Race Results'!D4),4,IF(UPPER(C4)=UPPER('Race Results'!E4),3,IF(UPPER(C4)=UPPER('Race Results'!F4),2,IF(UPPER(C4)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="F4" s="17">
+        <v/>
+      </c>
+      <c r="E4" s="15"/>
+      <c r="F4" s="17" t="str">
         <f>IF(E4="","",IF(UPPER(E4)=UPPER('Race Results'!B5),10,IF(UPPER(E4)=UPPER('Race Results'!C5),6,IF(UPPER(E4)=UPPER('Race Results'!D5),4,IF(UPPER(E4)=UPPER('Race Results'!E5),3,IF(UPPER(E4)=UPPER('Race Results'!F5),2,IF(UPPER(E4)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="H4" s="17">
+        <v/>
+      </c>
+      <c r="G4" s="15"/>
+      <c r="H4" s="17" t="str">
         <f>IF(G4="","",IF(UPPER(G4)=UPPER('Race Results'!B6),10,IF(UPPER(G4)=UPPER('Race Results'!C6),6,IF(UPPER(G4)=UPPER('Race Results'!D6),4,IF(UPPER(G4)=UPPER('Race Results'!E6),3,IF(UPPER(G4)=UPPER('Race Results'!F6),2,IF(UPPER(G4)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="J4" s="17">
+        <v/>
+      </c>
+      <c r="I4" s="15"/>
+      <c r="J4" s="17" t="str">
         <f>IF(I4="","",IF(UPPER(I4)=UPPER('Race Results'!B7),10,IF(UPPER(I4)=UPPER('Race Results'!C7),6,IF(UPPER(I4)=UPPER('Race Results'!D7),4,IF(UPPER(I4)=UPPER('Race Results'!E7),3,IF(UPPER(I4)=UPPER('Race Results'!F7),2,IF(UPPER(I4)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="L4" s="17">
+        <v/>
+      </c>
+      <c r="K4" s="15"/>
+      <c r="L4" s="17" t="str">
         <f>IF(K4="","",IF(UPPER(K4)=UPPER('Race Results'!B8),10,IF(UPPER(K4)=UPPER('Race Results'!C8),6,IF(UPPER(K4)=UPPER('Race Results'!D8),4,IF(UPPER(K4)=UPPER('Race Results'!E8),3,IF(UPPER(K4)=UPPER('Race Results'!F8),2,IF(UPPER(K4)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M4" s="18">
         <f t="shared" ref="M4:M33" si="0">IF(COUNTA(D4,F4,H4,J4,L4)=0,"",SUM(D4,F4,H4,J4,L4))</f>
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" s="17">
+      <c r="B5" s="5"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="17" t="str">
         <f>IF(C5="","",IF(UPPER(C5)=UPPER('Race Results'!B4),10,IF(UPPER(C5)=UPPER('Race Results'!C4),6,IF(UPPER(C5)=UPPER('Race Results'!D4),4,IF(UPPER(C5)=UPPER('Race Results'!E4),3,IF(UPPER(C5)=UPPER('Race Results'!F4),2,IF(UPPER(C5)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F5" s="17">
+        <v/>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="17" t="str">
         <f>IF(E5="","",IF(UPPER(E5)=UPPER('Race Results'!B5),10,IF(UPPER(E5)=UPPER('Race Results'!C5),6,IF(UPPER(E5)=UPPER('Race Results'!D5),4,IF(UPPER(E5)=UPPER('Race Results'!E5),3,IF(UPPER(E5)=UPPER('Race Results'!F5),2,IF(UPPER(E5)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="H5" s="17">
+        <v/>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="17" t="str">
         <f>IF(G5="","",IF(UPPER(G5)=UPPER('Race Results'!B6),10,IF(UPPER(G5)=UPPER('Race Results'!C6),6,IF(UPPER(G5)=UPPER('Race Results'!D6),4,IF(UPPER(G5)=UPPER('Race Results'!E6),3,IF(UPPER(G5)=UPPER('Race Results'!F6),2,IF(UPPER(G5)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="J5" s="17">
+        <v/>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="17" t="str">
         <f>IF(I5="","",IF(UPPER(I5)=UPPER('Race Results'!B7),10,IF(UPPER(I5)=UPPER('Race Results'!C7),6,IF(UPPER(I5)=UPPER('Race Results'!D7),4,IF(UPPER(I5)=UPPER('Race Results'!E7),3,IF(UPPER(I5)=UPPER('Race Results'!F7),2,IF(UPPER(I5)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="L5" s="17">
+        <v/>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="17" t="str">
         <f>IF(K5="","",IF(UPPER(K5)=UPPER('Race Results'!B8),10,IF(UPPER(K5)=UPPER('Race Results'!C8),6,IF(UPPER(K5)=UPPER('Race Results'!D8),4,IF(UPPER(K5)=UPPER('Race Results'!E8),3,IF(UPPER(K5)=UPPER('Race Results'!F8),2,IF(UPPER(K5)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M5" s="18">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="15">
         <v>3</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="D6" s="17">
+      <c r="B6" s="16"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="17" t="str">
         <f>IF(C6="","",IF(UPPER(C6)=UPPER('Race Results'!B4),10,IF(UPPER(C6)=UPPER('Race Results'!C4),6,IF(UPPER(C6)=UPPER('Race Results'!D4),4,IF(UPPER(C6)=UPPER('Race Results'!E4),3,IF(UPPER(C6)=UPPER('Race Results'!F4),2,IF(UPPER(C6)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>4</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="F6" s="17">
+        <v/>
+      </c>
+      <c r="E6" s="15"/>
+      <c r="F6" s="17" t="str">
         <f>IF(E6="","",IF(UPPER(E6)=UPPER('Race Results'!B5),10,IF(UPPER(E6)=UPPER('Race Results'!C5),6,IF(UPPER(E6)=UPPER('Race Results'!D5),4,IF(UPPER(E6)=UPPER('Race Results'!E5),3,IF(UPPER(E6)=UPPER('Race Results'!F5),2,IF(UPPER(E6)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="H6" s="17">
+        <v/>
+      </c>
+      <c r="G6" s="15"/>
+      <c r="H6" s="17" t="str">
         <f>IF(G6="","",IF(UPPER(G6)=UPPER('Race Results'!B6),10,IF(UPPER(G6)=UPPER('Race Results'!C6),6,IF(UPPER(G6)=UPPER('Race Results'!D6),4,IF(UPPER(G6)=UPPER('Race Results'!E6),3,IF(UPPER(G6)=UPPER('Race Results'!F6),2,IF(UPPER(G6)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>4</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="J6" s="17">
+        <v/>
+      </c>
+      <c r="I6" s="15"/>
+      <c r="J6" s="17" t="str">
         <f>IF(I6="","",IF(UPPER(I6)=UPPER('Race Results'!B7),10,IF(UPPER(I6)=UPPER('Race Results'!C7),6,IF(UPPER(I6)=UPPER('Race Results'!D7),4,IF(UPPER(I6)=UPPER('Race Results'!E7),3,IF(UPPER(I6)=UPPER('Race Results'!F7),2,IF(UPPER(I6)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>4</v>
-      </c>
-      <c r="K6" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L6" s="17">
+        <v/>
+      </c>
+      <c r="K6" s="15"/>
+      <c r="L6" s="17" t="str">
         <f>IF(K6="","",IF(UPPER(K6)=UPPER('Race Results'!B8),10,IF(UPPER(K6)=UPPER('Race Results'!C8),6,IF(UPPER(K6)=UPPER('Race Results'!D8),4,IF(UPPER(K6)=UPPER('Race Results'!E8),3,IF(UPPER(K6)=UPPER('Race Results'!F8),2,IF(UPPER(K6)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M6" s="18">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7" s="17">
+      <c r="B7" s="5"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="17" t="str">
         <f>IF(C7="","",IF(UPPER(C7)=UPPER('Race Results'!B4),10,IF(UPPER(C7)=UPPER('Race Results'!C4),6,IF(UPPER(C7)=UPPER('Race Results'!D4),4,IF(UPPER(C7)=UPPER('Race Results'!E4),3,IF(UPPER(C7)=UPPER('Race Results'!F4),2,IF(UPPER(C7)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F7" s="17">
+        <v/>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="17" t="str">
         <f>IF(E7="","",IF(UPPER(E7)=UPPER('Race Results'!B5),10,IF(UPPER(E7)=UPPER('Race Results'!C5),6,IF(UPPER(E7)=UPPER('Race Results'!D5),4,IF(UPPER(E7)=UPPER('Race Results'!E5),3,IF(UPPER(E7)=UPPER('Race Results'!F5),2,IF(UPPER(E7)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="H7" s="17">
+        <v/>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="17" t="str">
         <f>IF(G7="","",IF(UPPER(G7)=UPPER('Race Results'!B6),10,IF(UPPER(G7)=UPPER('Race Results'!C6),6,IF(UPPER(G7)=UPPER('Race Results'!D6),4,IF(UPPER(G7)=UPPER('Race Results'!E6),3,IF(UPPER(G7)=UPPER('Race Results'!F6),2,IF(UPPER(G7)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>3</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J7" s="17">
+        <v/>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="17" t="str">
         <f>IF(I7="","",IF(UPPER(I7)=UPPER('Race Results'!B7),10,IF(UPPER(I7)=UPPER('Race Results'!C7),6,IF(UPPER(I7)=UPPER('Race Results'!D7),4,IF(UPPER(I7)=UPPER('Race Results'!E7),3,IF(UPPER(I7)=UPPER('Race Results'!F7),2,IF(UPPER(I7)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="L7" s="17">
+        <v/>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="17" t="str">
         <f>IF(K7="","",IF(UPPER(K7)=UPPER('Race Results'!B8),10,IF(UPPER(K7)=UPPER('Race Results'!C8),6,IF(UPPER(K7)=UPPER('Race Results'!D8),4,IF(UPPER(K7)=UPPER('Race Results'!E8),3,IF(UPPER(K7)=UPPER('Race Results'!F8),2,IF(UPPER(K7)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M7" s="18">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="15">
         <v>5</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" s="17">
+      <c r="B8" s="16"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="17" t="str">
         <f>IF(C8="","",IF(UPPER(C8)=UPPER('Race Results'!B4),10,IF(UPPER(C8)=UPPER('Race Results'!C4),6,IF(UPPER(C8)=UPPER('Race Results'!D4),4,IF(UPPER(C8)=UPPER('Race Results'!E4),3,IF(UPPER(C8)=UPPER('Race Results'!F4),2,IF(UPPER(C8)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>3</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="F8" s="17">
+        <v/>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="17" t="str">
         <f>IF(E8="","",IF(UPPER(E8)=UPPER('Race Results'!B5),10,IF(UPPER(E8)=UPPER('Race Results'!C5),6,IF(UPPER(E8)=UPPER('Race Results'!D5),4,IF(UPPER(E8)=UPPER('Race Results'!E5),3,IF(UPPER(E8)=UPPER('Race Results'!F5),2,IF(UPPER(E8)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="H8" s="17">
+        <v/>
+      </c>
+      <c r="G8" s="15"/>
+      <c r="H8" s="17" t="str">
         <f>IF(G8="","",IF(UPPER(G8)=UPPER('Race Results'!B6),10,IF(UPPER(G8)=UPPER('Race Results'!C6),6,IF(UPPER(G8)=UPPER('Race Results'!D6),4,IF(UPPER(G8)=UPPER('Race Results'!E6),3,IF(UPPER(G8)=UPPER('Race Results'!F6),2,IF(UPPER(G8)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="J8" s="17">
+        <v/>
+      </c>
+      <c r="I8" s="15"/>
+      <c r="J8" s="17" t="str">
         <f>IF(I8="","",IF(UPPER(I8)=UPPER('Race Results'!B7),10,IF(UPPER(I8)=UPPER('Race Results'!C7),6,IF(UPPER(I8)=UPPER('Race Results'!D7),4,IF(UPPER(I8)=UPPER('Race Results'!E7),3,IF(UPPER(I8)=UPPER('Race Results'!F7),2,IF(UPPER(I8)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>3</v>
-      </c>
-      <c r="K8" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="L8" s="17">
+        <v/>
+      </c>
+      <c r="K8" s="15"/>
+      <c r="L8" s="17" t="str">
         <f>IF(K8="","",IF(UPPER(K8)=UPPER('Race Results'!B8),10,IF(UPPER(K8)=UPPER('Race Results'!C8),6,IF(UPPER(K8)=UPPER('Race Results'!D8),4,IF(UPPER(K8)=UPPER('Race Results'!E8),3,IF(UPPER(K8)=UPPER('Race Results'!F8),2,IF(UPPER(K8)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M8" s="18">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>6</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" s="17">
+      <c r="B9" s="5"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="17" t="str">
         <f>IF(C9="","",IF(UPPER(C9)=UPPER('Race Results'!B4),10,IF(UPPER(C9)=UPPER('Race Results'!C4),6,IF(UPPER(C9)=UPPER('Race Results'!D4),4,IF(UPPER(C9)=UPPER('Race Results'!E4),3,IF(UPPER(C9)=UPPER('Race Results'!F4),2,IF(UPPER(C9)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>2</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F9" s="17">
+        <v/>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="17" t="str">
         <f>IF(E9="","",IF(UPPER(E9)=UPPER('Race Results'!B5),10,IF(UPPER(E9)=UPPER('Race Results'!C5),6,IF(UPPER(E9)=UPPER('Race Results'!D5),4,IF(UPPER(E9)=UPPER('Race Results'!E5),3,IF(UPPER(E9)=UPPER('Race Results'!F5),2,IF(UPPER(E9)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="H9" s="17">
+        <v/>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="17" t="str">
         <f>IF(G9="","",IF(UPPER(G9)=UPPER('Race Results'!B6),10,IF(UPPER(G9)=UPPER('Race Results'!C6),6,IF(UPPER(G9)=UPPER('Race Results'!D6),4,IF(UPPER(G9)=UPPER('Race Results'!E6),3,IF(UPPER(G9)=UPPER('Race Results'!F6),2,IF(UPPER(G9)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>2</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="J9" s="17">
+        <v/>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="17" t="str">
         <f>IF(I9="","",IF(UPPER(I9)=UPPER('Race Results'!B7),10,IF(UPPER(I9)=UPPER('Race Results'!C7),6,IF(UPPER(I9)=UPPER('Race Results'!D7),4,IF(UPPER(I9)=UPPER('Race Results'!E7),3,IF(UPPER(I9)=UPPER('Race Results'!F7),2,IF(UPPER(I9)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>2</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="L9" s="17">
+        <v/>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="17" t="str">
         <f>IF(K9="","",IF(UPPER(K9)=UPPER('Race Results'!B8),10,IF(UPPER(K9)=UPPER('Race Results'!C8),6,IF(UPPER(K9)=UPPER('Race Results'!D8),4,IF(UPPER(K9)=UPPER('Race Results'!E8),3,IF(UPPER(K9)=UPPER('Race Results'!F8),2,IF(UPPER(K9)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M9" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="15">
         <v>7</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" s="17">
+      <c r="B10" s="16"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="17" t="str">
         <f>IF(C10="","",IF(UPPER(C10)=UPPER('Race Results'!B4),10,IF(UPPER(C10)=UPPER('Race Results'!C4),6,IF(UPPER(C10)=UPPER('Race Results'!D4),4,IF(UPPER(C10)=UPPER('Race Results'!E4),3,IF(UPPER(C10)=UPPER('Race Results'!F4),2,IF(UPPER(C10)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="F10" s="17">
+        <v/>
+      </c>
+      <c r="E10" s="15"/>
+      <c r="F10" s="17" t="str">
         <f>IF(E10="","",IF(UPPER(E10)=UPPER('Race Results'!B5),10,IF(UPPER(E10)=UPPER('Race Results'!C5),6,IF(UPPER(E10)=UPPER('Race Results'!D5),4,IF(UPPER(E10)=UPPER('Race Results'!E5),3,IF(UPPER(E10)=UPPER('Race Results'!F5),2,IF(UPPER(E10)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="H10" s="17">
+        <v/>
+      </c>
+      <c r="G10" s="15"/>
+      <c r="H10" s="17" t="str">
         <f>IF(G10="","",IF(UPPER(G10)=UPPER('Race Results'!B6),10,IF(UPPER(G10)=UPPER('Race Results'!C6),6,IF(UPPER(G10)=UPPER('Race Results'!D6),4,IF(UPPER(G10)=UPPER('Race Results'!E6),3,IF(UPPER(G10)=UPPER('Race Results'!F6),2,IF(UPPER(G10)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>1</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="J10" s="17">
+        <v/>
+      </c>
+      <c r="I10" s="15"/>
+      <c r="J10" s="17" t="str">
         <f>IF(I10="","",IF(UPPER(I10)=UPPER('Race Results'!B7),10,IF(UPPER(I10)=UPPER('Race Results'!C7),6,IF(UPPER(I10)=UPPER('Race Results'!D7),4,IF(UPPER(I10)=UPPER('Race Results'!E7),3,IF(UPPER(I10)=UPPER('Race Results'!F7),2,IF(UPPER(I10)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>1</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="L10" s="17">
+        <v/>
+      </c>
+      <c r="K10" s="15"/>
+      <c r="L10" s="17" t="str">
         <f>IF(K10="","",IF(UPPER(K10)=UPPER('Race Results'!B8),10,IF(UPPER(K10)=UPPER('Race Results'!C8),6,IF(UPPER(K10)=UPPER('Race Results'!D8),4,IF(UPPER(K10)=UPPER('Race Results'!E8),3,IF(UPPER(K10)=UPPER('Race Results'!F8),2,IF(UPPER(K10)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M10" s="18">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>8</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" s="17">
+      <c r="B11" s="5"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="17" t="str">
         <f>IF(C11="","",IF(UPPER(C11)=UPPER('Race Results'!B4),10,IF(UPPER(C11)=UPPER('Race Results'!C4),6,IF(UPPER(C11)=UPPER('Race Results'!D4),4,IF(UPPER(C11)=UPPER('Race Results'!E4),3,IF(UPPER(C11)=UPPER('Race Results'!F4),2,IF(UPPER(C11)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F11" s="17">
+        <v/>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="17" t="str">
         <f>IF(E11="","",IF(UPPER(E11)=UPPER('Race Results'!B5),10,IF(UPPER(E11)=UPPER('Race Results'!C5),6,IF(UPPER(E11)=UPPER('Race Results'!D5),4,IF(UPPER(E11)=UPPER('Race Results'!E5),3,IF(UPPER(E11)=UPPER('Race Results'!F5),2,IF(UPPER(E11)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="H11" s="17">
+        <v/>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="17" t="str">
         <f>IF(G11="","",IF(UPPER(G11)=UPPER('Race Results'!B6),10,IF(UPPER(G11)=UPPER('Race Results'!C6),6,IF(UPPER(G11)=UPPER('Race Results'!D6),4,IF(UPPER(G11)=UPPER('Race Results'!E6),3,IF(UPPER(G11)=UPPER('Race Results'!F6),2,IF(UPPER(G11)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J11" s="17">
+        <v/>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="17" t="str">
         <f>IF(I11="","",IF(UPPER(I11)=UPPER('Race Results'!B7),10,IF(UPPER(I11)=UPPER('Race Results'!C7),6,IF(UPPER(I11)=UPPER('Race Results'!D7),4,IF(UPPER(I11)=UPPER('Race Results'!E7),3,IF(UPPER(I11)=UPPER('Race Results'!F7),2,IF(UPPER(I11)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="L11" s="17">
+        <v/>
+      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="17" t="str">
         <f>IF(K11="","",IF(UPPER(K11)=UPPER('Race Results'!B8),10,IF(UPPER(K11)=UPPER('Race Results'!C8),6,IF(UPPER(K11)=UPPER('Race Results'!D8),4,IF(UPPER(K11)=UPPER('Race Results'!E8),3,IF(UPPER(K11)=UPPER('Race Results'!F8),2,IF(UPPER(K11)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M11" s="18">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="15">
         <v>9</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" s="17">
+      <c r="B12" s="16"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="17" t="str">
         <f>IF(C12="","",IF(UPPER(C12)=UPPER('Race Results'!B4),10,IF(UPPER(C12)=UPPER('Race Results'!C4),6,IF(UPPER(C12)=UPPER('Race Results'!D4),4,IF(UPPER(C12)=UPPER('Race Results'!E4),3,IF(UPPER(C12)=UPPER('Race Results'!F4),2,IF(UPPER(C12)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="F12" s="17">
+        <v/>
+      </c>
+      <c r="E12" s="15"/>
+      <c r="F12" s="17" t="str">
         <f>IF(E12="","",IF(UPPER(E12)=UPPER('Race Results'!B5),10,IF(UPPER(E12)=UPPER('Race Results'!C5),6,IF(UPPER(E12)=UPPER('Race Results'!D5),4,IF(UPPER(E12)=UPPER('Race Results'!E5),3,IF(UPPER(E12)=UPPER('Race Results'!F5),2,IF(UPPER(E12)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="H12" s="17">
+        <v/>
+      </c>
+      <c r="G12" s="15"/>
+      <c r="H12" s="17" t="str">
         <f>IF(G12="","",IF(UPPER(G12)=UPPER('Race Results'!B6),10,IF(UPPER(G12)=UPPER('Race Results'!C6),6,IF(UPPER(G12)=UPPER('Race Results'!D6),4,IF(UPPER(G12)=UPPER('Race Results'!E6),3,IF(UPPER(G12)=UPPER('Race Results'!F6),2,IF(UPPER(G12)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>4</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="J12" s="17">
+        <v/>
+      </c>
+      <c r="I12" s="15"/>
+      <c r="J12" s="17" t="str">
         <f>IF(I12="","",IF(UPPER(I12)=UPPER('Race Results'!B7),10,IF(UPPER(I12)=UPPER('Race Results'!C7),6,IF(UPPER(I12)=UPPER('Race Results'!D7),4,IF(UPPER(I12)=UPPER('Race Results'!E7),3,IF(UPPER(I12)=UPPER('Race Results'!F7),2,IF(UPPER(I12)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L12" s="17">
+        <v/>
+      </c>
+      <c r="K12" s="15"/>
+      <c r="L12" s="17" t="str">
         <f>IF(K12="","",IF(UPPER(K12)=UPPER('Race Results'!B8),10,IF(UPPER(K12)=UPPER('Race Results'!C8),6,IF(UPPER(K12)=UPPER('Race Results'!D8),4,IF(UPPER(K12)=UPPER('Race Results'!E8),3,IF(UPPER(K12)=UPPER('Race Results'!F8),2,IF(UPPER(K12)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M12" s="18">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>10</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D13" s="17">
+      <c r="B13" s="5"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="17" t="str">
         <f>IF(C13="","",IF(UPPER(C13)=UPPER('Race Results'!B4),10,IF(UPPER(C13)=UPPER('Race Results'!C4),6,IF(UPPER(C13)=UPPER('Race Results'!D4),4,IF(UPPER(C13)=UPPER('Race Results'!E4),3,IF(UPPER(C13)=UPPER('Race Results'!F4),2,IF(UPPER(C13)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>4</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="F13" s="17">
+        <v/>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="17" t="str">
         <f>IF(E13="","",IF(UPPER(E13)=UPPER('Race Results'!B5),10,IF(UPPER(E13)=UPPER('Race Results'!C5),6,IF(UPPER(E13)=UPPER('Race Results'!D5),4,IF(UPPER(E13)=UPPER('Race Results'!E5),3,IF(UPPER(E13)=UPPER('Race Results'!F5),2,IF(UPPER(E13)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="H13" s="17">
+        <v/>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="17" t="str">
         <f>IF(G13="","",IF(UPPER(G13)=UPPER('Race Results'!B6),10,IF(UPPER(G13)=UPPER('Race Results'!C6),6,IF(UPPER(G13)=UPPER('Race Results'!D6),4,IF(UPPER(G13)=UPPER('Race Results'!E6),3,IF(UPPER(G13)=UPPER('Race Results'!F6),2,IF(UPPER(G13)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="J13" s="17">
+        <v/>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="17" t="str">
         <f>IF(I13="","",IF(UPPER(I13)=UPPER('Race Results'!B7),10,IF(UPPER(I13)=UPPER('Race Results'!C7),6,IF(UPPER(I13)=UPPER('Race Results'!D7),4,IF(UPPER(I13)=UPPER('Race Results'!E7),3,IF(UPPER(I13)=UPPER('Race Results'!F7),2,IF(UPPER(I13)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="L13" s="17">
+        <v/>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="17" t="str">
         <f>IF(K13="","",IF(UPPER(K13)=UPPER('Race Results'!B8),10,IF(UPPER(K13)=UPPER('Race Results'!C8),6,IF(UPPER(K13)=UPPER('Race Results'!D8),4,IF(UPPER(K13)=UPPER('Race Results'!E8),3,IF(UPPER(K13)=UPPER('Race Results'!F8),2,IF(UPPER(K13)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M13" s="18">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="15">
         <v>11</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D14" s="17">
+      <c r="B14" s="16"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="17" t="str">
         <f>IF(C14="","",IF(UPPER(C14)=UPPER('Race Results'!B4),10,IF(UPPER(C14)=UPPER('Race Results'!C4),6,IF(UPPER(C14)=UPPER('Race Results'!D4),4,IF(UPPER(C14)=UPPER('Race Results'!E4),3,IF(UPPER(C14)=UPPER('Race Results'!F4),2,IF(UPPER(C14)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="F14" s="17">
+        <v/>
+      </c>
+      <c r="E14" s="15"/>
+      <c r="F14" s="17" t="str">
         <f>IF(E14="","",IF(UPPER(E14)=UPPER('Race Results'!B5),10,IF(UPPER(E14)=UPPER('Race Results'!C5),6,IF(UPPER(E14)=UPPER('Race Results'!D5),4,IF(UPPER(E14)=UPPER('Race Results'!E5),3,IF(UPPER(E14)=UPPER('Race Results'!F5),2,IF(UPPER(E14)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="H14" s="17">
+        <v/>
+      </c>
+      <c r="G14" s="15"/>
+      <c r="H14" s="17" t="str">
         <f>IF(G14="","",IF(UPPER(G14)=UPPER('Race Results'!B6),10,IF(UPPER(G14)=UPPER('Race Results'!C6),6,IF(UPPER(G14)=UPPER('Race Results'!D6),4,IF(UPPER(G14)=UPPER('Race Results'!E6),3,IF(UPPER(G14)=UPPER('Race Results'!F6),2,IF(UPPER(G14)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="J14" s="17">
+        <v/>
+      </c>
+      <c r="I14" s="15"/>
+      <c r="J14" s="17" t="str">
         <f>IF(I14="","",IF(UPPER(I14)=UPPER('Race Results'!B7),10,IF(UPPER(I14)=UPPER('Race Results'!C7),6,IF(UPPER(I14)=UPPER('Race Results'!D7),4,IF(UPPER(I14)=UPPER('Race Results'!E7),3,IF(UPPER(I14)=UPPER('Race Results'!F7),2,IF(UPPER(I14)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="L14" s="17">
+        <v/>
+      </c>
+      <c r="K14" s="15"/>
+      <c r="L14" s="17" t="str">
         <f>IF(K14="","",IF(UPPER(K14)=UPPER('Race Results'!B8),10,IF(UPPER(K14)=UPPER('Race Results'!C8),6,IF(UPPER(K14)=UPPER('Race Results'!D8),4,IF(UPPER(K14)=UPPER('Race Results'!E8),3,IF(UPPER(K14)=UPPER('Race Results'!F8),2,IF(UPPER(K14)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M14" s="18">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>12</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" s="17">
+      <c r="B15" s="5"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="17" t="str">
         <f>IF(C15="","",IF(UPPER(C15)=UPPER('Race Results'!B4),10,IF(UPPER(C15)=UPPER('Race Results'!C4),6,IF(UPPER(C15)=UPPER('Race Results'!D4),4,IF(UPPER(C15)=UPPER('Race Results'!E4),3,IF(UPPER(C15)=UPPER('Race Results'!F4),2,IF(UPPER(C15)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>3</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F15" s="17">
+        <v/>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="17" t="str">
         <f>IF(E15="","",IF(UPPER(E15)=UPPER('Race Results'!B5),10,IF(UPPER(E15)=UPPER('Race Results'!C5),6,IF(UPPER(E15)=UPPER('Race Results'!D5),4,IF(UPPER(E15)=UPPER('Race Results'!E5),3,IF(UPPER(E15)=UPPER('Race Results'!F5),2,IF(UPPER(E15)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="H15" s="17">
+        <v/>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="17" t="str">
         <f>IF(G15="","",IF(UPPER(G15)=UPPER('Race Results'!B6),10,IF(UPPER(G15)=UPPER('Race Results'!C6),6,IF(UPPER(G15)=UPPER('Race Results'!D6),4,IF(UPPER(G15)=UPPER('Race Results'!E6),3,IF(UPPER(G15)=UPPER('Race Results'!F6),2,IF(UPPER(G15)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>3</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="J15" s="17">
+        <v/>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="17" t="str">
         <f>IF(I15="","",IF(UPPER(I15)=UPPER('Race Results'!B7),10,IF(UPPER(I15)=UPPER('Race Results'!C7),6,IF(UPPER(I15)=UPPER('Race Results'!D7),4,IF(UPPER(I15)=UPPER('Race Results'!E7),3,IF(UPPER(I15)=UPPER('Race Results'!F7),2,IF(UPPER(I15)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>3</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="L15" s="17">
+        <v/>
+      </c>
+      <c r="K15" s="4"/>
+      <c r="L15" s="17" t="str">
         <f>IF(K15="","",IF(UPPER(K15)=UPPER('Race Results'!B8),10,IF(UPPER(K15)=UPPER('Race Results'!C8),6,IF(UPPER(K15)=UPPER('Race Results'!D8),4,IF(UPPER(K15)=UPPER('Race Results'!E8),3,IF(UPPER(K15)=UPPER('Race Results'!F8),2,IF(UPPER(K15)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M15" s="18">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="15">
         <v>13</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D16" s="17">
+      <c r="B16" s="16"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="17" t="str">
         <f>IF(C16="","",IF(UPPER(C16)=UPPER('Race Results'!B4),10,IF(UPPER(C16)=UPPER('Race Results'!C4),6,IF(UPPER(C16)=UPPER('Race Results'!D4),4,IF(UPPER(C16)=UPPER('Race Results'!E4),3,IF(UPPER(C16)=UPPER('Race Results'!F4),2,IF(UPPER(C16)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="F16" s="17">
+        <v/>
+      </c>
+      <c r="E16" s="15"/>
+      <c r="F16" s="17" t="str">
         <f>IF(E16="","",IF(UPPER(E16)=UPPER('Race Results'!B5),10,IF(UPPER(E16)=UPPER('Race Results'!C5),6,IF(UPPER(E16)=UPPER('Race Results'!D5),4,IF(UPPER(E16)=UPPER('Race Results'!E5),3,IF(UPPER(E16)=UPPER('Race Results'!F5),2,IF(UPPER(E16)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="H16" s="17">
+        <v/>
+      </c>
+      <c r="G16" s="15"/>
+      <c r="H16" s="17" t="str">
         <f>IF(G16="","",IF(UPPER(G16)=UPPER('Race Results'!B6),10,IF(UPPER(G16)=UPPER('Race Results'!C6),6,IF(UPPER(G16)=UPPER('Race Results'!D6),4,IF(UPPER(G16)=UPPER('Race Results'!E6),3,IF(UPPER(G16)=UPPER('Race Results'!F6),2,IF(UPPER(G16)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>2</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="J16" s="17">
+        <v/>
+      </c>
+      <c r="I16" s="15"/>
+      <c r="J16" s="17" t="str">
         <f>IF(I16="","",IF(UPPER(I16)=UPPER('Race Results'!B7),10,IF(UPPER(I16)=UPPER('Race Results'!C7),6,IF(UPPER(I16)=UPPER('Race Results'!D7),4,IF(UPPER(I16)=UPPER('Race Results'!E7),3,IF(UPPER(I16)=UPPER('Race Results'!F7),2,IF(UPPER(I16)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>2</v>
-      </c>
-      <c r="K16" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="L16" s="17">
+        <v/>
+      </c>
+      <c r="K16" s="15"/>
+      <c r="L16" s="17" t="str">
         <f>IF(K16="","",IF(UPPER(K16)=UPPER('Race Results'!B8),10,IF(UPPER(K16)=UPPER('Race Results'!C8),6,IF(UPPER(K16)=UPPER('Race Results'!D8),4,IF(UPPER(K16)=UPPER('Race Results'!E8),3,IF(UPPER(K16)=UPPER('Race Results'!F8),2,IF(UPPER(K16)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M16" s="18">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>14</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="17">
+      <c r="B17" s="5"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="17" t="str">
         <f>IF(C17="","",IF(UPPER(C17)=UPPER('Race Results'!B4),10,IF(UPPER(C17)=UPPER('Race Results'!C4),6,IF(UPPER(C17)=UPPER('Race Results'!D4),4,IF(UPPER(C17)=UPPER('Race Results'!E4),3,IF(UPPER(C17)=UPPER('Race Results'!F4),2,IF(UPPER(C17)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F17" s="17">
+        <v/>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="17" t="str">
         <f>IF(E17="","",IF(UPPER(E17)=UPPER('Race Results'!B5),10,IF(UPPER(E17)=UPPER('Race Results'!C5),6,IF(UPPER(E17)=UPPER('Race Results'!D5),4,IF(UPPER(E17)=UPPER('Race Results'!E5),3,IF(UPPER(E17)=UPPER('Race Results'!F5),2,IF(UPPER(E17)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="H17" s="17">
+        <v/>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="17" t="str">
         <f>IF(G17="","",IF(UPPER(G17)=UPPER('Race Results'!B6),10,IF(UPPER(G17)=UPPER('Race Results'!C6),6,IF(UPPER(G17)=UPPER('Race Results'!D6),4,IF(UPPER(G17)=UPPER('Race Results'!E6),3,IF(UPPER(G17)=UPPER('Race Results'!F6),2,IF(UPPER(G17)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="J17" s="17">
+        <v/>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="17" t="str">
         <f>IF(I17="","",IF(UPPER(I17)=UPPER('Race Results'!B7),10,IF(UPPER(I17)=UPPER('Race Results'!C7),6,IF(UPPER(I17)=UPPER('Race Results'!D7),4,IF(UPPER(I17)=UPPER('Race Results'!E7),3,IF(UPPER(I17)=UPPER('Race Results'!F7),2,IF(UPPER(I17)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>1</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="L17" s="17">
+        <v/>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="17" t="str">
         <f>IF(K17="","",IF(UPPER(K17)=UPPER('Race Results'!B8),10,IF(UPPER(K17)=UPPER('Race Results'!C8),6,IF(UPPER(K17)=UPPER('Race Results'!D8),4,IF(UPPER(K17)=UPPER('Race Results'!E8),3,IF(UPPER(K17)=UPPER('Race Results'!F8),2,IF(UPPER(K17)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M17" s="18">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="15">
         <v>15</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" s="17">
+      <c r="B18" s="16"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="17" t="str">
         <f>IF(C18="","",IF(UPPER(C18)=UPPER('Race Results'!B4),10,IF(UPPER(C18)=UPPER('Race Results'!C4),6,IF(UPPER(C18)=UPPER('Race Results'!D4),4,IF(UPPER(C18)=UPPER('Race Results'!E4),3,IF(UPPER(C18)=UPPER('Race Results'!F4),2,IF(UPPER(C18)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>2</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="F18" s="17">
+        <v/>
+      </c>
+      <c r="E18" s="15"/>
+      <c r="F18" s="17" t="str">
         <f>IF(E18="","",IF(UPPER(E18)=UPPER('Race Results'!B5),10,IF(UPPER(E18)=UPPER('Race Results'!C5),6,IF(UPPER(E18)=UPPER('Race Results'!D5),4,IF(UPPER(E18)=UPPER('Race Results'!E5),3,IF(UPPER(E18)=UPPER('Race Results'!F5),2,IF(UPPER(E18)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="H18" s="17">
+        <v/>
+      </c>
+      <c r="G18" s="15"/>
+      <c r="H18" s="17" t="str">
         <f>IF(G18="","",IF(UPPER(G18)=UPPER('Race Results'!B6),10,IF(UPPER(G18)=UPPER('Race Results'!C6),6,IF(UPPER(G18)=UPPER('Race Results'!D6),4,IF(UPPER(G18)=UPPER('Race Results'!E6),3,IF(UPPER(G18)=UPPER('Race Results'!F6),2,IF(UPPER(G18)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>4</v>
-      </c>
-      <c r="I18" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="J18" s="17">
+        <v/>
+      </c>
+      <c r="I18" s="15"/>
+      <c r="J18" s="17" t="str">
         <f>IF(I18="","",IF(UPPER(I18)=UPPER('Race Results'!B7),10,IF(UPPER(I18)=UPPER('Race Results'!C7),6,IF(UPPER(I18)=UPPER('Race Results'!D7),4,IF(UPPER(I18)=UPPER('Race Results'!E7),3,IF(UPPER(I18)=UPPER('Race Results'!F7),2,IF(UPPER(I18)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L18" s="17">
+        <v/>
+      </c>
+      <c r="K18" s="15"/>
+      <c r="L18" s="17" t="str">
         <f>IF(K18="","",IF(UPPER(K18)=UPPER('Race Results'!B8),10,IF(UPPER(K18)=UPPER('Race Results'!C8),6,IF(UPPER(K18)=UPPER('Race Results'!D8),4,IF(UPPER(K18)=UPPER('Race Results'!E8),3,IF(UPPER(K18)=UPPER('Race Results'!F8),2,IF(UPPER(K18)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M18" s="18">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>16</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D19" s="17">
+      <c r="B19" s="5"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="17" t="str">
         <f>IF(C19="","",IF(UPPER(C19)=UPPER('Race Results'!B4),10,IF(UPPER(C19)=UPPER('Race Results'!C4),6,IF(UPPER(C19)=UPPER('Race Results'!D4),4,IF(UPPER(C19)=UPPER('Race Results'!E4),3,IF(UPPER(C19)=UPPER('Race Results'!F4),2,IF(UPPER(C19)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>1</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="F19" s="17">
+        <v/>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="17" t="str">
         <f>IF(E19="","",IF(UPPER(E19)=UPPER('Race Results'!B5),10,IF(UPPER(E19)=UPPER('Race Results'!C5),6,IF(UPPER(E19)=UPPER('Race Results'!D5),4,IF(UPPER(E19)=UPPER('Race Results'!E5),3,IF(UPPER(E19)=UPPER('Race Results'!F5),2,IF(UPPER(E19)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H19" s="17">
+        <v/>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="17" t="str">
         <f>IF(G19="","",IF(UPPER(G19)=UPPER('Race Results'!B6),10,IF(UPPER(G19)=UPPER('Race Results'!C6),6,IF(UPPER(G19)=UPPER('Race Results'!D6),4,IF(UPPER(G19)=UPPER('Race Results'!E6),3,IF(UPPER(G19)=UPPER('Race Results'!F6),2,IF(UPPER(G19)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>1</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="J19" s="17">
+        <v/>
+      </c>
+      <c r="I19" s="4"/>
+      <c r="J19" s="17" t="str">
         <f>IF(I19="","",IF(UPPER(I19)=UPPER('Race Results'!B7),10,IF(UPPER(I19)=UPPER('Race Results'!C7),6,IF(UPPER(I19)=UPPER('Race Results'!D7),4,IF(UPPER(I19)=UPPER('Race Results'!E7),3,IF(UPPER(I19)=UPPER('Race Results'!F7),2,IF(UPPER(I19)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>4</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="L19" s="17">
+        <v/>
+      </c>
+      <c r="K19" s="4"/>
+      <c r="L19" s="17" t="str">
         <f>IF(K19="","",IF(UPPER(K19)=UPPER('Race Results'!B8),10,IF(UPPER(K19)=UPPER('Race Results'!C8),6,IF(UPPER(K19)=UPPER('Race Results'!D8),4,IF(UPPER(K19)=UPPER('Race Results'!E8),3,IF(UPPER(K19)=UPPER('Race Results'!F8),2,IF(UPPER(K19)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M19" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="15">
         <v>17</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" s="17">
+      <c r="B20" s="16"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="17" t="str">
         <f>IF(C20="","",IF(UPPER(C20)=UPPER('Race Results'!B4),10,IF(UPPER(C20)=UPPER('Race Results'!C4),6,IF(UPPER(C20)=UPPER('Race Results'!D4),4,IF(UPPER(C20)=UPPER('Race Results'!E4),3,IF(UPPER(C20)=UPPER('Race Results'!F4),2,IF(UPPER(C20)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="F20" s="17">
+        <v/>
+      </c>
+      <c r="E20" s="15"/>
+      <c r="F20" s="17" t="str">
         <f>IF(E20="","",IF(UPPER(E20)=UPPER('Race Results'!B5),10,IF(UPPER(E20)=UPPER('Race Results'!C5),6,IF(UPPER(E20)=UPPER('Race Results'!D5),4,IF(UPPER(E20)=UPPER('Race Results'!E5),3,IF(UPPER(E20)=UPPER('Race Results'!F5),2,IF(UPPER(E20)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="H20" s="17">
+        <v/>
+      </c>
+      <c r="G20" s="15"/>
+      <c r="H20" s="17" t="str">
         <f>IF(G20="","",IF(UPPER(G20)=UPPER('Race Results'!B6),10,IF(UPPER(G20)=UPPER('Race Results'!C6),6,IF(UPPER(G20)=UPPER('Race Results'!D6),4,IF(UPPER(G20)=UPPER('Race Results'!E6),3,IF(UPPER(G20)=UPPER('Race Results'!F6),2,IF(UPPER(G20)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="J20" s="17">
+        <v/>
+      </c>
+      <c r="I20" s="15"/>
+      <c r="J20" s="17" t="str">
         <f>IF(I20="","",IF(UPPER(I20)=UPPER('Race Results'!B7),10,IF(UPPER(I20)=UPPER('Race Results'!C7),6,IF(UPPER(I20)=UPPER('Race Results'!D7),4,IF(UPPER(I20)=UPPER('Race Results'!E7),3,IF(UPPER(I20)=UPPER('Race Results'!F7),2,IF(UPPER(I20)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="L20" s="17">
+        <v/>
+      </c>
+      <c r="K20" s="15"/>
+      <c r="L20" s="17" t="str">
         <f>IF(K20="","",IF(UPPER(K20)=UPPER('Race Results'!B8),10,IF(UPPER(K20)=UPPER('Race Results'!C8),6,IF(UPPER(K20)=UPPER('Race Results'!D8),4,IF(UPPER(K20)=UPPER('Race Results'!E8),3,IF(UPPER(K20)=UPPER('Race Results'!F8),2,IF(UPPER(K20)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M20" s="18">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>18</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D21" s="17">
+      <c r="B21" s="16"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="17" t="str">
         <f>IF(C21="","",IF(UPPER(C21)=UPPER('Race Results'!B4),10,IF(UPPER(C21)=UPPER('Race Results'!C4),6,IF(UPPER(C21)=UPPER('Race Results'!D4),4,IF(UPPER(C21)=UPPER('Race Results'!E4),3,IF(UPPER(C21)=UPPER('Race Results'!F4),2,IF(UPPER(C21)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F21" s="17">
+        <v/>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="17" t="str">
         <f>IF(E21="","",IF(UPPER(E21)=UPPER('Race Results'!B5),10,IF(UPPER(E21)=UPPER('Race Results'!C5),6,IF(UPPER(E21)=UPPER('Race Results'!D5),4,IF(UPPER(E21)=UPPER('Race Results'!E5),3,IF(UPPER(E21)=UPPER('Race Results'!F5),2,IF(UPPER(E21)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="H21" s="17">
+        <v/>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="17" t="str">
         <f>IF(G21="","",IF(UPPER(G21)=UPPER('Race Results'!B6),10,IF(UPPER(G21)=UPPER('Race Results'!C6),6,IF(UPPER(G21)=UPPER('Race Results'!D6),4,IF(UPPER(G21)=UPPER('Race Results'!E6),3,IF(UPPER(G21)=UPPER('Race Results'!F6),2,IF(UPPER(G21)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="J21" s="17">
+        <v/>
+      </c>
+      <c r="I21" s="4"/>
+      <c r="J21" s="17" t="str">
         <f>IF(I21="","",IF(UPPER(I21)=UPPER('Race Results'!B7),10,IF(UPPER(I21)=UPPER('Race Results'!C7),6,IF(UPPER(I21)=UPPER('Race Results'!D7),4,IF(UPPER(I21)=UPPER('Race Results'!E7),3,IF(UPPER(I21)=UPPER('Race Results'!F7),2,IF(UPPER(I21)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="L21" s="17">
+        <v/>
+      </c>
+      <c r="K21" s="4"/>
+      <c r="L21" s="17" t="str">
         <f>IF(K21="","",IF(UPPER(K21)=UPPER('Race Results'!B8),10,IF(UPPER(K21)=UPPER('Race Results'!C8),6,IF(UPPER(K21)=UPPER('Race Results'!D8),4,IF(UPPER(K21)=UPPER('Race Results'!E8),3,IF(UPPER(K21)=UPPER('Race Results'!F8),2,IF(UPPER(K21)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M21" s="18">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="15">
         <v>19</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="D22" s="17">
+      <c r="B22" s="16"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="17" t="str">
         <f>IF(C22="","",IF(UPPER(C22)=UPPER('Race Results'!B4),10,IF(UPPER(C22)=UPPER('Race Results'!C4),6,IF(UPPER(C22)=UPPER('Race Results'!D4),4,IF(UPPER(C22)=UPPER('Race Results'!E4),3,IF(UPPER(C22)=UPPER('Race Results'!F4),2,IF(UPPER(C22)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>4</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="F22" s="17">
+        <v/>
+      </c>
+      <c r="E22" s="15"/>
+      <c r="F22" s="17" t="str">
         <f>IF(E22="","",IF(UPPER(E22)=UPPER('Race Results'!B5),10,IF(UPPER(E22)=UPPER('Race Results'!C5),6,IF(UPPER(E22)=UPPER('Race Results'!D5),4,IF(UPPER(E22)=UPPER('Race Results'!E5),3,IF(UPPER(E22)=UPPER('Race Results'!F5),2,IF(UPPER(E22)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="H22" s="17">
+        <v/>
+      </c>
+      <c r="G22" s="15"/>
+      <c r="H22" s="17" t="str">
         <f>IF(G22="","",IF(UPPER(G22)=UPPER('Race Results'!B6),10,IF(UPPER(G22)=UPPER('Race Results'!C6),6,IF(UPPER(G22)=UPPER('Race Results'!D6),4,IF(UPPER(G22)=UPPER('Race Results'!E6),3,IF(UPPER(G22)=UPPER('Race Results'!F6),2,IF(UPPER(G22)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>3</v>
-      </c>
-      <c r="I22" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="J22" s="17">
+        <v/>
+      </c>
+      <c r="I22" s="15"/>
+      <c r="J22" s="17" t="str">
         <f>IF(I22="","",IF(UPPER(I22)=UPPER('Race Results'!B7),10,IF(UPPER(I22)=UPPER('Race Results'!C7),6,IF(UPPER(I22)=UPPER('Race Results'!D7),4,IF(UPPER(I22)=UPPER('Race Results'!E7),3,IF(UPPER(I22)=UPPER('Race Results'!F7),2,IF(UPPER(I22)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>3</v>
-      </c>
-      <c r="K22" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="L22" s="17">
+        <v/>
+      </c>
+      <c r="K22" s="15"/>
+      <c r="L22" s="17" t="str">
         <f>IF(K22="","",IF(UPPER(K22)=UPPER('Race Results'!B8),10,IF(UPPER(K22)=UPPER('Race Results'!C8),6,IF(UPPER(K22)=UPPER('Race Results'!D8),4,IF(UPPER(K22)=UPPER('Race Results'!E8),3,IF(UPPER(K22)=UPPER('Race Results'!F8),2,IF(UPPER(K22)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M22" s="18">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>20</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" s="17">
+      <c r="B23" s="5"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="17" t="str">
         <f>IF(C23="","",IF(UPPER(C23)=UPPER('Race Results'!B4),10,IF(UPPER(C23)=UPPER('Race Results'!C4),6,IF(UPPER(C23)=UPPER('Race Results'!D4),4,IF(UPPER(C23)=UPPER('Race Results'!E4),3,IF(UPPER(C23)=UPPER('Race Results'!F4),2,IF(UPPER(C23)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F23" s="17">
+        <v/>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="17" t="str">
         <f>IF(E23="","",IF(UPPER(E23)=UPPER('Race Results'!B5),10,IF(UPPER(E23)=UPPER('Race Results'!C5),6,IF(UPPER(E23)=UPPER('Race Results'!D5),4,IF(UPPER(E23)=UPPER('Race Results'!E5),3,IF(UPPER(E23)=UPPER('Race Results'!F5),2,IF(UPPER(E23)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="H23" s="17">
+        <v/>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="17" t="str">
         <f>IF(G23="","",IF(UPPER(G23)=UPPER('Race Results'!B6),10,IF(UPPER(G23)=UPPER('Race Results'!C6),6,IF(UPPER(G23)=UPPER('Race Results'!D6),4,IF(UPPER(G23)=UPPER('Race Results'!E6),3,IF(UPPER(G23)=UPPER('Race Results'!F6),2,IF(UPPER(G23)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>2</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="J23" s="17">
+        <v/>
+      </c>
+      <c r="I23" s="4"/>
+      <c r="J23" s="17" t="str">
         <f>IF(I23="","",IF(UPPER(I23)=UPPER('Race Results'!B7),10,IF(UPPER(I23)=UPPER('Race Results'!C7),6,IF(UPPER(I23)=UPPER('Race Results'!D7),4,IF(UPPER(I23)=UPPER('Race Results'!E7),3,IF(UPPER(I23)=UPPER('Race Results'!F7),2,IF(UPPER(I23)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>2</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="L23" s="17">
+        <v/>
+      </c>
+      <c r="K23" s="4"/>
+      <c r="L23" s="17" t="str">
         <f>IF(K23="","",IF(UPPER(K23)=UPPER('Race Results'!B8),10,IF(UPPER(K23)=UPPER('Race Results'!C8),6,IF(UPPER(K23)=UPPER('Race Results'!D8),4,IF(UPPER(K23)=UPPER('Race Results'!E8),3,IF(UPPER(K23)=UPPER('Race Results'!F8),2,IF(UPPER(K23)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M23" s="18">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="15">
         <v>21</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D24" s="17">
+      <c r="B24" s="16"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="17" t="str">
         <f>IF(C24="","",IF(UPPER(C24)=UPPER('Race Results'!B4),10,IF(UPPER(C24)=UPPER('Race Results'!C4),6,IF(UPPER(C24)=UPPER('Race Results'!D4),4,IF(UPPER(C24)=UPPER('Race Results'!E4),3,IF(UPPER(C24)=UPPER('Race Results'!F4),2,IF(UPPER(C24)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="F24" s="17">
+        <v/>
+      </c>
+      <c r="E24" s="15"/>
+      <c r="F24" s="17" t="str">
         <f>IF(E24="","",IF(UPPER(E24)=UPPER('Race Results'!B5),10,IF(UPPER(E24)=UPPER('Race Results'!C5),6,IF(UPPER(E24)=UPPER('Race Results'!D5),4,IF(UPPER(E24)=UPPER('Race Results'!E5),3,IF(UPPER(E24)=UPPER('Race Results'!F5),2,IF(UPPER(E24)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="H24" s="17">
+        <v/>
+      </c>
+      <c r="G24" s="15"/>
+      <c r="H24" s="17" t="str">
         <f>IF(G24="","",IF(UPPER(G24)=UPPER('Race Results'!B6),10,IF(UPPER(G24)=UPPER('Race Results'!C6),6,IF(UPPER(G24)=UPPER('Race Results'!D6),4,IF(UPPER(G24)=UPPER('Race Results'!E6),3,IF(UPPER(G24)=UPPER('Race Results'!F6),2,IF(UPPER(G24)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="J24" s="17">
+        <v/>
+      </c>
+      <c r="I24" s="15"/>
+      <c r="J24" s="17" t="str">
         <f>IF(I24="","",IF(UPPER(I24)=UPPER('Race Results'!B7),10,IF(UPPER(I24)=UPPER('Race Results'!C7),6,IF(UPPER(I24)=UPPER('Race Results'!D7),4,IF(UPPER(I24)=UPPER('Race Results'!E7),3,IF(UPPER(I24)=UPPER('Race Results'!F7),2,IF(UPPER(I24)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>4</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L24" s="17">
+        <v/>
+      </c>
+      <c r="K24" s="15"/>
+      <c r="L24" s="17" t="str">
         <f>IF(K24="","",IF(UPPER(K24)=UPPER('Race Results'!B8),10,IF(UPPER(K24)=UPPER('Race Results'!C8),6,IF(UPPER(K24)=UPPER('Race Results'!D8),4,IF(UPPER(K24)=UPPER('Race Results'!E8),3,IF(UPPER(K24)=UPPER('Race Results'!F8),2,IF(UPPER(K24)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M24" s="18">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>22</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" s="17">
+      <c r="B25" s="5"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="17" t="str">
         <f>IF(C25="","",IF(UPPER(C25)=UPPER('Race Results'!B4),10,IF(UPPER(C25)=UPPER('Race Results'!C4),6,IF(UPPER(C25)=UPPER('Race Results'!D4),4,IF(UPPER(C25)=UPPER('Race Results'!E4),3,IF(UPPER(C25)=UPPER('Race Results'!F4),2,IF(UPPER(C25)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>3</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F25" s="17">
+        <v/>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="17" t="str">
         <f>IF(E25="","",IF(UPPER(E25)=UPPER('Race Results'!B5),10,IF(UPPER(E25)=UPPER('Race Results'!C5),6,IF(UPPER(E25)=UPPER('Race Results'!D5),4,IF(UPPER(E25)=UPPER('Race Results'!E5),3,IF(UPPER(E25)=UPPER('Race Results'!F5),2,IF(UPPER(E25)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="H25" s="17">
+        <v/>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="17" t="str">
         <f>IF(G25="","",IF(UPPER(G25)=UPPER('Race Results'!B6),10,IF(UPPER(G25)=UPPER('Race Results'!C6),6,IF(UPPER(G25)=UPPER('Race Results'!D6),4,IF(UPPER(G25)=UPPER('Race Results'!E6),3,IF(UPPER(G25)=UPPER('Race Results'!F6),2,IF(UPPER(G25)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>4</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J25" s="17">
+        <v/>
+      </c>
+      <c r="I25" s="4"/>
+      <c r="J25" s="17" t="str">
         <f>IF(I25="","",IF(UPPER(I25)=UPPER('Race Results'!B7),10,IF(UPPER(I25)=UPPER('Race Results'!C7),6,IF(UPPER(I25)=UPPER('Race Results'!D7),4,IF(UPPER(I25)=UPPER('Race Results'!E7),3,IF(UPPER(I25)=UPPER('Race Results'!F7),2,IF(UPPER(I25)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="L25" s="17">
+        <v/>
+      </c>
+      <c r="K25" s="4"/>
+      <c r="L25" s="17" t="str">
         <f>IF(K25="","",IF(UPPER(K25)=UPPER('Race Results'!B8),10,IF(UPPER(K25)=UPPER('Race Results'!C8),6,IF(UPPER(K25)=UPPER('Race Results'!D8),4,IF(UPPER(K25)=UPPER('Race Results'!E8),3,IF(UPPER(K25)=UPPER('Race Results'!F8),2,IF(UPPER(K25)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M25" s="18">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="15">
         <v>23</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D26" s="17">
+      <c r="B26" s="16"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="17" t="str">
         <f>IF(C26="","",IF(UPPER(C26)=UPPER('Race Results'!B4),10,IF(UPPER(C26)=UPPER('Race Results'!C4),6,IF(UPPER(C26)=UPPER('Race Results'!D4),4,IF(UPPER(C26)=UPPER('Race Results'!E4),3,IF(UPPER(C26)=UPPER('Race Results'!F4),2,IF(UPPER(C26)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>2</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="F26" s="17">
+        <v/>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="17" t="str">
         <f>IF(E26="","",IF(UPPER(E26)=UPPER('Race Results'!B5),10,IF(UPPER(E26)=UPPER('Race Results'!C5),6,IF(UPPER(E26)=UPPER('Race Results'!D5),4,IF(UPPER(E26)=UPPER('Race Results'!E5),3,IF(UPPER(E26)=UPPER('Race Results'!F5),2,IF(UPPER(E26)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="G26" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="H26" s="17">
+        <v/>
+      </c>
+      <c r="G26" s="15"/>
+      <c r="H26" s="17" t="str">
         <f>IF(G26="","",IF(UPPER(G26)=UPPER('Race Results'!B6),10,IF(UPPER(G26)=UPPER('Race Results'!C6),6,IF(UPPER(G26)=UPPER('Race Results'!D6),4,IF(UPPER(G26)=UPPER('Race Results'!E6),3,IF(UPPER(G26)=UPPER('Race Results'!F6),2,IF(UPPER(G26)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="I26" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="J26" s="17">
+        <v/>
+      </c>
+      <c r="I26" s="15"/>
+      <c r="J26" s="17" t="str">
         <f>IF(I26="","",IF(UPPER(I26)=UPPER('Race Results'!B7),10,IF(UPPER(I26)=UPPER('Race Results'!C7),6,IF(UPPER(I26)=UPPER('Race Results'!D7),4,IF(UPPER(I26)=UPPER('Race Results'!E7),3,IF(UPPER(I26)=UPPER('Race Results'!F7),2,IF(UPPER(I26)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>1</v>
-      </c>
-      <c r="K26" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="L26" s="17">
+        <v/>
+      </c>
+      <c r="K26" s="15"/>
+      <c r="L26" s="17" t="str">
         <f>IF(K26="","",IF(UPPER(K26)=UPPER('Race Results'!B8),10,IF(UPPER(K26)=UPPER('Race Results'!C8),6,IF(UPPER(K26)=UPPER('Race Results'!D8),4,IF(UPPER(K26)=UPPER('Race Results'!E8),3,IF(UPPER(K26)=UPPER('Race Results'!F8),2,IF(UPPER(K26)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M26" s="18">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>24</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" s="17">
+      <c r="B27" s="5"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="17" t="str">
         <f>IF(C27="","",IF(UPPER(C27)=UPPER('Race Results'!B4),10,IF(UPPER(C27)=UPPER('Race Results'!C4),6,IF(UPPER(C27)=UPPER('Race Results'!D4),4,IF(UPPER(C27)=UPPER('Race Results'!E4),3,IF(UPPER(C27)=UPPER('Race Results'!F4),2,IF(UPPER(C27)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F27" s="17">
+        <v/>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="17" t="str">
         <f>IF(E27="","",IF(UPPER(E27)=UPPER('Race Results'!B5),10,IF(UPPER(E27)=UPPER('Race Results'!C5),6,IF(UPPER(E27)=UPPER('Race Results'!D5),4,IF(UPPER(E27)=UPPER('Race Results'!E5),3,IF(UPPER(E27)=UPPER('Race Results'!F5),2,IF(UPPER(E27)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="H27" s="17">
+        <v/>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="17" t="str">
         <f>IF(G27="","",IF(UPPER(G27)=UPPER('Race Results'!B6),10,IF(UPPER(G27)=UPPER('Race Results'!C6),6,IF(UPPER(G27)=UPPER('Race Results'!D6),4,IF(UPPER(G27)=UPPER('Race Results'!E6),3,IF(UPPER(G27)=UPPER('Race Results'!F6),2,IF(UPPER(G27)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>3</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="J27" s="17">
+        <v/>
+      </c>
+      <c r="I27" s="4"/>
+      <c r="J27" s="17" t="str">
         <f>IF(I27="","",IF(UPPER(I27)=UPPER('Race Results'!B7),10,IF(UPPER(I27)=UPPER('Race Results'!C7),6,IF(UPPER(I27)=UPPER('Race Results'!D7),4,IF(UPPER(I27)=UPPER('Race Results'!E7),3,IF(UPPER(I27)=UPPER('Race Results'!F7),2,IF(UPPER(I27)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="L27" s="17">
+        <v/>
+      </c>
+      <c r="K27" s="4"/>
+      <c r="L27" s="17" t="str">
         <f>IF(K27="","",IF(UPPER(K27)=UPPER('Race Results'!B8),10,IF(UPPER(K27)=UPPER('Race Results'!C8),6,IF(UPPER(K27)=UPPER('Race Results'!D8),4,IF(UPPER(K27)=UPPER('Race Results'!E8),3,IF(UPPER(K27)=UPPER('Race Results'!F8),2,IF(UPPER(K27)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M27" s="18">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="15">
         <v>25</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" s="17">
+      <c r="B28" s="16"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="17" t="str">
         <f>IF(C28="","",IF(UPPER(C28)=UPPER('Race Results'!B4),10,IF(UPPER(C28)=UPPER('Race Results'!C4),6,IF(UPPER(C28)=UPPER('Race Results'!D4),4,IF(UPPER(C28)=UPPER('Race Results'!E4),3,IF(UPPER(C28)=UPPER('Race Results'!F4),2,IF(UPPER(C28)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="F28" s="17">
+        <v/>
+      </c>
+      <c r="E28" s="15"/>
+      <c r="F28" s="17" t="str">
         <f>IF(E28="","",IF(UPPER(E28)=UPPER('Race Results'!B5),10,IF(UPPER(E28)=UPPER('Race Results'!C5),6,IF(UPPER(E28)=UPPER('Race Results'!D5),4,IF(UPPER(E28)=UPPER('Race Results'!E5),3,IF(UPPER(E28)=UPPER('Race Results'!F5),2,IF(UPPER(E28)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="H28" s="17">
+        <v/>
+      </c>
+      <c r="G28" s="15"/>
+      <c r="H28" s="17" t="str">
         <f>IF(G28="","",IF(UPPER(G28)=UPPER('Race Results'!B6),10,IF(UPPER(G28)=UPPER('Race Results'!C6),6,IF(UPPER(G28)=UPPER('Race Results'!D6),4,IF(UPPER(G28)=UPPER('Race Results'!E6),3,IF(UPPER(G28)=UPPER('Race Results'!F6),2,IF(UPPER(G28)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="I28" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="J28" s="17">
+        <v/>
+      </c>
+      <c r="I28" s="15"/>
+      <c r="J28" s="17" t="str">
         <f>IF(I28="","",IF(UPPER(I28)=UPPER('Race Results'!B7),10,IF(UPPER(I28)=UPPER('Race Results'!C7),6,IF(UPPER(I28)=UPPER('Race Results'!D7),4,IF(UPPER(I28)=UPPER('Race Results'!E7),3,IF(UPPER(I28)=UPPER('Race Results'!F7),2,IF(UPPER(I28)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="L28" s="17">
+        <v/>
+      </c>
+      <c r="K28" s="15"/>
+      <c r="L28" s="17" t="str">
         <f>IF(K28="","",IF(UPPER(K28)=UPPER('Race Results'!B8),10,IF(UPPER(K28)=UPPER('Race Results'!C8),6,IF(UPPER(K28)=UPPER('Race Results'!D8),4,IF(UPPER(K28)=UPPER('Race Results'!E8),3,IF(UPPER(K28)=UPPER('Race Results'!F8),2,IF(UPPER(K28)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M28" s="18">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>26</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D29" s="17">
+      <c r="B29" s="5"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="17" t="str">
         <f>IF(C29="","",IF(UPPER(C29)=UPPER('Race Results'!B4),10,IF(UPPER(C29)=UPPER('Race Results'!C4),6,IF(UPPER(C29)=UPPER('Race Results'!D4),4,IF(UPPER(C29)=UPPER('Race Results'!E4),3,IF(UPPER(C29)=UPPER('Race Results'!F4),2,IF(UPPER(C29)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F29" s="17">
+        <v/>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="17" t="str">
         <f>IF(E29="","",IF(UPPER(E29)=UPPER('Race Results'!B5),10,IF(UPPER(E29)=UPPER('Race Results'!C5),6,IF(UPPER(E29)=UPPER('Race Results'!D5),4,IF(UPPER(E29)=UPPER('Race Results'!E5),3,IF(UPPER(E29)=UPPER('Race Results'!F5),2,IF(UPPER(E29)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="H29" s="17">
+        <v/>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="17" t="str">
         <f>IF(G29="","",IF(UPPER(G29)=UPPER('Race Results'!B6),10,IF(UPPER(G29)=UPPER('Race Results'!C6),6,IF(UPPER(G29)=UPPER('Race Results'!D6),4,IF(UPPER(G29)=UPPER('Race Results'!E6),3,IF(UPPER(G29)=UPPER('Race Results'!F6),2,IF(UPPER(G29)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>2</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="J29" s="17">
+        <v/>
+      </c>
+      <c r="I29" s="4"/>
+      <c r="J29" s="17" t="str">
         <f>IF(I29="","",IF(UPPER(I29)=UPPER('Race Results'!B7),10,IF(UPPER(I29)=UPPER('Race Results'!C7),6,IF(UPPER(I29)=UPPER('Race Results'!D7),4,IF(UPPER(I29)=UPPER('Race Results'!E7),3,IF(UPPER(I29)=UPPER('Race Results'!F7),2,IF(UPPER(I29)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="L29" s="17">
+        <v/>
+      </c>
+      <c r="K29" s="4"/>
+      <c r="L29" s="17" t="str">
         <f>IF(K29="","",IF(UPPER(K29)=UPPER('Race Results'!B8),10,IF(UPPER(K29)=UPPER('Race Results'!C8),6,IF(UPPER(K29)=UPPER('Race Results'!D8),4,IF(UPPER(K29)=UPPER('Race Results'!E8),3,IF(UPPER(K29)=UPPER('Race Results'!F8),2,IF(UPPER(K29)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M29" s="18">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="15">
         <v>27</v>
       </c>
-      <c r="B30" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D30" s="17">
+      <c r="B30" s="16"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="17" t="str">
         <f>IF(C30="","",IF(UPPER(C30)=UPPER('Race Results'!B4),10,IF(UPPER(C30)=UPPER('Race Results'!C4),6,IF(UPPER(C30)=UPPER('Race Results'!D4),4,IF(UPPER(C30)=UPPER('Race Results'!E4),3,IF(UPPER(C30)=UPPER('Race Results'!F4),2,IF(UPPER(C30)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>6</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="F30" s="17">
+        <v/>
+      </c>
+      <c r="E30" s="15"/>
+      <c r="F30" s="17" t="str">
         <f>IF(E30="","",IF(UPPER(E30)=UPPER('Race Results'!B5),10,IF(UPPER(E30)=UPPER('Race Results'!C5),6,IF(UPPER(E30)=UPPER('Race Results'!D5),4,IF(UPPER(E30)=UPPER('Race Results'!E5),3,IF(UPPER(E30)=UPPER('Race Results'!F5),2,IF(UPPER(E30)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
-      </c>
-      <c r="G30" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="H30" s="17">
+        <v/>
+      </c>
+      <c r="G30" s="15"/>
+      <c r="H30" s="17" t="str">
         <f>IF(G30="","",IF(UPPER(G30)=UPPER('Race Results'!B6),10,IF(UPPER(G30)=UPPER('Race Results'!C6),6,IF(UPPER(G30)=UPPER('Race Results'!D6),4,IF(UPPER(G30)=UPPER('Race Results'!E6),3,IF(UPPER(G30)=UPPER('Race Results'!F6),2,IF(UPPER(G30)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>1</v>
-      </c>
-      <c r="I30" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="J30" s="17">
+        <v/>
+      </c>
+      <c r="I30" s="15"/>
+      <c r="J30" s="17" t="str">
         <f>IF(I30="","",IF(UPPER(I30)=UPPER('Race Results'!B7),10,IF(UPPER(I30)=UPPER('Race Results'!C7),6,IF(UPPER(I30)=UPPER('Race Results'!D7),4,IF(UPPER(I30)=UPPER('Race Results'!E7),3,IF(UPPER(I30)=UPPER('Race Results'!F7),2,IF(UPPER(I30)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>3</v>
-      </c>
-      <c r="K30" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L30" s="17">
+        <v/>
+      </c>
+      <c r="K30" s="15"/>
+      <c r="L30" s="17" t="str">
         <f>IF(K30="","",IF(UPPER(K30)=UPPER('Race Results'!B8),10,IF(UPPER(K30)=UPPER('Race Results'!C8),6,IF(UPPER(K30)=UPPER('Race Results'!D8),4,IF(UPPER(K30)=UPPER('Race Results'!E8),3,IF(UPPER(K30)=UPPER('Race Results'!F8),2,IF(UPPER(K30)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M30" s="18">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -4032,336 +3625,336 @@
       <c r="A3" s="19">
         <v>1</v>
       </c>
-      <c r="B3" s="20" t="str">
+      <c r="B3" s="20">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,1),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Emily Sardo</v>
+        <v>0</v>
       </c>
       <c r="C3" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,1),"")</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D3" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C3,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="19">
         <v>2</v>
       </c>
-      <c r="B4" s="20" t="str">
+      <c r="B4" s="20">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>0</v>
       </c>
       <c r="C4" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),"")</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D4" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C4,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="19">
         <v>3</v>
       </c>
-      <c r="B5" s="20" t="str">
+      <c r="B5" s="20">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,3),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Marianne Chardon</v>
+        <v>0</v>
       </c>
       <c r="C5" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,3),"")</f>
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D5" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C5,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="23">
         <v>4</v>
       </c>
-      <c r="B6" s="24" t="str">
+      <c r="B6" s="24">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,4),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Mick Hogg</v>
+        <v>0</v>
       </c>
       <c r="C6" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,4),"")</f>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D6" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C6,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="27">
         <v>5</v>
       </c>
-      <c r="B7" s="28" t="str">
+      <c r="B7" s="28">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,5),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Steve Burfitt</v>
+        <v>0</v>
       </c>
       <c r="C7" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,5),"")</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D7" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C7,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="23">
         <v>6</v>
       </c>
-      <c r="B8" s="24" t="str">
+      <c r="B8" s="24">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,6),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Sean Horan</v>
+        <v>0</v>
       </c>
       <c r="C8" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,6),"")</f>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D8" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C8,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="27">
         <v>7</v>
       </c>
-      <c r="B9" s="28" t="str">
+      <c r="B9" s="28">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,7),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Anthony Burke</v>
+        <v>0</v>
       </c>
       <c r="C9" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,7),"")</f>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D9" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C9,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="23">
         <v>8</v>
       </c>
-      <c r="B10" s="24" t="str">
+      <c r="B10" s="24">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,8),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Anthony Burke</v>
+        <v>0</v>
       </c>
       <c r="C10" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,8),"")</f>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D10" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C10,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="27">
         <v>9</v>
       </c>
-      <c r="B11" s="28" t="str">
+      <c r="B11" s="28">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,9),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Gemma Forsyth</v>
+        <v>0</v>
       </c>
       <c r="C11" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,9),"")</f>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D11" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C11,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="23">
         <v>10</v>
       </c>
-      <c r="B12" s="24" t="str">
+      <c r="B12" s="24">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,10),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Vahi Crowley</v>
+        <v>0</v>
       </c>
       <c r="C12" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,10),"")</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D12" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C12,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="27">
         <v>11</v>
       </c>
-      <c r="B13" s="28" t="str">
+      <c r="B13" s="28">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,11),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Vahi Crowley</v>
+        <v>0</v>
       </c>
       <c r="C13" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,11),"")</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D13" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C13,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="23">
         <v>12</v>
       </c>
-      <c r="B14" s="24" t="str">
+      <c r="B14" s="24">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,12),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Vahi Crowley</v>
+        <v>0</v>
       </c>
       <c r="C14" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,12),"")</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D14" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C14,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="27">
         <v>13</v>
       </c>
-      <c r="B15" s="28" t="str">
+      <c r="B15" s="28">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,13),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Stephen Hughes</v>
+        <v>0</v>
       </c>
       <c r="C15" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,13),"")</f>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D15" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C15,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="23">
         <v>14</v>
       </c>
-      <c r="B16" s="24" t="str">
+      <c r="B16" s="24">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,14),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Bryan White</v>
+        <v>0</v>
       </c>
       <c r="C16" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,14),"")</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D16" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C16,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="27">
         <v>15</v>
       </c>
-      <c r="B17" s="28" t="str">
+      <c r="B17" s="28">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,15),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Bryan White</v>
+        <v>0</v>
       </c>
       <c r="C17" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,15),"")</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D17" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C17,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="23">
         <v>16</v>
       </c>
-      <c r="B18" s="24" t="str">
+      <c r="B18" s="24">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,16),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ryan Crowley</v>
+        <v>0</v>
       </c>
       <c r="C18" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,16),"")</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D18" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C18,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A19" s="27">
         <v>17</v>
       </c>
-      <c r="B19" s="28" t="str">
+      <c r="B19" s="28">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,17),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ryan Crowley</v>
+        <v>0</v>
       </c>
       <c r="C19" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,17),"")</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D19" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C19,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A20" s="23">
         <v>18</v>
       </c>
-      <c r="B20" s="24" t="str">
+      <c r="B20" s="24">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,18),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ryan Crowley</v>
+        <v>0</v>
       </c>
       <c r="C20" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,18),"")</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D20" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C20,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A21" s="27">
         <v>19</v>
       </c>
-      <c r="B21" s="28" t="str">
+      <c r="B21" s="28">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,19),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ryan Crowley</v>
+        <v>0</v>
       </c>
       <c r="C21" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,19),"")</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D21" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C21,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A22" s="23">
         <v>20</v>
       </c>
-      <c r="B22" s="24" t="str">
+      <c r="B22" s="24">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,20),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Liam Bridgeman</v>
+        <v>0</v>
       </c>
       <c r="C22" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,20),"")</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D22" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C22,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4372,13 +3965,13 @@
       <c r="A23" s="27">
         <v>21</v>
       </c>
-      <c r="B23" s="28" t="str">
+      <c r="B23" s="28">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,21),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ronan Keohane</v>
+        <v>0</v>
       </c>
       <c r="C23" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,21),"")</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D23" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C23,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4389,64 +3982,64 @@
       <c r="A24" s="23">
         <v>22</v>
       </c>
-      <c r="B24" s="24" t="str">
+      <c r="B24" s="24">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,22),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Lynn Forsyth</v>
+        <v>0</v>
       </c>
       <c r="C24" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,22),"")</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D24" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C24,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A25" s="27">
         <v>23</v>
       </c>
-      <c r="B25" s="28" t="str">
+      <c r="B25" s="28">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,23),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Lynn Forsyth</v>
+        <v>0</v>
       </c>
       <c r="C25" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,23),"")</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D25" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C25,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A26" s="23">
         <v>24</v>
       </c>
-      <c r="B26" s="24" t="str">
+      <c r="B26" s="24">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,24),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Lynn Forsyth</v>
+        <v>0</v>
       </c>
       <c r="C26" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,24),"")</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D26" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C26,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A27" s="27">
         <v>25</v>
       </c>
-      <c r="B27" s="28" t="str">
+      <c r="B27" s="28">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,25),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Steve Hunt</v>
+        <v>0</v>
       </c>
       <c r="C27" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,25),"")</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D27" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C27,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4457,13 +4050,13 @@
       <c r="A28" s="23">
         <v>26</v>
       </c>
-      <c r="B28" s="24" t="str">
+      <c r="B28" s="24">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,26),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Denise White</v>
+        <v>0</v>
       </c>
       <c r="C28" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,26),"")</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D28" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C28,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
@@ -4474,13 +4067,13 @@
       <c r="A29" s="27">
         <v>27</v>
       </c>
-      <c r="B29" s="28" t="str">
+      <c r="B29" s="28">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,27),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Denise White</v>
+        <v>0</v>
       </c>
       <c r="C29" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,27),"")</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D29" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C29,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="381" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41923381-1E13-455E-A6BA-A2C27A04891D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest List" sheetId="1" r:id="rId1"/>
@@ -903,20 +903,20 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1218,16 +1218,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="36"/>
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37"/>
+      <c r="B2" s="34"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1612,24 +1612,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
     </row>
     <row r="3" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -2177,26 +2177,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
     </row>
     <row r="3" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
@@ -2286,15 +2286,15 @@
       <c r="G9" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2391,38 +2391,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
     </row>
     <row r="3" spans="1:13" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -4152,14 +4152,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
     </row>
     <row r="3" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A3" s="40" t="s">

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="381" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41923381-1E13-455E-A6BA-A2C27A04891D}"/>
+  <xr:revisionPtr revIDLastSave="400" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B545749-5358-44F6-865E-BA55FE9338A6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest List" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="183">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -903,13 +903,14 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -920,7 +921,6 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1218,16 +1218,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="33"/>
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="34"/>
+      <c r="B2" s="36"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1612,24 +1612,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -2177,26 +2177,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
     </row>
     <row r="3" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
@@ -2225,7 +2225,9 @@
       <c r="A4" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -2236,7 +2238,9 @@
       <c r="A5" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>111</v>
+      </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -2247,7 +2251,9 @@
       <c r="A6" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="4"/>
+      <c r="B6" s="4" t="s">
+        <v>130</v>
+      </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -2258,8 +2264,12 @@
       <c r="A7" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
+      <c r="B7" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -2269,7 +2279,9 @@
       <c r="A8" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -2286,15 +2298,15 @@
       <c r="G9" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2391,38 +2403,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
     </row>
     <row r="3" spans="1:13" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -2924,26 +2936,34 @@
       <c r="A17" s="4">
         <v>14</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="17" t="str">
+      <c r="B17" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="17">
         <f>IF(C17="","",IF(UPPER(C17)=UPPER('Race Results'!B4),10,IF(UPPER(C17)=UPPER('Race Results'!C4),6,IF(UPPER(C17)=UPPER('Race Results'!D4),4,IF(UPPER(C17)=UPPER('Race Results'!E4),3,IF(UPPER(C17)=UPPER('Race Results'!F4),2,IF(UPPER(C17)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="17" t="str">
         <f>IF(E17="","",IF(UPPER(E17)=UPPER('Race Results'!B5),10,IF(UPPER(E17)=UPPER('Race Results'!C5),6,IF(UPPER(E17)=UPPER('Race Results'!D5),4,IF(UPPER(E17)=UPPER('Race Results'!E5),3,IF(UPPER(E17)=UPPER('Race Results'!F5),2,IF(UPPER(E17)=UPPER('Race Results'!G5),1,0)))))))</f>
         <v/>
       </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="17" t="str">
+      <c r="G17" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="H17" s="17">
         <f>IF(G17="","",IF(UPPER(G17)=UPPER('Race Results'!B6),10,IF(UPPER(G17)=UPPER('Race Results'!C6),6,IF(UPPER(G17)=UPPER('Race Results'!D6),4,IF(UPPER(G17)=UPPER('Race Results'!E6),3,IF(UPPER(G17)=UPPER('Race Results'!F6),2,IF(UPPER(G17)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="17" t="str">
+        <v>10</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J17" s="17">
         <f>IF(I17="","",IF(UPPER(I17)=UPPER('Race Results'!B7),10,IF(UPPER(I17)=UPPER('Race Results'!C7),6,IF(UPPER(I17)=UPPER('Race Results'!D7),4,IF(UPPER(I17)=UPPER('Race Results'!E7),3,IF(UPPER(I17)=UPPER('Race Results'!F7),2,IF(UPPER(I17)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="17" t="str">
@@ -2952,23 +2972,27 @@
       </c>
       <c r="M17" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="15">
         <v>15</v>
       </c>
-      <c r="B18" s="16"/>
+      <c r="B18" s="16" t="s">
+        <v>79</v>
+      </c>
       <c r="C18" s="15"/>
       <c r="D18" s="17" t="str">
         <f>IF(C18="","",IF(UPPER(C18)=UPPER('Race Results'!B4),10,IF(UPPER(C18)=UPPER('Race Results'!C4),6,IF(UPPER(C18)=UPPER('Race Results'!D4),4,IF(UPPER(C18)=UPPER('Race Results'!E4),3,IF(UPPER(C18)=UPPER('Race Results'!F4),2,IF(UPPER(C18)=UPPER('Race Results'!G4),1,0)))))))</f>
         <v/>
       </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="17" t="str">
+      <c r="E18" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="17">
         <f>IF(E18="","",IF(UPPER(E18)=UPPER('Race Results'!B5),10,IF(UPPER(E18)=UPPER('Race Results'!C5),6,IF(UPPER(E18)=UPPER('Race Results'!D5),4,IF(UPPER(E18)=UPPER('Race Results'!E5),3,IF(UPPER(E18)=UPPER('Race Results'!F5),2,IF(UPPER(E18)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="17" t="str">
@@ -2980,21 +3004,25 @@
         <f>IF(I18="","",IF(UPPER(I18)=UPPER('Race Results'!B7),10,IF(UPPER(I18)=UPPER('Race Results'!C7),6,IF(UPPER(I18)=UPPER('Race Results'!D7),4,IF(UPPER(I18)=UPPER('Race Results'!E7),3,IF(UPPER(I18)=UPPER('Race Results'!F7),2,IF(UPPER(I18)=UPPER('Race Results'!G7),1,0)))))))</f>
         <v/>
       </c>
-      <c r="K18" s="15"/>
-      <c r="L18" s="17" t="str">
+      <c r="K18" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="L18" s="17">
         <f>IF(K18="","",IF(UPPER(K18)=UPPER('Race Results'!B8),10,IF(UPPER(K18)=UPPER('Race Results'!C8),6,IF(UPPER(K18)=UPPER('Race Results'!D8),4,IF(UPPER(K18)=UPPER('Race Results'!E8),3,IF(UPPER(K18)=UPPER('Race Results'!F8),2,IF(UPPER(K18)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="M18" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>16</v>
       </c>
-      <c r="B19" s="5"/>
+      <c r="B19" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="C19" s="4"/>
       <c r="D19" s="17" t="str">
         <f>IF(C19="","",IF(UPPER(C19)=UPPER('Race Results'!B4),10,IF(UPPER(C19)=UPPER('Race Results'!C4),6,IF(UPPER(C19)=UPPER('Race Results'!D4),4,IF(UPPER(C19)=UPPER('Race Results'!E4),3,IF(UPPER(C19)=UPPER('Race Results'!F4),2,IF(UPPER(C19)=UPPER('Race Results'!G4),1,0)))))))</f>
@@ -3029,7 +3057,9 @@
       <c r="A20" s="15">
         <v>17</v>
       </c>
-      <c r="B20" s="16"/>
+      <c r="B20" s="16" t="s">
+        <v>88</v>
+      </c>
       <c r="C20" s="15"/>
       <c r="D20" s="17" t="str">
         <f>IF(C20="","",IF(UPPER(C20)=UPPER('Race Results'!B4),10,IF(UPPER(C20)=UPPER('Race Results'!C4),6,IF(UPPER(C20)=UPPER('Race Results'!D4),4,IF(UPPER(C20)=UPPER('Race Results'!E4),3,IF(UPPER(C20)=UPPER('Race Results'!F4),2,IF(UPPER(C20)=UPPER('Race Results'!G4),1,0)))))))</f>
@@ -3600,12 +3630,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -3625,34 +3655,34 @@
       <c r="A3" s="19">
         <v>1</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,1),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Ryan Crowley</v>
       </c>
       <c r="C3" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,1),"")</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D3" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C3,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="19">
         <v>2</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+        <v>Emily Sardo</v>
       </c>
       <c r="C4" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),"")</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D4" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C4,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4152,24 +4182,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="3" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="31" t="s">
@@ -4187,14 +4217,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="31" t="s">
@@ -4232,14 +4262,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="31" t="s">
@@ -4282,14 +4312,14 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A27" s="40" t="s">
+      <c r="A27" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="31" t="s">

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="400" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B545749-5358-44F6-865E-BA55FE9338A6}"/>
+  <xr:revisionPtr revIDLastSave="411" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B81F3B41-D214-4D02-8CCA-8B5DE18ADF8F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest List" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="183">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -906,7 +906,10 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -914,13 +917,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1218,16 +1218,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35"/>
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1622,14 +1622,14 @@
       <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -2188,15 +2188,15 @@
       <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
     </row>
     <row r="3" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
@@ -2225,9 +2225,7 @@
       <c r="A4" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>96</v>
-      </c>
+      <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -2238,9 +2236,7 @@
       <c r="A5" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>111</v>
-      </c>
+      <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -2251,9 +2247,7 @@
       <c r="A6" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>130</v>
-      </c>
+      <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -2264,12 +2258,8 @@
       <c r="A7" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>143</v>
-      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -2279,9 +2269,7 @@
       <c r="A8" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>153</v>
-      </c>
+      <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -2298,15 +2286,15 @@
       <c r="G9" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2420,21 +2408,21 @@
       <c r="M1" s="33"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
     </row>
     <row r="3" spans="1:13" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -2939,31 +2927,25 @@
       <c r="B17" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" s="17">
+      <c r="C17" s="4"/>
+      <c r="D17" s="17" t="str">
         <f>IF(C17="","",IF(UPPER(C17)=UPPER('Race Results'!B4),10,IF(UPPER(C17)=UPPER('Race Results'!C4),6,IF(UPPER(C17)=UPPER('Race Results'!D4),4,IF(UPPER(C17)=UPPER('Race Results'!E4),3,IF(UPPER(C17)=UPPER('Race Results'!F4),2,IF(UPPER(C17)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="17" t="str">
         <f>IF(E17="","",IF(UPPER(E17)=UPPER('Race Results'!B5),10,IF(UPPER(E17)=UPPER('Race Results'!C5),6,IF(UPPER(E17)=UPPER('Race Results'!D5),4,IF(UPPER(E17)=UPPER('Race Results'!E5),3,IF(UPPER(E17)=UPPER('Race Results'!F5),2,IF(UPPER(E17)=UPPER('Race Results'!G5),1,0)))))))</f>
         <v/>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="H17" s="17">
+      <c r="G17" s="4"/>
+      <c r="H17" s="17" t="str">
         <f>IF(G17="","",IF(UPPER(G17)=UPPER('Race Results'!B6),10,IF(UPPER(G17)=UPPER('Race Results'!C6),6,IF(UPPER(G17)=UPPER('Race Results'!D6),4,IF(UPPER(G17)=UPPER('Race Results'!E6),3,IF(UPPER(G17)=UPPER('Race Results'!F6),2,IF(UPPER(G17)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>10</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="J17" s="17">
+        <v/>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="17" t="str">
         <f>IF(I17="","",IF(UPPER(I17)=UPPER('Race Results'!B7),10,IF(UPPER(I17)=UPPER('Race Results'!C7),6,IF(UPPER(I17)=UPPER('Race Results'!D7),4,IF(UPPER(I17)=UPPER('Race Results'!E7),3,IF(UPPER(I17)=UPPER('Race Results'!F7),2,IF(UPPER(I17)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="17" t="str">
@@ -2972,7 +2954,7 @@
       </c>
       <c r="M17" s="18">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2987,12 +2969,10 @@
         <f>IF(C18="","",IF(UPPER(C18)=UPPER('Race Results'!B4),10,IF(UPPER(C18)=UPPER('Race Results'!C4),6,IF(UPPER(C18)=UPPER('Race Results'!D4),4,IF(UPPER(C18)=UPPER('Race Results'!E4),3,IF(UPPER(C18)=UPPER('Race Results'!F4),2,IF(UPPER(C18)=UPPER('Race Results'!G4),1,0)))))))</f>
         <v/>
       </c>
-      <c r="E18" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" s="17">
+      <c r="E18" s="15"/>
+      <c r="F18" s="17" t="str">
         <f>IF(E18="","",IF(UPPER(E18)=UPPER('Race Results'!B5),10,IF(UPPER(E18)=UPPER('Race Results'!C5),6,IF(UPPER(E18)=UPPER('Race Results'!D5),4,IF(UPPER(E18)=UPPER('Race Results'!E5),3,IF(UPPER(E18)=UPPER('Race Results'!F5),2,IF(UPPER(E18)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="17" t="str">
@@ -3004,16 +2984,14 @@
         <f>IF(I18="","",IF(UPPER(I18)=UPPER('Race Results'!B7),10,IF(UPPER(I18)=UPPER('Race Results'!C7),6,IF(UPPER(I18)=UPPER('Race Results'!D7),4,IF(UPPER(I18)=UPPER('Race Results'!E7),3,IF(UPPER(I18)=UPPER('Race Results'!F7),2,IF(UPPER(I18)=UPPER('Race Results'!G7),1,0)))))))</f>
         <v/>
       </c>
-      <c r="K18" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="L18" s="17">
+      <c r="K18" s="15"/>
+      <c r="L18" s="17" t="str">
         <f>IF(K18="","",IF(UPPER(K18)=UPPER('Race Results'!B8),10,IF(UPPER(K18)=UPPER('Race Results'!C8),6,IF(UPPER(K18)=UPPER('Race Results'!D8),4,IF(UPPER(K18)=UPPER('Race Results'!E8),3,IF(UPPER(K18)=UPPER('Race Results'!F8),2,IF(UPPER(K18)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="M18" s="18">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3630,12 +3608,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -3655,34 +3633,34 @@
       <c r="A3" s="19">
         <v>1</v>
       </c>
-      <c r="B3" s="20" t="str">
+      <c r="B3" s="20">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,1),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Ryan Crowley</v>
+        <v>0</v>
       </c>
       <c r="C3" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,1),"")</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D3" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C3,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="19">
         <v>2</v>
       </c>
-      <c r="B4" s="20" t="str">
+      <c r="B4" s="20">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>Emily Sardo</v>
+        <v>0</v>
       </c>
       <c r="C4" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),"")</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D4" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C4,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4192,14 +4170,14 @@
       <c r="F1" s="33"/>
     </row>
     <row r="3" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="31" t="s">
@@ -4217,14 +4195,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="31" t="s">
@@ -4262,14 +4240,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="31" t="s">
@@ -4312,14 +4290,14 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A27" s="34" t="s">
+      <c r="A27" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="31" t="s">

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="411" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B81F3B41-D214-4D02-8CCA-8B5DE18ADF8F}"/>
+  <xr:revisionPtr revIDLastSave="564" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DE502F1-73DA-4C34-BB7E-E5F0D80C7C4D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="183">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -909,7 +909,6 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -917,6 +916,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1004,6 +1004,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1218,16 +1222,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="36"/>
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37"/>
+      <c r="B2" s="36"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1622,14 +1626,14 @@
       <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -2225,9 +2229,15 @@
       <c r="A4" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>108</v>
+      </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -2286,15 +2296,15 @@
       <c r="G9" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2372,7 +2382,7 @@
   <sheetPr>
     <tabColor rgb="FFC9A84C"/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -2469,101 +2479,137 @@
       <c r="A4" s="15">
         <v>1</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="17" t="str">
+      <c r="B4" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="17">
         <f>IF(C4="","",IF(UPPER(C4)=UPPER('Race Results'!B4),10,IF(UPPER(C4)=UPPER('Race Results'!C4),6,IF(UPPER(C4)=UPPER('Race Results'!D4),4,IF(UPPER(C4)=UPPER('Race Results'!E4),3,IF(UPPER(C4)=UPPER('Race Results'!F4),2,IF(UPPER(C4)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="17">
         <f>IF(E4="","",IF(UPPER(E4)=UPPER('Race Results'!B5),10,IF(UPPER(E4)=UPPER('Race Results'!C5),6,IF(UPPER(E4)=UPPER('Race Results'!D5),4,IF(UPPER(E4)=UPPER('Race Results'!E5),3,IF(UPPER(E4)=UPPER('Race Results'!F5),2,IF(UPPER(E4)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H4" s="17">
         <f>IF(G4="","",IF(UPPER(G4)=UPPER('Race Results'!B6),10,IF(UPPER(G4)=UPPER('Race Results'!C6),6,IF(UPPER(G4)=UPPER('Race Results'!D6),4,IF(UPPER(G4)=UPPER('Race Results'!E6),3,IF(UPPER(G4)=UPPER('Race Results'!F6),2,IF(UPPER(G4)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I4" s="15"/>
-      <c r="J4" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="J4" s="17">
         <f>IF(I4="","",IF(UPPER(I4)=UPPER('Race Results'!B7),10,IF(UPPER(I4)=UPPER('Race Results'!C7),6,IF(UPPER(I4)=UPPER('Race Results'!D7),4,IF(UPPER(I4)=UPPER('Race Results'!E7),3,IF(UPPER(I4)=UPPER('Race Results'!F7),2,IF(UPPER(I4)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K4" s="15"/>
-      <c r="L4" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="L4" s="17">
         <f>IF(K4="","",IF(UPPER(K4)=UPPER('Race Results'!B8),10,IF(UPPER(K4)=UPPER('Race Results'!C8),6,IF(UPPER(K4)=UPPER('Race Results'!D8),4,IF(UPPER(K4)=UPPER('Race Results'!E8),3,IF(UPPER(K4)=UPPER('Race Results'!F8),2,IF(UPPER(K4)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M4" s="18">
-        <f t="shared" ref="M4:M33" si="0">IF(COUNTA(D4,F4,H4,J4,L4)=0,"",SUM(D4,F4,H4,J4,L4))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <f t="shared" ref="M4:M32" si="0">IF(COUNTA(D4,F4,H4,J4,L4)=0,"",SUM(D4,F4,H4,J4,L4))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="17" t="str">
+      <c r="B5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="17">
         <f>IF(C5="","",IF(UPPER(C5)=UPPER('Race Results'!B4),10,IF(UPPER(C5)=UPPER('Race Results'!C4),6,IF(UPPER(C5)=UPPER('Race Results'!D4),4,IF(UPPER(C5)=UPPER('Race Results'!E4),3,IF(UPPER(C5)=UPPER('Race Results'!F4),2,IF(UPPER(C5)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="17" t="str">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="17">
         <f>IF(E5="","",IF(UPPER(E5)=UPPER('Race Results'!B5),10,IF(UPPER(E5)=UPPER('Race Results'!C5),6,IF(UPPER(E5)=UPPER('Race Results'!D5),4,IF(UPPER(E5)=UPPER('Race Results'!E5),3,IF(UPPER(E5)=UPPER('Race Results'!F5),2,IF(UPPER(E5)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H5" s="17">
         <f>IF(G5="","",IF(UPPER(G5)=UPPER('Race Results'!B6),10,IF(UPPER(G5)=UPPER('Race Results'!C6),6,IF(UPPER(G5)=UPPER('Race Results'!D6),4,IF(UPPER(G5)=UPPER('Race Results'!E6),3,IF(UPPER(G5)=UPPER('Race Results'!F6),2,IF(UPPER(G5)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J5" s="17">
         <f>IF(I5="","",IF(UPPER(I5)=UPPER('Race Results'!B7),10,IF(UPPER(I5)=UPPER('Race Results'!C7),6,IF(UPPER(I5)=UPPER('Race Results'!D7),4,IF(UPPER(I5)=UPPER('Race Results'!E7),3,IF(UPPER(I5)=UPPER('Race Results'!F7),2,IF(UPPER(I5)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="L5" s="17">
         <f>IF(K5="","",IF(UPPER(K5)=UPPER('Race Results'!B8),10,IF(UPPER(K5)=UPPER('Race Results'!C8),6,IF(UPPER(K5)=UPPER('Race Results'!D8),4,IF(UPPER(K5)=UPPER('Race Results'!E8),3,IF(UPPER(K5)=UPPER('Race Results'!F8),2,IF(UPPER(K5)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M5" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A6" s="15">
         <v>3</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="17" t="str">
+      <c r="B6" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="17">
         <f>IF(C6="","",IF(UPPER(C6)=UPPER('Race Results'!B4),10,IF(UPPER(C6)=UPPER('Race Results'!C4),6,IF(UPPER(C6)=UPPER('Race Results'!D4),4,IF(UPPER(C6)=UPPER('Race Results'!E4),3,IF(UPPER(C6)=UPPER('Race Results'!F4),2,IF(UPPER(C6)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" s="17">
         <f>IF(E6="","",IF(UPPER(E6)=UPPER('Race Results'!B5),10,IF(UPPER(E6)=UPPER('Race Results'!C5),6,IF(UPPER(E6)=UPPER('Race Results'!D5),4,IF(UPPER(E6)=UPPER('Race Results'!E5),3,IF(UPPER(E6)=UPPER('Race Results'!F5),2,IF(UPPER(E6)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="H6" s="17">
         <f>IF(G6="","",IF(UPPER(G6)=UPPER('Race Results'!B6),10,IF(UPPER(G6)=UPPER('Race Results'!C6),6,IF(UPPER(G6)=UPPER('Race Results'!D6),4,IF(UPPER(G6)=UPPER('Race Results'!E6),3,IF(UPPER(G6)=UPPER('Race Results'!F6),2,IF(UPPER(G6)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="J6" s="17">
         <f>IF(I6="","",IF(UPPER(I6)=UPPER('Race Results'!B7),10,IF(UPPER(I6)=UPPER('Race Results'!C7),6,IF(UPPER(I6)=UPPER('Race Results'!D7),4,IF(UPPER(I6)=UPPER('Race Results'!E7),3,IF(UPPER(I6)=UPPER('Race Results'!F7),2,IF(UPPER(I6)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K6" s="15"/>
-      <c r="L6" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="L6" s="17">
         <f>IF(K6="","",IF(UPPER(K6)=UPPER('Race Results'!B8),10,IF(UPPER(K6)=UPPER('Race Results'!C8),6,IF(UPPER(K6)=UPPER('Race Results'!D8),4,IF(UPPER(K6)=UPPER('Race Results'!E8),3,IF(UPPER(K6)=UPPER('Race Results'!F8),2,IF(UPPER(K6)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M6" s="18">
         <f t="shared" si="0"/>
@@ -2574,31 +2620,43 @@
       <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="17" t="str">
+      <c r="B7" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="17">
         <f>IF(C7="","",IF(UPPER(C7)=UPPER('Race Results'!B4),10,IF(UPPER(C7)=UPPER('Race Results'!C4),6,IF(UPPER(C7)=UPPER('Race Results'!D4),4,IF(UPPER(C7)=UPPER('Race Results'!E4),3,IF(UPPER(C7)=UPPER('Race Results'!F4),2,IF(UPPER(C7)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7" s="17">
         <f>IF(E7="","",IF(UPPER(E7)=UPPER('Race Results'!B5),10,IF(UPPER(E7)=UPPER('Race Results'!C5),6,IF(UPPER(E7)=UPPER('Race Results'!D5),4,IF(UPPER(E7)=UPPER('Race Results'!E5),3,IF(UPPER(E7)=UPPER('Race Results'!F5),2,IF(UPPER(E7)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H7" s="17">
         <f>IF(G7="","",IF(UPPER(G7)=UPPER('Race Results'!B6),10,IF(UPPER(G7)=UPPER('Race Results'!C6),6,IF(UPPER(G7)=UPPER('Race Results'!D6),4,IF(UPPER(G7)=UPPER('Race Results'!E6),3,IF(UPPER(G7)=UPPER('Race Results'!F6),2,IF(UPPER(G7)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J7" s="17">
         <f>IF(I7="","",IF(UPPER(I7)=UPPER('Race Results'!B7),10,IF(UPPER(I7)=UPPER('Race Results'!C7),6,IF(UPPER(I7)=UPPER('Race Results'!D7),4,IF(UPPER(I7)=UPPER('Race Results'!E7),3,IF(UPPER(I7)=UPPER('Race Results'!F7),2,IF(UPPER(I7)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="L7" s="17">
         <f>IF(K7="","",IF(UPPER(K7)=UPPER('Race Results'!B8),10,IF(UPPER(K7)=UPPER('Race Results'!C8),6,IF(UPPER(K7)=UPPER('Race Results'!D8),4,IF(UPPER(K7)=UPPER('Race Results'!E8),3,IF(UPPER(K7)=UPPER('Race Results'!F8),2,IF(UPPER(K7)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M7" s="18">
         <f t="shared" si="0"/>
@@ -2609,31 +2667,43 @@
       <c r="A8" s="15">
         <v>5</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="17" t="str">
+      <c r="B8" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="17">
         <f>IF(C8="","",IF(UPPER(C8)=UPPER('Race Results'!B4),10,IF(UPPER(C8)=UPPER('Race Results'!C4),6,IF(UPPER(C8)=UPPER('Race Results'!D4),4,IF(UPPER(C8)=UPPER('Race Results'!E4),3,IF(UPPER(C8)=UPPER('Race Results'!F4),2,IF(UPPER(C8)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" s="17">
         <f>IF(E8="","",IF(UPPER(E8)=UPPER('Race Results'!B5),10,IF(UPPER(E8)=UPPER('Race Results'!C5),6,IF(UPPER(E8)=UPPER('Race Results'!D5),4,IF(UPPER(E8)=UPPER('Race Results'!E5),3,IF(UPPER(E8)=UPPER('Race Results'!F5),2,IF(UPPER(E8)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="H8" s="17">
         <f>IF(G8="","",IF(UPPER(G8)=UPPER('Race Results'!B6),10,IF(UPPER(G8)=UPPER('Race Results'!C6),6,IF(UPPER(G8)=UPPER('Race Results'!D6),4,IF(UPPER(G8)=UPPER('Race Results'!E6),3,IF(UPPER(G8)=UPPER('Race Results'!F6),2,IF(UPPER(G8)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="J8" s="17">
         <f>IF(I8="","",IF(UPPER(I8)=UPPER('Race Results'!B7),10,IF(UPPER(I8)=UPPER('Race Results'!C7),6,IF(UPPER(I8)=UPPER('Race Results'!D7),4,IF(UPPER(I8)=UPPER('Race Results'!E7),3,IF(UPPER(I8)=UPPER('Race Results'!F7),2,IF(UPPER(I8)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="L8" s="17">
         <f>IF(K8="","",IF(UPPER(K8)=UPPER('Race Results'!B8),10,IF(UPPER(K8)=UPPER('Race Results'!C8),6,IF(UPPER(K8)=UPPER('Race Results'!D8),4,IF(UPPER(K8)=UPPER('Race Results'!E8),3,IF(UPPER(K8)=UPPER('Race Results'!F8),2,IF(UPPER(K8)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M8" s="18">
         <f t="shared" si="0"/>
@@ -2644,66 +2714,90 @@
       <c r="A9" s="4">
         <v>6</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="17" t="str">
+      <c r="B9" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="17">
         <f>IF(C9="","",IF(UPPER(C9)=UPPER('Race Results'!B4),10,IF(UPPER(C9)=UPPER('Race Results'!C4),6,IF(UPPER(C9)=UPPER('Race Results'!D4),4,IF(UPPER(C9)=UPPER('Race Results'!E4),3,IF(UPPER(C9)=UPPER('Race Results'!F4),2,IF(UPPER(C9)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="17" t="str">
+        <v>6</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F9" s="17">
         <f>IF(E9="","",IF(UPPER(E9)=UPPER('Race Results'!B5),10,IF(UPPER(E9)=UPPER('Race Results'!C5),6,IF(UPPER(E9)=UPPER('Race Results'!D5),4,IF(UPPER(E9)=UPPER('Race Results'!E5),3,IF(UPPER(E9)=UPPER('Race Results'!F5),2,IF(UPPER(E9)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H9" s="17">
         <f>IF(G9="","",IF(UPPER(G9)=UPPER('Race Results'!B6),10,IF(UPPER(G9)=UPPER('Race Results'!C6),6,IF(UPPER(G9)=UPPER('Race Results'!D6),4,IF(UPPER(G9)=UPPER('Race Results'!E6),3,IF(UPPER(G9)=UPPER('Race Results'!F6),2,IF(UPPER(G9)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="J9" s="17">
         <f>IF(I9="","",IF(UPPER(I9)=UPPER('Race Results'!B7),10,IF(UPPER(I9)=UPPER('Race Results'!C7),6,IF(UPPER(I9)=UPPER('Race Results'!D7),4,IF(UPPER(I9)=UPPER('Race Results'!E7),3,IF(UPPER(I9)=UPPER('Race Results'!F7),2,IF(UPPER(I9)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="L9" s="17">
         <f>IF(K9="","",IF(UPPER(K9)=UPPER('Race Results'!B8),10,IF(UPPER(K9)=UPPER('Race Results'!C8),6,IF(UPPER(K9)=UPPER('Race Results'!D8),4,IF(UPPER(K9)=UPPER('Race Results'!E8),3,IF(UPPER(K9)=UPPER('Race Results'!F8),2,IF(UPPER(K9)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M9" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="15">
         <v>7</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="17" t="str">
+      <c r="B10" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="17">
         <f>IF(C10="","",IF(UPPER(C10)=UPPER('Race Results'!B4),10,IF(UPPER(C10)=UPPER('Race Results'!C4),6,IF(UPPER(C10)=UPPER('Race Results'!D4),4,IF(UPPER(C10)=UPPER('Race Results'!E4),3,IF(UPPER(C10)=UPPER('Race Results'!F4),2,IF(UPPER(C10)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10" s="17">
         <f>IF(E10="","",IF(UPPER(E10)=UPPER('Race Results'!B5),10,IF(UPPER(E10)=UPPER('Race Results'!C5),6,IF(UPPER(E10)=UPPER('Race Results'!D5),4,IF(UPPER(E10)=UPPER('Race Results'!E5),3,IF(UPPER(E10)=UPPER('Race Results'!F5),2,IF(UPPER(E10)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G10" s="15"/>
-      <c r="H10" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="H10" s="17">
         <f>IF(G10="","",IF(UPPER(G10)=UPPER('Race Results'!B6),10,IF(UPPER(G10)=UPPER('Race Results'!C6),6,IF(UPPER(G10)=UPPER('Race Results'!D6),4,IF(UPPER(G10)=UPPER('Race Results'!E6),3,IF(UPPER(G10)=UPPER('Race Results'!F6),2,IF(UPPER(G10)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="J10" s="17">
         <f>IF(I10="","",IF(UPPER(I10)=UPPER('Race Results'!B7),10,IF(UPPER(I10)=UPPER('Race Results'!C7),6,IF(UPPER(I10)=UPPER('Race Results'!D7),4,IF(UPPER(I10)=UPPER('Race Results'!E7),3,IF(UPPER(I10)=UPPER('Race Results'!F7),2,IF(UPPER(I10)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K10" s="15"/>
-      <c r="L10" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="L10" s="17">
         <f>IF(K10="","",IF(UPPER(K10)=UPPER('Race Results'!B8),10,IF(UPPER(K10)=UPPER('Race Results'!C8),6,IF(UPPER(K10)=UPPER('Race Results'!D8),4,IF(UPPER(K10)=UPPER('Race Results'!E8),3,IF(UPPER(K10)=UPPER('Race Results'!F8),2,IF(UPPER(K10)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M10" s="18">
         <f t="shared" si="0"/>
@@ -2714,31 +2808,43 @@
       <c r="A11" s="4">
         <v>8</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="17" t="str">
+      <c r="B11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="17">
         <f>IF(C11="","",IF(UPPER(C11)=UPPER('Race Results'!B4),10,IF(UPPER(C11)=UPPER('Race Results'!C4),6,IF(UPPER(C11)=UPPER('Race Results'!D4),4,IF(UPPER(C11)=UPPER('Race Results'!E4),3,IF(UPPER(C11)=UPPER('Race Results'!F4),2,IF(UPPER(C11)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" s="17">
         <f>IF(E11="","",IF(UPPER(E11)=UPPER('Race Results'!B5),10,IF(UPPER(E11)=UPPER('Race Results'!C5),6,IF(UPPER(E11)=UPPER('Race Results'!D5),4,IF(UPPER(E11)=UPPER('Race Results'!E5),3,IF(UPPER(E11)=UPPER('Race Results'!F5),2,IF(UPPER(E11)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H11" s="17">
         <f>IF(G11="","",IF(UPPER(G11)=UPPER('Race Results'!B6),10,IF(UPPER(G11)=UPPER('Race Results'!C6),6,IF(UPPER(G11)=UPPER('Race Results'!D6),4,IF(UPPER(G11)=UPPER('Race Results'!E6),3,IF(UPPER(G11)=UPPER('Race Results'!F6),2,IF(UPPER(G11)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J11" s="17">
         <f>IF(I11="","",IF(UPPER(I11)=UPPER('Race Results'!B7),10,IF(UPPER(I11)=UPPER('Race Results'!C7),6,IF(UPPER(I11)=UPPER('Race Results'!D7),4,IF(UPPER(I11)=UPPER('Race Results'!E7),3,IF(UPPER(I11)=UPPER('Race Results'!F7),2,IF(UPPER(I11)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="L11" s="17">
         <f>IF(K11="","",IF(UPPER(K11)=UPPER('Race Results'!B8),10,IF(UPPER(K11)=UPPER('Race Results'!C8),6,IF(UPPER(K11)=UPPER('Race Results'!D8),4,IF(UPPER(K11)=UPPER('Race Results'!E8),3,IF(UPPER(K11)=UPPER('Race Results'!F8),2,IF(UPPER(K11)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M11" s="18">
         <f t="shared" si="0"/>
@@ -2749,31 +2855,43 @@
       <c r="A12" s="15">
         <v>9</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="17" t="str">
+      <c r="B12" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="17">
         <f>IF(C12="","",IF(UPPER(C12)=UPPER('Race Results'!B4),10,IF(UPPER(C12)=UPPER('Race Results'!C4),6,IF(UPPER(C12)=UPPER('Race Results'!D4),4,IF(UPPER(C12)=UPPER('Race Results'!E4),3,IF(UPPER(C12)=UPPER('Race Results'!F4),2,IF(UPPER(C12)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" s="17">
         <f>IF(E12="","",IF(UPPER(E12)=UPPER('Race Results'!B5),10,IF(UPPER(E12)=UPPER('Race Results'!C5),6,IF(UPPER(E12)=UPPER('Race Results'!D5),4,IF(UPPER(E12)=UPPER('Race Results'!E5),3,IF(UPPER(E12)=UPPER('Race Results'!F5),2,IF(UPPER(E12)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="H12" s="17">
         <f>IF(G12="","",IF(UPPER(G12)=UPPER('Race Results'!B6),10,IF(UPPER(G12)=UPPER('Race Results'!C6),6,IF(UPPER(G12)=UPPER('Race Results'!D6),4,IF(UPPER(G12)=UPPER('Race Results'!E6),3,IF(UPPER(G12)=UPPER('Race Results'!F6),2,IF(UPPER(G12)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J12" s="17">
         <f>IF(I12="","",IF(UPPER(I12)=UPPER('Race Results'!B7),10,IF(UPPER(I12)=UPPER('Race Results'!C7),6,IF(UPPER(I12)=UPPER('Race Results'!D7),4,IF(UPPER(I12)=UPPER('Race Results'!E7),3,IF(UPPER(I12)=UPPER('Race Results'!F7),2,IF(UPPER(I12)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="L12" s="17">
         <f>IF(K12="","",IF(UPPER(K12)=UPPER('Race Results'!B8),10,IF(UPPER(K12)=UPPER('Race Results'!C8),6,IF(UPPER(K12)=UPPER('Race Results'!D8),4,IF(UPPER(K12)=UPPER('Race Results'!E8),3,IF(UPPER(K12)=UPPER('Race Results'!F8),2,IF(UPPER(K12)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M12" s="18">
         <f t="shared" si="0"/>
@@ -2784,31 +2902,43 @@
       <c r="A13" s="4">
         <v>10</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="17" t="str">
+      <c r="B13" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="17">
         <f>IF(C13="","",IF(UPPER(C13)=UPPER('Race Results'!B4),10,IF(UPPER(C13)=UPPER('Race Results'!C4),6,IF(UPPER(C13)=UPPER('Race Results'!D4),4,IF(UPPER(C13)=UPPER('Race Results'!E4),3,IF(UPPER(C13)=UPPER('Race Results'!F4),2,IF(UPPER(C13)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F13" s="17">
         <f>IF(E13="","",IF(UPPER(E13)=UPPER('Race Results'!B5),10,IF(UPPER(E13)=UPPER('Race Results'!C5),6,IF(UPPER(E13)=UPPER('Race Results'!D5),4,IF(UPPER(E13)=UPPER('Race Results'!E5),3,IF(UPPER(E13)=UPPER('Race Results'!F5),2,IF(UPPER(E13)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H13" s="17">
         <f>IF(G13="","",IF(UPPER(G13)=UPPER('Race Results'!B6),10,IF(UPPER(G13)=UPPER('Race Results'!C6),6,IF(UPPER(G13)=UPPER('Race Results'!D6),4,IF(UPPER(G13)=UPPER('Race Results'!E6),3,IF(UPPER(G13)=UPPER('Race Results'!F6),2,IF(UPPER(G13)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J13" s="17">
         <f>IF(I13="","",IF(UPPER(I13)=UPPER('Race Results'!B7),10,IF(UPPER(I13)=UPPER('Race Results'!C7),6,IF(UPPER(I13)=UPPER('Race Results'!D7),4,IF(UPPER(I13)=UPPER('Race Results'!E7),3,IF(UPPER(I13)=UPPER('Race Results'!F7),2,IF(UPPER(I13)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L13" s="17">
         <f>IF(K13="","",IF(UPPER(K13)=UPPER('Race Results'!B8),10,IF(UPPER(K13)=UPPER('Race Results'!C8),6,IF(UPPER(K13)=UPPER('Race Results'!D8),4,IF(UPPER(K13)=UPPER('Race Results'!E8),3,IF(UPPER(K13)=UPPER('Race Results'!F8),2,IF(UPPER(K13)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M13" s="18">
         <f t="shared" si="0"/>
@@ -2819,31 +2949,43 @@
       <c r="A14" s="15">
         <v>11</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="17" t="str">
+      <c r="B14" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="17">
         <f>IF(C14="","",IF(UPPER(C14)=UPPER('Race Results'!B4),10,IF(UPPER(C14)=UPPER('Race Results'!C4),6,IF(UPPER(C14)=UPPER('Race Results'!D4),4,IF(UPPER(C14)=UPPER('Race Results'!E4),3,IF(UPPER(C14)=UPPER('Race Results'!F4),2,IF(UPPER(C14)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" s="17">
         <f>IF(E14="","",IF(UPPER(E14)=UPPER('Race Results'!B5),10,IF(UPPER(E14)=UPPER('Race Results'!C5),6,IF(UPPER(E14)=UPPER('Race Results'!D5),4,IF(UPPER(E14)=UPPER('Race Results'!E5),3,IF(UPPER(E14)=UPPER('Race Results'!F5),2,IF(UPPER(E14)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="H14" s="17">
         <f>IF(G14="","",IF(UPPER(G14)=UPPER('Race Results'!B6),10,IF(UPPER(G14)=UPPER('Race Results'!C6),6,IF(UPPER(G14)=UPPER('Race Results'!D6),4,IF(UPPER(G14)=UPPER('Race Results'!E6),3,IF(UPPER(G14)=UPPER('Race Results'!F6),2,IF(UPPER(G14)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="J14" s="17">
         <f>IF(I14="","",IF(UPPER(I14)=UPPER('Race Results'!B7),10,IF(UPPER(I14)=UPPER('Race Results'!C7),6,IF(UPPER(I14)=UPPER('Race Results'!D7),4,IF(UPPER(I14)=UPPER('Race Results'!E7),3,IF(UPPER(I14)=UPPER('Race Results'!F7),2,IF(UPPER(I14)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K14" s="15"/>
-      <c r="L14" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="L14" s="17">
         <f>IF(K14="","",IF(UPPER(K14)=UPPER('Race Results'!B8),10,IF(UPPER(K14)=UPPER('Race Results'!C8),6,IF(UPPER(K14)=UPPER('Race Results'!D8),4,IF(UPPER(K14)=UPPER('Race Results'!E8),3,IF(UPPER(K14)=UPPER('Race Results'!F8),2,IF(UPPER(K14)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M14" s="18">
         <f t="shared" si="0"/>
@@ -2851,69 +2993,93 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
-        <v>12</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="17" t="str">
+      <c r="A15" s="15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="17">
         <f>IF(C15="","",IF(UPPER(C15)=UPPER('Race Results'!B4),10,IF(UPPER(C15)=UPPER('Race Results'!C4),6,IF(UPPER(C15)=UPPER('Race Results'!D4),4,IF(UPPER(C15)=UPPER('Race Results'!E4),3,IF(UPPER(C15)=UPPER('Race Results'!F4),2,IF(UPPER(C15)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="17" t="str">
+        <v>6</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" s="17">
         <f>IF(E15="","",IF(UPPER(E15)=UPPER('Race Results'!B5),10,IF(UPPER(E15)=UPPER('Race Results'!C5),6,IF(UPPER(E15)=UPPER('Race Results'!D5),4,IF(UPPER(E15)=UPPER('Race Results'!E5),3,IF(UPPER(E15)=UPPER('Race Results'!F5),2,IF(UPPER(E15)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="H15" s="17">
         <f>IF(G15="","",IF(UPPER(G15)=UPPER('Race Results'!B6),10,IF(UPPER(G15)=UPPER('Race Results'!C6),6,IF(UPPER(G15)=UPPER('Race Results'!D6),4,IF(UPPER(G15)=UPPER('Race Results'!E6),3,IF(UPPER(G15)=UPPER('Race Results'!F6),2,IF(UPPER(G15)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="J15" s="17">
         <f>IF(I15="","",IF(UPPER(I15)=UPPER('Race Results'!B7),10,IF(UPPER(I15)=UPPER('Race Results'!C7),6,IF(UPPER(I15)=UPPER('Race Results'!D7),4,IF(UPPER(I15)=UPPER('Race Results'!E7),3,IF(UPPER(I15)=UPPER('Race Results'!F7),2,IF(UPPER(I15)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K15" s="4"/>
-      <c r="L15" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="L15" s="17">
         <f>IF(K15="","",IF(UPPER(K15)=UPPER('Race Results'!B8),10,IF(UPPER(K15)=UPPER('Race Results'!C8),6,IF(UPPER(K15)=UPPER('Race Results'!D8),4,IF(UPPER(K15)=UPPER('Race Results'!E8),3,IF(UPPER(K15)=UPPER('Race Results'!F8),2,IF(UPPER(K15)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M15" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
-        <v>13</v>
-      </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="17" t="str">
+      <c r="A16" s="4">
+        <v>14</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="17">
         <f>IF(C16="","",IF(UPPER(C16)=UPPER('Race Results'!B4),10,IF(UPPER(C16)=UPPER('Race Results'!C4),6,IF(UPPER(C16)=UPPER('Race Results'!D4),4,IF(UPPER(C16)=UPPER('Race Results'!E4),3,IF(UPPER(C16)=UPPER('Race Results'!F4),2,IF(UPPER(C16)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E16" s="15"/>
-      <c r="F16" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F16" s="17">
         <f>IF(E16="","",IF(UPPER(E16)=UPPER('Race Results'!B5),10,IF(UPPER(E16)=UPPER('Race Results'!C5),6,IF(UPPER(E16)=UPPER('Race Results'!D5),4,IF(UPPER(E16)=UPPER('Race Results'!E5),3,IF(UPPER(E16)=UPPER('Race Results'!F5),2,IF(UPPER(E16)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="17">
         <f>IF(G16="","",IF(UPPER(G16)=UPPER('Race Results'!B6),10,IF(UPPER(G16)=UPPER('Race Results'!C6),6,IF(UPPER(G16)=UPPER('Race Results'!D6),4,IF(UPPER(G16)=UPPER('Race Results'!E6),3,IF(UPPER(G16)=UPPER('Race Results'!F6),2,IF(UPPER(G16)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I16" s="15"/>
-      <c r="J16" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J16" s="17">
         <f>IF(I16="","",IF(UPPER(I16)=UPPER('Race Results'!B7),10,IF(UPPER(I16)=UPPER('Race Results'!C7),6,IF(UPPER(I16)=UPPER('Race Results'!D7),4,IF(UPPER(I16)=UPPER('Race Results'!E7),3,IF(UPPER(I16)=UPPER('Race Results'!F7),2,IF(UPPER(I16)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K16" s="15"/>
-      <c r="L16" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="L16" s="17">
         <f>IF(K16="","",IF(UPPER(K16)=UPPER('Race Results'!B8),10,IF(UPPER(K16)=UPPER('Race Results'!C8),6,IF(UPPER(K16)=UPPER('Race Results'!D8),4,IF(UPPER(K16)=UPPER('Race Results'!E8),3,IF(UPPER(K16)=UPPER('Race Results'!F8),2,IF(UPPER(K16)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M16" s="18">
         <f t="shared" si="0"/>
@@ -2921,73 +3087,93 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>14</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="17" t="str">
+      <c r="A17" s="15">
+        <v>15</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="17">
         <f>IF(C17="","",IF(UPPER(C17)=UPPER('Race Results'!B4),10,IF(UPPER(C17)=UPPER('Race Results'!C4),6,IF(UPPER(C17)=UPPER('Race Results'!D4),4,IF(UPPER(C17)=UPPER('Race Results'!E4),3,IF(UPPER(C17)=UPPER('Race Results'!F4),2,IF(UPPER(C17)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F17" s="17">
         <f>IF(E17="","",IF(UPPER(E17)=UPPER('Race Results'!B5),10,IF(UPPER(E17)=UPPER('Race Results'!C5),6,IF(UPPER(E17)=UPPER('Race Results'!D5),4,IF(UPPER(E17)=UPPER('Race Results'!E5),3,IF(UPPER(E17)=UPPER('Race Results'!F5),2,IF(UPPER(E17)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="H17" s="17">
         <f>IF(G17="","",IF(UPPER(G17)=UPPER('Race Results'!B6),10,IF(UPPER(G17)=UPPER('Race Results'!C6),6,IF(UPPER(G17)=UPPER('Race Results'!D6),4,IF(UPPER(G17)=UPPER('Race Results'!E6),3,IF(UPPER(G17)=UPPER('Race Results'!F6),2,IF(UPPER(G17)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="J17" s="17">
         <f>IF(I17="","",IF(UPPER(I17)=UPPER('Race Results'!B7),10,IF(UPPER(I17)=UPPER('Race Results'!C7),6,IF(UPPER(I17)=UPPER('Race Results'!D7),4,IF(UPPER(I17)=UPPER('Race Results'!E7),3,IF(UPPER(I17)=UPPER('Race Results'!F7),2,IF(UPPER(I17)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K17" s="4"/>
-      <c r="L17" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="L17" s="17">
         <f>IF(K17="","",IF(UPPER(K17)=UPPER('Race Results'!B8),10,IF(UPPER(K17)=UPPER('Race Results'!C8),6,IF(UPPER(K17)=UPPER('Race Results'!D8),4,IF(UPPER(K17)=UPPER('Race Results'!E8),3,IF(UPPER(K17)=UPPER('Race Results'!F8),2,IF(UPPER(K17)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M17" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="15">
-        <v>15</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="17" t="str">
+    <row r="18" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="17">
         <f>IF(C18="","",IF(UPPER(C18)=UPPER('Race Results'!B4),10,IF(UPPER(C18)=UPPER('Race Results'!C4),6,IF(UPPER(C18)=UPPER('Race Results'!D4),4,IF(UPPER(C18)=UPPER('Race Results'!E4),3,IF(UPPER(C18)=UPPER('Race Results'!F4),2,IF(UPPER(C18)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" s="17">
         <f>IF(E18="","",IF(UPPER(E18)=UPPER('Race Results'!B5),10,IF(UPPER(E18)=UPPER('Race Results'!C5),6,IF(UPPER(E18)=UPPER('Race Results'!D5),4,IF(UPPER(E18)=UPPER('Race Results'!E5),3,IF(UPPER(E18)=UPPER('Race Results'!F5),2,IF(UPPER(E18)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="H18" s="17">
         <f>IF(G18="","",IF(UPPER(G18)=UPPER('Race Results'!B6),10,IF(UPPER(G18)=UPPER('Race Results'!C6),6,IF(UPPER(G18)=UPPER('Race Results'!D6),4,IF(UPPER(G18)=UPPER('Race Results'!E6),3,IF(UPPER(G18)=UPPER('Race Results'!F6),2,IF(UPPER(G18)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I18" s="15"/>
-      <c r="J18" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J18" s="17">
         <f>IF(I18="","",IF(UPPER(I18)=UPPER('Race Results'!B7),10,IF(UPPER(I18)=UPPER('Race Results'!C7),6,IF(UPPER(I18)=UPPER('Race Results'!D7),4,IF(UPPER(I18)=UPPER('Race Results'!E7),3,IF(UPPER(I18)=UPPER('Race Results'!F7),2,IF(UPPER(I18)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K18" s="15"/>
-      <c r="L18" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="L18" s="17">
         <f>IF(K18="","",IF(UPPER(K18)=UPPER('Race Results'!B8),10,IF(UPPER(K18)=UPPER('Race Results'!C8),6,IF(UPPER(K18)=UPPER('Race Results'!D8),4,IF(UPPER(K18)=UPPER('Race Results'!E8),3,IF(UPPER(K18)=UPPER('Race Results'!F8),2,IF(UPPER(K18)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M18" s="18">
         <f t="shared" si="0"/>
@@ -2995,36 +3181,46 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
-        <v>16</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="17" t="str">
+      <c r="A19" s="15">
+        <v>17</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="17">
         <f>IF(C19="","",IF(UPPER(C19)=UPPER('Race Results'!B4),10,IF(UPPER(C19)=UPPER('Race Results'!C4),6,IF(UPPER(C19)=UPPER('Race Results'!D4),4,IF(UPPER(C19)=UPPER('Race Results'!E4),3,IF(UPPER(C19)=UPPER('Race Results'!F4),2,IF(UPPER(C19)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" s="17">
         <f>IF(E19="","",IF(UPPER(E19)=UPPER('Race Results'!B5),10,IF(UPPER(E19)=UPPER('Race Results'!C5),6,IF(UPPER(E19)=UPPER('Race Results'!D5),4,IF(UPPER(E19)=UPPER('Race Results'!E5),3,IF(UPPER(E19)=UPPER('Race Results'!F5),2,IF(UPPER(E19)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="H19" s="17">
         <f>IF(G19="","",IF(UPPER(G19)=UPPER('Race Results'!B6),10,IF(UPPER(G19)=UPPER('Race Results'!C6),6,IF(UPPER(G19)=UPPER('Race Results'!D6),4,IF(UPPER(G19)=UPPER('Race Results'!E6),3,IF(UPPER(G19)=UPPER('Race Results'!F6),2,IF(UPPER(G19)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I19" s="4"/>
-      <c r="J19" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="J19" s="17">
         <f>IF(I19="","",IF(UPPER(I19)=UPPER('Race Results'!B7),10,IF(UPPER(I19)=UPPER('Race Results'!C7),6,IF(UPPER(I19)=UPPER('Race Results'!D7),4,IF(UPPER(I19)=UPPER('Race Results'!E7),3,IF(UPPER(I19)=UPPER('Race Results'!F7),2,IF(UPPER(I19)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K19" s="4"/>
-      <c r="L19" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="L19" s="17">
         <f>IF(K19="","",IF(UPPER(K19)=UPPER('Race Results'!B8),10,IF(UPPER(K19)=UPPER('Race Results'!C8),6,IF(UPPER(K19)=UPPER('Race Results'!D8),4,IF(UPPER(K19)=UPPER('Race Results'!E8),3,IF(UPPER(K19)=UPPER('Race Results'!F8),2,IF(UPPER(K19)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M19" s="18">
         <f t="shared" si="0"/>
@@ -3032,36 +3228,46 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="15">
-        <v>17</v>
+      <c r="A20" s="4">
+        <v>18</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="17" t="str">
+        <v>74</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" s="17">
         <f>IF(C20="","",IF(UPPER(C20)=UPPER('Race Results'!B4),10,IF(UPPER(C20)=UPPER('Race Results'!C4),6,IF(UPPER(C20)=UPPER('Race Results'!D4),4,IF(UPPER(C20)=UPPER('Race Results'!E4),3,IF(UPPER(C20)=UPPER('Race Results'!F4),2,IF(UPPER(C20)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E20" s="15"/>
-      <c r="F20" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F20" s="17">
         <f>IF(E20="","",IF(UPPER(E20)=UPPER('Race Results'!B5),10,IF(UPPER(E20)=UPPER('Race Results'!C5),6,IF(UPPER(E20)=UPPER('Race Results'!D5),4,IF(UPPER(E20)=UPPER('Race Results'!E5),3,IF(UPPER(E20)=UPPER('Race Results'!F5),2,IF(UPPER(E20)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G20" s="15"/>
-      <c r="H20" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H20" s="17">
         <f>IF(G20="","",IF(UPPER(G20)=UPPER('Race Results'!B6),10,IF(UPPER(G20)=UPPER('Race Results'!C6),6,IF(UPPER(G20)=UPPER('Race Results'!D6),4,IF(UPPER(G20)=UPPER('Race Results'!E6),3,IF(UPPER(G20)=UPPER('Race Results'!F6),2,IF(UPPER(G20)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I20" s="15"/>
-      <c r="J20" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J20" s="17">
         <f>IF(I20="","",IF(UPPER(I20)=UPPER('Race Results'!B7),10,IF(UPPER(I20)=UPPER('Race Results'!C7),6,IF(UPPER(I20)=UPPER('Race Results'!D7),4,IF(UPPER(I20)=UPPER('Race Results'!E7),3,IF(UPPER(I20)=UPPER('Race Results'!F7),2,IF(UPPER(I20)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K20" s="15"/>
-      <c r="L20" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="L20" s="17">
         <f>IF(K20="","",IF(UPPER(K20)=UPPER('Race Results'!B8),10,IF(UPPER(K20)=UPPER('Race Results'!C8),6,IF(UPPER(K20)=UPPER('Race Results'!D8),4,IF(UPPER(K20)=UPPER('Race Results'!E8),3,IF(UPPER(K20)=UPPER('Race Results'!F8),2,IF(UPPER(K20)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M20" s="18">
         <f t="shared" si="0"/>
@@ -3069,34 +3275,46 @@
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>18</v>
-      </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="17" t="str">
+      <c r="A21" s="15">
+        <v>19</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="17">
         <f>IF(C21="","",IF(UPPER(C21)=UPPER('Race Results'!B4),10,IF(UPPER(C21)=UPPER('Race Results'!C4),6,IF(UPPER(C21)=UPPER('Race Results'!D4),4,IF(UPPER(C21)=UPPER('Race Results'!E4),3,IF(UPPER(C21)=UPPER('Race Results'!F4),2,IF(UPPER(C21)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F21" s="17">
         <f>IF(E21="","",IF(UPPER(E21)=UPPER('Race Results'!B5),10,IF(UPPER(E21)=UPPER('Race Results'!C5),6,IF(UPPER(E21)=UPPER('Race Results'!D5),4,IF(UPPER(E21)=UPPER('Race Results'!E5),3,IF(UPPER(E21)=UPPER('Race Results'!F5),2,IF(UPPER(E21)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="H21" s="17">
         <f>IF(G21="","",IF(UPPER(G21)=UPPER('Race Results'!B6),10,IF(UPPER(G21)=UPPER('Race Results'!C6),6,IF(UPPER(G21)=UPPER('Race Results'!D6),4,IF(UPPER(G21)=UPPER('Race Results'!E6),3,IF(UPPER(G21)=UPPER('Race Results'!F6),2,IF(UPPER(G21)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I21" s="4"/>
-      <c r="J21" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="J21" s="17">
         <f>IF(I21="","",IF(UPPER(I21)=UPPER('Race Results'!B7),10,IF(UPPER(I21)=UPPER('Race Results'!C7),6,IF(UPPER(I21)=UPPER('Race Results'!D7),4,IF(UPPER(I21)=UPPER('Race Results'!E7),3,IF(UPPER(I21)=UPPER('Race Results'!F7),2,IF(UPPER(I21)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K21" s="4"/>
-      <c r="L21" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="L21" s="17">
         <f>IF(K21="","",IF(UPPER(K21)=UPPER('Race Results'!B8),10,IF(UPPER(K21)=UPPER('Race Results'!C8),6,IF(UPPER(K21)=UPPER('Race Results'!D8),4,IF(UPPER(K21)=UPPER('Race Results'!E8),3,IF(UPPER(K21)=UPPER('Race Results'!F8),2,IF(UPPER(K21)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M21" s="18">
         <f t="shared" si="0"/>
@@ -3104,69 +3322,93 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="15">
-        <v>19</v>
-      </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="17" t="str">
+      <c r="A22" s="4">
+        <v>20</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="17">
         <f>IF(C22="","",IF(UPPER(C22)=UPPER('Race Results'!B4),10,IF(UPPER(C22)=UPPER('Race Results'!C4),6,IF(UPPER(C22)=UPPER('Race Results'!D4),4,IF(UPPER(C22)=UPPER('Race Results'!E4),3,IF(UPPER(C22)=UPPER('Race Results'!F4),2,IF(UPPER(C22)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E22" s="15"/>
-      <c r="F22" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F22" s="17">
         <f>IF(E22="","",IF(UPPER(E22)=UPPER('Race Results'!B5),10,IF(UPPER(E22)=UPPER('Race Results'!C5),6,IF(UPPER(E22)=UPPER('Race Results'!D5),4,IF(UPPER(E22)=UPPER('Race Results'!E5),3,IF(UPPER(E22)=UPPER('Race Results'!F5),2,IF(UPPER(E22)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G22" s="15"/>
-      <c r="H22" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H22" s="17">
         <f>IF(G22="","",IF(UPPER(G22)=UPPER('Race Results'!B6),10,IF(UPPER(G22)=UPPER('Race Results'!C6),6,IF(UPPER(G22)=UPPER('Race Results'!D6),4,IF(UPPER(G22)=UPPER('Race Results'!E6),3,IF(UPPER(G22)=UPPER('Race Results'!F6),2,IF(UPPER(G22)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I22" s="15"/>
-      <c r="J22" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J22" s="17">
         <f>IF(I22="","",IF(UPPER(I22)=UPPER('Race Results'!B7),10,IF(UPPER(I22)=UPPER('Race Results'!C7),6,IF(UPPER(I22)=UPPER('Race Results'!D7),4,IF(UPPER(I22)=UPPER('Race Results'!E7),3,IF(UPPER(I22)=UPPER('Race Results'!F7),2,IF(UPPER(I22)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K22" s="15"/>
-      <c r="L22" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="L22" s="17">
         <f>IF(K22="","",IF(UPPER(K22)=UPPER('Race Results'!B8),10,IF(UPPER(K22)=UPPER('Race Results'!C8),6,IF(UPPER(K22)=UPPER('Race Results'!D8),4,IF(UPPER(K22)=UPPER('Race Results'!E8),3,IF(UPPER(K22)=UPPER('Race Results'!F8),2,IF(UPPER(K22)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M22" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="4">
-        <v>20</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="17" t="str">
+    <row r="23" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="15">
+        <v>21</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="17">
         <f>IF(C23="","",IF(UPPER(C23)=UPPER('Race Results'!B4),10,IF(UPPER(C23)=UPPER('Race Results'!C4),6,IF(UPPER(C23)=UPPER('Race Results'!D4),4,IF(UPPER(C23)=UPPER('Race Results'!E4),3,IF(UPPER(C23)=UPPER('Race Results'!F4),2,IF(UPPER(C23)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F23" s="17">
         <f>IF(E23="","",IF(UPPER(E23)=UPPER('Race Results'!B5),10,IF(UPPER(E23)=UPPER('Race Results'!C5),6,IF(UPPER(E23)=UPPER('Race Results'!D5),4,IF(UPPER(E23)=UPPER('Race Results'!E5),3,IF(UPPER(E23)=UPPER('Race Results'!F5),2,IF(UPPER(E23)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23" s="17">
         <f>IF(G23="","",IF(UPPER(G23)=UPPER('Race Results'!B6),10,IF(UPPER(G23)=UPPER('Race Results'!C6),6,IF(UPPER(G23)=UPPER('Race Results'!D6),4,IF(UPPER(G23)=UPPER('Race Results'!E6),3,IF(UPPER(G23)=UPPER('Race Results'!F6),2,IF(UPPER(G23)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I23" s="4"/>
-      <c r="J23" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="17">
         <f>IF(I23="","",IF(UPPER(I23)=UPPER('Race Results'!B7),10,IF(UPPER(I23)=UPPER('Race Results'!C7),6,IF(UPPER(I23)=UPPER('Race Results'!D7),4,IF(UPPER(I23)=UPPER('Race Results'!E7),3,IF(UPPER(I23)=UPPER('Race Results'!F7),2,IF(UPPER(I23)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K23" s="4"/>
-      <c r="L23" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="L23" s="17">
         <f>IF(K23="","",IF(UPPER(K23)=UPPER('Race Results'!B8),10,IF(UPPER(K23)=UPPER('Race Results'!C8),6,IF(UPPER(K23)=UPPER('Race Results'!D8),4,IF(UPPER(K23)=UPPER('Race Results'!E8),3,IF(UPPER(K23)=UPPER('Race Results'!F8),2,IF(UPPER(K23)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M23" s="18">
         <f t="shared" si="0"/>
@@ -3174,34 +3416,46 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="15">
-        <v>21</v>
-      </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="17" t="str">
+      <c r="A24" s="4">
+        <v>22</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="17">
         <f>IF(C24="","",IF(UPPER(C24)=UPPER('Race Results'!B4),10,IF(UPPER(C24)=UPPER('Race Results'!C4),6,IF(UPPER(C24)=UPPER('Race Results'!D4),4,IF(UPPER(C24)=UPPER('Race Results'!E4),3,IF(UPPER(C24)=UPPER('Race Results'!F4),2,IF(UPPER(C24)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F24" s="17">
         <f>IF(E24="","",IF(UPPER(E24)=UPPER('Race Results'!B5),10,IF(UPPER(E24)=UPPER('Race Results'!C5),6,IF(UPPER(E24)=UPPER('Race Results'!D5),4,IF(UPPER(E24)=UPPER('Race Results'!E5),3,IF(UPPER(E24)=UPPER('Race Results'!F5),2,IF(UPPER(E24)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G24" s="15"/>
-      <c r="H24" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="H24" s="17">
         <f>IF(G24="","",IF(UPPER(G24)=UPPER('Race Results'!B6),10,IF(UPPER(G24)=UPPER('Race Results'!C6),6,IF(UPPER(G24)=UPPER('Race Results'!D6),4,IF(UPPER(G24)=UPPER('Race Results'!E6),3,IF(UPPER(G24)=UPPER('Race Results'!F6),2,IF(UPPER(G24)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I24" s="15"/>
-      <c r="J24" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J24" s="17">
         <f>IF(I24="","",IF(UPPER(I24)=UPPER('Race Results'!B7),10,IF(UPPER(I24)=UPPER('Race Results'!C7),6,IF(UPPER(I24)=UPPER('Race Results'!D7),4,IF(UPPER(I24)=UPPER('Race Results'!E7),3,IF(UPPER(I24)=UPPER('Race Results'!F7),2,IF(UPPER(I24)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K24" s="15"/>
-      <c r="L24" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="L24" s="17">
         <f>IF(K24="","",IF(UPPER(K24)=UPPER('Race Results'!B8),10,IF(UPPER(K24)=UPPER('Race Results'!C8),6,IF(UPPER(K24)=UPPER('Race Results'!D8),4,IF(UPPER(K24)=UPPER('Race Results'!E8),3,IF(UPPER(K24)=UPPER('Race Results'!F8),2,IF(UPPER(K24)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M24" s="18">
         <f t="shared" si="0"/>
@@ -3209,69 +3463,93 @@
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
-        <v>22</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="17" t="str">
+      <c r="A25" s="15">
+        <v>23</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="17">
         <f>IF(C25="","",IF(UPPER(C25)=UPPER('Race Results'!B4),10,IF(UPPER(C25)=UPPER('Race Results'!C4),6,IF(UPPER(C25)=UPPER('Race Results'!D4),4,IF(UPPER(C25)=UPPER('Race Results'!E4),3,IF(UPPER(C25)=UPPER('Race Results'!F4),2,IF(UPPER(C25)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="17" t="str">
+        <v>10</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" s="17">
         <f>IF(E25="","",IF(UPPER(E25)=UPPER('Race Results'!B5),10,IF(UPPER(E25)=UPPER('Race Results'!C5),6,IF(UPPER(E25)=UPPER('Race Results'!D5),4,IF(UPPER(E25)=UPPER('Race Results'!E5),3,IF(UPPER(E25)=UPPER('Race Results'!F5),2,IF(UPPER(E25)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="H25" s="17">
         <f>IF(G25="","",IF(UPPER(G25)=UPPER('Race Results'!B6),10,IF(UPPER(G25)=UPPER('Race Results'!C6),6,IF(UPPER(G25)=UPPER('Race Results'!D6),4,IF(UPPER(G25)=UPPER('Race Results'!E6),3,IF(UPPER(G25)=UPPER('Race Results'!F6),2,IF(UPPER(G25)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I25" s="4"/>
-      <c r="J25" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="J25" s="17">
         <f>IF(I25="","",IF(UPPER(I25)=UPPER('Race Results'!B7),10,IF(UPPER(I25)=UPPER('Race Results'!C7),6,IF(UPPER(I25)=UPPER('Race Results'!D7),4,IF(UPPER(I25)=UPPER('Race Results'!E7),3,IF(UPPER(I25)=UPPER('Race Results'!F7),2,IF(UPPER(I25)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K25" s="4"/>
-      <c r="L25" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="L25" s="17">
         <f>IF(K25="","",IF(UPPER(K25)=UPPER('Race Results'!B8),10,IF(UPPER(K25)=UPPER('Race Results'!C8),6,IF(UPPER(K25)=UPPER('Race Results'!D8),4,IF(UPPER(K25)=UPPER('Race Results'!E8),3,IF(UPPER(K25)=UPPER('Race Results'!F8),2,IF(UPPER(K25)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M25" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="15">
-        <v>23</v>
-      </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="17" t="str">
+      <c r="A26" s="4">
+        <v>24</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="17">
         <f>IF(C26="","",IF(UPPER(C26)=UPPER('Race Results'!B4),10,IF(UPPER(C26)=UPPER('Race Results'!C4),6,IF(UPPER(C26)=UPPER('Race Results'!D4),4,IF(UPPER(C26)=UPPER('Race Results'!E4),3,IF(UPPER(C26)=UPPER('Race Results'!F4),2,IF(UPPER(C26)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F26" s="17">
         <f>IF(E26="","",IF(UPPER(E26)=UPPER('Race Results'!B5),10,IF(UPPER(E26)=UPPER('Race Results'!C5),6,IF(UPPER(E26)=UPPER('Race Results'!D5),4,IF(UPPER(E26)=UPPER('Race Results'!E5),3,IF(UPPER(E26)=UPPER('Race Results'!F5),2,IF(UPPER(E26)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G26" s="15"/>
-      <c r="H26" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H26" s="17">
         <f>IF(G26="","",IF(UPPER(G26)=UPPER('Race Results'!B6),10,IF(UPPER(G26)=UPPER('Race Results'!C6),6,IF(UPPER(G26)=UPPER('Race Results'!D6),4,IF(UPPER(G26)=UPPER('Race Results'!E6),3,IF(UPPER(G26)=UPPER('Race Results'!F6),2,IF(UPPER(G26)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I26" s="15"/>
-      <c r="J26" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J26" s="17">
         <f>IF(I26="","",IF(UPPER(I26)=UPPER('Race Results'!B7),10,IF(UPPER(I26)=UPPER('Race Results'!C7),6,IF(UPPER(I26)=UPPER('Race Results'!D7),4,IF(UPPER(I26)=UPPER('Race Results'!E7),3,IF(UPPER(I26)=UPPER('Race Results'!F7),2,IF(UPPER(I26)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K26" s="15"/>
-      <c r="L26" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="L26" s="17">
         <f>IF(K26="","",IF(UPPER(K26)=UPPER('Race Results'!B8),10,IF(UPPER(K26)=UPPER('Race Results'!C8),6,IF(UPPER(K26)=UPPER('Race Results'!D8),4,IF(UPPER(K26)=UPPER('Race Results'!E8),3,IF(UPPER(K26)=UPPER('Race Results'!F8),2,IF(UPPER(K26)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M26" s="18">
         <f t="shared" si="0"/>
@@ -3279,34 +3557,46 @@
       </c>
     </row>
     <row r="27" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="4">
-        <v>24</v>
-      </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="17" t="str">
+      <c r="A27" s="15">
+        <v>25</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="17">
         <f>IF(C27="","",IF(UPPER(C27)=UPPER('Race Results'!B4),10,IF(UPPER(C27)=UPPER('Race Results'!C4),6,IF(UPPER(C27)=UPPER('Race Results'!D4),4,IF(UPPER(C27)=UPPER('Race Results'!E4),3,IF(UPPER(C27)=UPPER('Race Results'!F4),2,IF(UPPER(C27)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="F27" s="17">
         <f>IF(E27="","",IF(UPPER(E27)=UPPER('Race Results'!B5),10,IF(UPPER(E27)=UPPER('Race Results'!C5),6,IF(UPPER(E27)=UPPER('Race Results'!D5),4,IF(UPPER(E27)=UPPER('Race Results'!E5),3,IF(UPPER(E27)=UPPER('Race Results'!F5),2,IF(UPPER(E27)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="H27" s="17">
         <f>IF(G27="","",IF(UPPER(G27)=UPPER('Race Results'!B6),10,IF(UPPER(G27)=UPPER('Race Results'!C6),6,IF(UPPER(G27)=UPPER('Race Results'!D6),4,IF(UPPER(G27)=UPPER('Race Results'!E6),3,IF(UPPER(G27)=UPPER('Race Results'!F6),2,IF(UPPER(G27)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I27" s="4"/>
-      <c r="J27" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="J27" s="17">
         <f>IF(I27="","",IF(UPPER(I27)=UPPER('Race Results'!B7),10,IF(UPPER(I27)=UPPER('Race Results'!C7),6,IF(UPPER(I27)=UPPER('Race Results'!D7),4,IF(UPPER(I27)=UPPER('Race Results'!E7),3,IF(UPPER(I27)=UPPER('Race Results'!F7),2,IF(UPPER(I27)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K27" s="4"/>
-      <c r="L27" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="L27" s="17">
         <f>IF(K27="","",IF(UPPER(K27)=UPPER('Race Results'!B8),10,IF(UPPER(K27)=UPPER('Race Results'!C8),6,IF(UPPER(K27)=UPPER('Race Results'!D8),4,IF(UPPER(K27)=UPPER('Race Results'!E8),3,IF(UPPER(K27)=UPPER('Race Results'!F8),2,IF(UPPER(K27)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M27" s="18">
         <f t="shared" si="0"/>
@@ -3314,34 +3604,46 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="15">
-        <v>25</v>
-      </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="17" t="str">
+      <c r="A28" s="4">
+        <v>26</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" s="17">
         <f>IF(C28="","",IF(UPPER(C28)=UPPER('Race Results'!B4),10,IF(UPPER(C28)=UPPER('Race Results'!C4),6,IF(UPPER(C28)=UPPER('Race Results'!D4),4,IF(UPPER(C28)=UPPER('Race Results'!E4),3,IF(UPPER(C28)=UPPER('Race Results'!F4),2,IF(UPPER(C28)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E28" s="15"/>
-      <c r="F28" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F28" s="17">
         <f>IF(E28="","",IF(UPPER(E28)=UPPER('Race Results'!B5),10,IF(UPPER(E28)=UPPER('Race Results'!C5),6,IF(UPPER(E28)=UPPER('Race Results'!D5),4,IF(UPPER(E28)=UPPER('Race Results'!E5),3,IF(UPPER(E28)=UPPER('Race Results'!F5),2,IF(UPPER(E28)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G28" s="15"/>
-      <c r="H28" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H28" s="17">
         <f>IF(G28="","",IF(UPPER(G28)=UPPER('Race Results'!B6),10,IF(UPPER(G28)=UPPER('Race Results'!C6),6,IF(UPPER(G28)=UPPER('Race Results'!D6),4,IF(UPPER(G28)=UPPER('Race Results'!E6),3,IF(UPPER(G28)=UPPER('Race Results'!F6),2,IF(UPPER(G28)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I28" s="15"/>
-      <c r="J28" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J28" s="17">
         <f>IF(I28="","",IF(UPPER(I28)=UPPER('Race Results'!B7),10,IF(UPPER(I28)=UPPER('Race Results'!C7),6,IF(UPPER(I28)=UPPER('Race Results'!D7),4,IF(UPPER(I28)=UPPER('Race Results'!E7),3,IF(UPPER(I28)=UPPER('Race Results'!F7),2,IF(UPPER(I28)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K28" s="15"/>
-      <c r="L28" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="L28" s="17">
         <f>IF(K28="","",IF(UPPER(K28)=UPPER('Race Results'!B8),10,IF(UPPER(K28)=UPPER('Race Results'!C8),6,IF(UPPER(K28)=UPPER('Race Results'!D8),4,IF(UPPER(K28)=UPPER('Race Results'!E8),3,IF(UPPER(K28)=UPPER('Race Results'!F8),2,IF(UPPER(K28)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M28" s="18">
         <f t="shared" si="0"/>
@@ -3349,31 +3651,31 @@
       </c>
     </row>
     <row r="29" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="4">
-        <v>26</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="4"/>
+      <c r="A29" s="15">
+        <v>27</v>
+      </c>
+      <c r="B29" s="16"/>
+      <c r="C29" s="15"/>
       <c r="D29" s="17" t="str">
         <f>IF(C29="","",IF(UPPER(C29)=UPPER('Race Results'!B4),10,IF(UPPER(C29)=UPPER('Race Results'!C4),6,IF(UPPER(C29)=UPPER('Race Results'!D4),4,IF(UPPER(C29)=UPPER('Race Results'!E4),3,IF(UPPER(C29)=UPPER('Race Results'!F4),2,IF(UPPER(C29)=UPPER('Race Results'!G4),1,0)))))))</f>
         <v/>
       </c>
-      <c r="E29" s="4"/>
+      <c r="E29" s="15"/>
       <c r="F29" s="17" t="str">
         <f>IF(E29="","",IF(UPPER(E29)=UPPER('Race Results'!B5),10,IF(UPPER(E29)=UPPER('Race Results'!C5),6,IF(UPPER(E29)=UPPER('Race Results'!D5),4,IF(UPPER(E29)=UPPER('Race Results'!E5),3,IF(UPPER(E29)=UPPER('Race Results'!F5),2,IF(UPPER(E29)=UPPER('Race Results'!G5),1,0)))))))</f>
         <v/>
       </c>
-      <c r="G29" s="4"/>
+      <c r="G29" s="15"/>
       <c r="H29" s="17" t="str">
         <f>IF(G29="","",IF(UPPER(G29)=UPPER('Race Results'!B6),10,IF(UPPER(G29)=UPPER('Race Results'!C6),6,IF(UPPER(G29)=UPPER('Race Results'!D6),4,IF(UPPER(G29)=UPPER('Race Results'!E6),3,IF(UPPER(G29)=UPPER('Race Results'!F6),2,IF(UPPER(G29)=UPPER('Race Results'!G6),1,0)))))))</f>
         <v/>
       </c>
-      <c r="I29" s="4"/>
+      <c r="I29" s="15"/>
       <c r="J29" s="17" t="str">
         <f>IF(I29="","",IF(UPPER(I29)=UPPER('Race Results'!B7),10,IF(UPPER(I29)=UPPER('Race Results'!C7),6,IF(UPPER(I29)=UPPER('Race Results'!D7),4,IF(UPPER(I29)=UPPER('Race Results'!E7),3,IF(UPPER(I29)=UPPER('Race Results'!F7),2,IF(UPPER(I29)=UPPER('Race Results'!G7),1,0)))))))</f>
         <v/>
       </c>
-      <c r="K29" s="4"/>
+      <c r="K29" s="15"/>
       <c r="L29" s="17" t="str">
         <f>IF(K29="","",IF(UPPER(K29)=UPPER('Race Results'!B8),10,IF(UPPER(K29)=UPPER('Race Results'!C8),6,IF(UPPER(K29)=UPPER('Race Results'!D8),4,IF(UPPER(K29)=UPPER('Race Results'!E8),3,IF(UPPER(K29)=UPPER('Race Results'!F8),2,IF(UPPER(K29)=UPPER('Race Results'!G8),1,0)))))))</f>
         <v/>
@@ -3384,31 +3686,31 @@
       </c>
     </row>
     <row r="30" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="15">
-        <v>27</v>
-      </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="15"/>
+      <c r="A30" s="4">
+        <v>28</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="4"/>
       <c r="D30" s="17" t="str">
         <f>IF(C30="","",IF(UPPER(C30)=UPPER('Race Results'!B4),10,IF(UPPER(C30)=UPPER('Race Results'!C4),6,IF(UPPER(C30)=UPPER('Race Results'!D4),4,IF(UPPER(C30)=UPPER('Race Results'!E4),3,IF(UPPER(C30)=UPPER('Race Results'!F4),2,IF(UPPER(C30)=UPPER('Race Results'!G4),1,0)))))))</f>
         <v/>
       </c>
-      <c r="E30" s="15"/>
+      <c r="E30" s="4"/>
       <c r="F30" s="17" t="str">
         <f>IF(E30="","",IF(UPPER(E30)=UPPER('Race Results'!B5),10,IF(UPPER(E30)=UPPER('Race Results'!C5),6,IF(UPPER(E30)=UPPER('Race Results'!D5),4,IF(UPPER(E30)=UPPER('Race Results'!E5),3,IF(UPPER(E30)=UPPER('Race Results'!F5),2,IF(UPPER(E30)=UPPER('Race Results'!G5),1,0)))))))</f>
         <v/>
       </c>
-      <c r="G30" s="15"/>
+      <c r="G30" s="4"/>
       <c r="H30" s="17" t="str">
         <f>IF(G30="","",IF(UPPER(G30)=UPPER('Race Results'!B6),10,IF(UPPER(G30)=UPPER('Race Results'!C6),6,IF(UPPER(G30)=UPPER('Race Results'!D6),4,IF(UPPER(G30)=UPPER('Race Results'!E6),3,IF(UPPER(G30)=UPPER('Race Results'!F6),2,IF(UPPER(G30)=UPPER('Race Results'!G6),1,0)))))))</f>
         <v/>
       </c>
-      <c r="I30" s="15"/>
+      <c r="I30" s="4"/>
       <c r="J30" s="17" t="str">
         <f>IF(I30="","",IF(UPPER(I30)=UPPER('Race Results'!B7),10,IF(UPPER(I30)=UPPER('Race Results'!C7),6,IF(UPPER(I30)=UPPER('Race Results'!D7),4,IF(UPPER(I30)=UPPER('Race Results'!E7),3,IF(UPPER(I30)=UPPER('Race Results'!F7),2,IF(UPPER(I30)=UPPER('Race Results'!G7),1,0)))))))</f>
         <v/>
       </c>
-      <c r="K30" s="15"/>
+      <c r="K30" s="4"/>
       <c r="L30" s="17" t="str">
         <f>IF(K30="","",IF(UPPER(K30)=UPPER('Race Results'!B8),10,IF(UPPER(K30)=UPPER('Race Results'!C8),6,IF(UPPER(K30)=UPPER('Race Results'!D8),4,IF(UPPER(K30)=UPPER('Race Results'!E8),3,IF(UPPER(K30)=UPPER('Race Results'!F8),2,IF(UPPER(K30)=UPPER('Race Results'!G8),1,0)))))))</f>
         <v/>
@@ -3419,31 +3721,31 @@
       </c>
     </row>
     <row r="31" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="4">
-        <v>28</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="4"/>
+      <c r="A31" s="15">
+        <v>29</v>
+      </c>
+      <c r="B31" s="16"/>
+      <c r="C31" s="15"/>
       <c r="D31" s="17" t="str">
         <f>IF(C31="","",IF(UPPER(C31)=UPPER('Race Results'!B4),10,IF(UPPER(C31)=UPPER('Race Results'!C4),6,IF(UPPER(C31)=UPPER('Race Results'!D4),4,IF(UPPER(C31)=UPPER('Race Results'!E4),3,IF(UPPER(C31)=UPPER('Race Results'!F4),2,IF(UPPER(C31)=UPPER('Race Results'!G4),1,0)))))))</f>
         <v/>
       </c>
-      <c r="E31" s="4"/>
+      <c r="E31" s="15"/>
       <c r="F31" s="17" t="str">
         <f>IF(E31="","",IF(UPPER(E31)=UPPER('Race Results'!B5),10,IF(UPPER(E31)=UPPER('Race Results'!C5),6,IF(UPPER(E31)=UPPER('Race Results'!D5),4,IF(UPPER(E31)=UPPER('Race Results'!E5),3,IF(UPPER(E31)=UPPER('Race Results'!F5),2,IF(UPPER(E31)=UPPER('Race Results'!G5),1,0)))))))</f>
         <v/>
       </c>
-      <c r="G31" s="4"/>
+      <c r="G31" s="15"/>
       <c r="H31" s="17" t="str">
         <f>IF(G31="","",IF(UPPER(G31)=UPPER('Race Results'!B6),10,IF(UPPER(G31)=UPPER('Race Results'!C6),6,IF(UPPER(G31)=UPPER('Race Results'!D6),4,IF(UPPER(G31)=UPPER('Race Results'!E6),3,IF(UPPER(G31)=UPPER('Race Results'!F6),2,IF(UPPER(G31)=UPPER('Race Results'!G6),1,0)))))))</f>
         <v/>
       </c>
-      <c r="I31" s="4"/>
+      <c r="I31" s="15"/>
       <c r="J31" s="17" t="str">
         <f>IF(I31="","",IF(UPPER(I31)=UPPER('Race Results'!B7),10,IF(UPPER(I31)=UPPER('Race Results'!C7),6,IF(UPPER(I31)=UPPER('Race Results'!D7),4,IF(UPPER(I31)=UPPER('Race Results'!E7),3,IF(UPPER(I31)=UPPER('Race Results'!F7),2,IF(UPPER(I31)=UPPER('Race Results'!G7),1,0)))))))</f>
         <v/>
       </c>
-      <c r="K31" s="4"/>
+      <c r="K31" s="15"/>
       <c r="L31" s="17" t="str">
         <f>IF(K31="","",IF(UPPER(K31)=UPPER('Race Results'!B8),10,IF(UPPER(K31)=UPPER('Race Results'!C8),6,IF(UPPER(K31)=UPPER('Race Results'!D8),4,IF(UPPER(K31)=UPPER('Race Results'!E8),3,IF(UPPER(K31)=UPPER('Race Results'!F8),2,IF(UPPER(K31)=UPPER('Race Results'!G8),1,0)))))))</f>
         <v/>
@@ -3454,71 +3756,36 @@
       </c>
     </row>
     <row r="32" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="15">
-        <v>29</v>
-      </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="15"/>
+      <c r="A32" s="4">
+        <v>30</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="4"/>
       <c r="D32" s="17" t="str">
         <f>IF(C32="","",IF(UPPER(C32)=UPPER('Race Results'!B4),10,IF(UPPER(C32)=UPPER('Race Results'!C4),6,IF(UPPER(C32)=UPPER('Race Results'!D4),4,IF(UPPER(C32)=UPPER('Race Results'!E4),3,IF(UPPER(C32)=UPPER('Race Results'!F4),2,IF(UPPER(C32)=UPPER('Race Results'!G4),1,0)))))))</f>
         <v/>
       </c>
-      <c r="E32" s="15"/>
+      <c r="E32" s="4"/>
       <c r="F32" s="17" t="str">
         <f>IF(E32="","",IF(UPPER(E32)=UPPER('Race Results'!B5),10,IF(UPPER(E32)=UPPER('Race Results'!C5),6,IF(UPPER(E32)=UPPER('Race Results'!D5),4,IF(UPPER(E32)=UPPER('Race Results'!E5),3,IF(UPPER(E32)=UPPER('Race Results'!F5),2,IF(UPPER(E32)=UPPER('Race Results'!G5),1,0)))))))</f>
         <v/>
       </c>
-      <c r="G32" s="15"/>
+      <c r="G32" s="4"/>
       <c r="H32" s="17" t="str">
         <f>IF(G32="","",IF(UPPER(G32)=UPPER('Race Results'!B6),10,IF(UPPER(G32)=UPPER('Race Results'!C6),6,IF(UPPER(G32)=UPPER('Race Results'!D6),4,IF(UPPER(G32)=UPPER('Race Results'!E6),3,IF(UPPER(G32)=UPPER('Race Results'!F6),2,IF(UPPER(G32)=UPPER('Race Results'!G6),1,0)))))))</f>
         <v/>
       </c>
-      <c r="I32" s="15"/>
+      <c r="I32" s="4"/>
       <c r="J32" s="17" t="str">
         <f>IF(I32="","",IF(UPPER(I32)=UPPER('Race Results'!B7),10,IF(UPPER(I32)=UPPER('Race Results'!C7),6,IF(UPPER(I32)=UPPER('Race Results'!D7),4,IF(UPPER(I32)=UPPER('Race Results'!E7),3,IF(UPPER(I32)=UPPER('Race Results'!F7),2,IF(UPPER(I32)=UPPER('Race Results'!G7),1,0)))))))</f>
         <v/>
       </c>
-      <c r="K32" s="15"/>
+      <c r="K32" s="4"/>
       <c r="L32" s="17" t="str">
         <f>IF(K32="","",IF(UPPER(K32)=UPPER('Race Results'!B8),10,IF(UPPER(K32)=UPPER('Race Results'!C8),6,IF(UPPER(K32)=UPPER('Race Results'!D8),4,IF(UPPER(K32)=UPPER('Race Results'!E8),3,IF(UPPER(K32)=UPPER('Race Results'!F8),2,IF(UPPER(K32)=UPPER('Race Results'!G8),1,0)))))))</f>
         <v/>
       </c>
       <c r="M32" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="4">
-        <v>30</v>
-      </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="17" t="str">
-        <f>IF(C33="","",IF(UPPER(C33)=UPPER('Race Results'!B4),10,IF(UPPER(C33)=UPPER('Race Results'!C4),6,IF(UPPER(C33)=UPPER('Race Results'!D4),4,IF(UPPER(C33)=UPPER('Race Results'!E4),3,IF(UPPER(C33)=UPPER('Race Results'!F4),2,IF(UPPER(C33)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="E33" s="4"/>
-      <c r="F33" s="17" t="str">
-        <f>IF(E33="","",IF(UPPER(E33)=UPPER('Race Results'!B5),10,IF(UPPER(E33)=UPPER('Race Results'!C5),6,IF(UPPER(E33)=UPPER('Race Results'!D5),4,IF(UPPER(E33)=UPPER('Race Results'!E5),3,IF(UPPER(E33)=UPPER('Race Results'!F5),2,IF(UPPER(E33)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G33" s="4"/>
-      <c r="H33" s="17" t="str">
-        <f>IF(G33="","",IF(UPPER(G33)=UPPER('Race Results'!B6),10,IF(UPPER(G33)=UPPER('Race Results'!C6),6,IF(UPPER(G33)=UPPER('Race Results'!D6),4,IF(UPPER(G33)=UPPER('Race Results'!E6),3,IF(UPPER(G33)=UPPER('Race Results'!F6),2,IF(UPPER(G33)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I33" s="4"/>
-      <c r="J33" s="17" t="str">
-        <f>IF(I33="","",IF(UPPER(I33)=UPPER('Race Results'!B7),10,IF(UPPER(I33)=UPPER('Race Results'!C7),6,IF(UPPER(I33)=UPPER('Race Results'!D7),4,IF(UPPER(I33)=UPPER('Race Results'!E7),3,IF(UPPER(I33)=UPPER('Race Results'!F7),2,IF(UPPER(I33)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K33" s="4"/>
-      <c r="L33" s="17" t="str">
-        <f>IF(K33="","",IF(UPPER(K33)=UPPER('Race Results'!B8),10,IF(UPPER(K33)=UPPER('Race Results'!C8),6,IF(UPPER(K33)=UPPER('Race Results'!D8),4,IF(UPPER(K33)=UPPER('Race Results'!E8),3,IF(UPPER(K33)=UPPER('Race Results'!F8),2,IF(UPPER(K33)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="M33" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3540,7 +3807,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>B4:B33</xm:sqref>
+          <xm:sqref>B4:B32</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Norfolk Stakes" prompt="Select horse for Norfolk Stakes" xr:uid="{00000000-0002-0000-0300-000001000000}">
           <x14:formula1>
@@ -3549,7 +3816,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>C4:C33</xm:sqref>
+          <xm:sqref>C4:C32</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="King George V" prompt="Select horse for King George V" xr:uid="{00000000-0002-0000-0300-000002000000}">
           <x14:formula1>
@@ -3558,7 +3825,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E4:E33</xm:sqref>
+          <xm:sqref>E4:E32</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Ribblesdale Stakes" prompt="Select horse for Ribblesdale Stakes" xr:uid="{00000000-0002-0000-0300-000003000000}">
           <x14:formula1>
@@ -3567,7 +3834,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>G4:G33</xm:sqref>
+          <xm:sqref>G4:G32</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Gold Cup" prompt="Select horse for Gold Cup" xr:uid="{00000000-0002-0000-0300-000004000000}">
           <x14:formula1>
@@ -3576,7 +3843,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>I4:I33</xm:sqref>
+          <xm:sqref>I4:I32</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Britannia Stakes" prompt="Select horse for Britannia Stakes" xr:uid="{00000000-0002-0000-0300-000005000000}">
           <x14:formula1>
@@ -3585,7 +3852,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>K4:K33</xm:sqref>
+          <xm:sqref>K4:K32</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3633,33 +3900,33 @@
       <c r="A3" s="19">
         <v>1</v>
       </c>
-      <c r="B3" s="20">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,1),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B3" s="20" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,1),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liam Bridgeman</v>
       </c>
       <c r="C3" s="21">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,1),"")</f>
-        <v>0</v>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,1),"")</f>
+        <v>10</v>
       </c>
       <c r="D3" s="22">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C3,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C3,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="19">
         <v>2</v>
       </c>
-      <c r="B4" s="20">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B4" s="20" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,2),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Steve Burfitt</v>
       </c>
       <c r="C4" s="21">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,2),"")</f>
-        <v>0</v>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,2),"")</f>
+        <v>6</v>
       </c>
       <c r="D4" s="22">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C4,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C4,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3667,16 +3934,16 @@
       <c r="A5" s="19">
         <v>3</v>
       </c>
-      <c r="B5" s="20">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,3),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B5" s="20" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,3),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Steve Burfitt</v>
       </c>
       <c r="C5" s="21">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,3),"")</f>
-        <v>0</v>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,3),"")</f>
+        <v>6</v>
       </c>
       <c r="D5" s="22">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C5,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C5,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3684,16 +3951,16 @@
       <c r="A6" s="23">
         <v>4</v>
       </c>
-      <c r="B6" s="24">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,4),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B6" s="24" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,4),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Marianne Chardon</v>
       </c>
       <c r="C6" s="25">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,4),"")</f>
-        <v>0</v>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,4),"")</f>
+        <v>4</v>
       </c>
       <c r="D6" s="26">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C6,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C6,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3701,16 +3968,16 @@
       <c r="A7" s="27">
         <v>5</v>
       </c>
-      <c r="B7" s="28">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,5),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B7" s="28" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,5),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C7" s="29">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,5),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,5),"")</f>
         <v>0</v>
       </c>
       <c r="D7" s="30">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C7,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C7,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3718,16 +3985,16 @@
       <c r="A8" s="23">
         <v>6</v>
       </c>
-      <c r="B8" s="24">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,6),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B8" s="24" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,6),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C8" s="25">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,6),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,6),"")</f>
         <v>0</v>
       </c>
       <c r="D8" s="26">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C8,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C8,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3735,16 +4002,16 @@
       <c r="A9" s="27">
         <v>7</v>
       </c>
-      <c r="B9" s="28">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,7),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B9" s="28" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,7),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C9" s="29">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,7),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,7),"")</f>
         <v>0</v>
       </c>
       <c r="D9" s="30">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C9,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C9,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3752,16 +4019,16 @@
       <c r="A10" s="23">
         <v>8</v>
       </c>
-      <c r="B10" s="24">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,8),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B10" s="24" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,8),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C10" s="25">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,8),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,8),"")</f>
         <v>0</v>
       </c>
       <c r="D10" s="26">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C10,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C10,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3769,16 +4036,16 @@
       <c r="A11" s="27">
         <v>9</v>
       </c>
-      <c r="B11" s="28">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,9),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B11" s="28" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,9),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C11" s="29">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,9),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,9),"")</f>
         <v>0</v>
       </c>
       <c r="D11" s="30">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C11,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C11,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3786,16 +4053,16 @@
       <c r="A12" s="23">
         <v>10</v>
       </c>
-      <c r="B12" s="24">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,10),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B12" s="24" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,10),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C12" s="25">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,10),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,10),"")</f>
         <v>0</v>
       </c>
       <c r="D12" s="26">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C12,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C12,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3803,16 +4070,16 @@
       <c r="A13" s="27">
         <v>11</v>
       </c>
-      <c r="B13" s="28">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,11),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B13" s="28" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,11),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C13" s="29">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,11),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,11),"")</f>
         <v>0</v>
       </c>
       <c r="D13" s="30">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C13,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C13,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3820,16 +4087,16 @@
       <c r="A14" s="23">
         <v>12</v>
       </c>
-      <c r="B14" s="24">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,12),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B14" s="24" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,12),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C14" s="25">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,12),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,12),"")</f>
         <v>0</v>
       </c>
       <c r="D14" s="26">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C14,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C14,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3837,16 +4104,16 @@
       <c r="A15" s="27">
         <v>13</v>
       </c>
-      <c r="B15" s="28">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,13),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B15" s="28" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,13),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C15" s="29">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,13),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,13),"")</f>
         <v>0</v>
       </c>
       <c r="D15" s="30">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C15,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C15,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3854,16 +4121,16 @@
       <c r="A16" s="23">
         <v>14</v>
       </c>
-      <c r="B16" s="24">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,14),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B16" s="24" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,14),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C16" s="25">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,14),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,14),"")</f>
         <v>0</v>
       </c>
       <c r="D16" s="26">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C16,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C16,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3871,16 +4138,16 @@
       <c r="A17" s="27">
         <v>15</v>
       </c>
-      <c r="B17" s="28">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,15),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B17" s="28" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,15),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C17" s="29">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,15),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,15),"")</f>
         <v>0</v>
       </c>
       <c r="D17" s="30">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C17,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C17,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3888,16 +4155,16 @@
       <c r="A18" s="23">
         <v>16</v>
       </c>
-      <c r="B18" s="24">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,16),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B18" s="24" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,16),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C18" s="25">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,16),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,16),"")</f>
         <v>0</v>
       </c>
       <c r="D18" s="26">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C18,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C18,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3905,16 +4172,16 @@
       <c r="A19" s="27">
         <v>17</v>
       </c>
-      <c r="B19" s="28">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,17),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B19" s="28" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,17),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C19" s="29">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,17),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,17),"")</f>
         <v>0</v>
       </c>
       <c r="D19" s="30">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C19,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C19,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3922,16 +4189,16 @@
       <c r="A20" s="23">
         <v>18</v>
       </c>
-      <c r="B20" s="24">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,18),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B20" s="24" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,18),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C20" s="25">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,18),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,18),"")</f>
         <v>0</v>
       </c>
       <c r="D20" s="26">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C20,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C20,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3939,16 +4206,16 @@
       <c r="A21" s="27">
         <v>19</v>
       </c>
-      <c r="B21" s="28">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,19),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B21" s="28" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,19),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C21" s="29">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,19),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,19),"")</f>
         <v>0</v>
       </c>
       <c r="D21" s="30">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C21,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C21,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3956,16 +4223,16 @@
       <c r="A22" s="23">
         <v>20</v>
       </c>
-      <c r="B22" s="24">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,20),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B22" s="24" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,20),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C22" s="25">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,20),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,20),"")</f>
         <v>0</v>
       </c>
       <c r="D22" s="26">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C22,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C22,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3973,16 +4240,16 @@
       <c r="A23" s="27">
         <v>21</v>
       </c>
-      <c r="B23" s="28">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,21),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B23" s="28" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,21),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C23" s="29">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,21),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,21),"")</f>
         <v>0</v>
       </c>
       <c r="D23" s="30">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C23,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C23,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3990,16 +4257,16 @@
       <c r="A24" s="23">
         <v>22</v>
       </c>
-      <c r="B24" s="24">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,22),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B24" s="24" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,22),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C24" s="25">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,22),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,22),"")</f>
         <v>0</v>
       </c>
       <c r="D24" s="26">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C24,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C24,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -4007,16 +4274,16 @@
       <c r="A25" s="27">
         <v>23</v>
       </c>
-      <c r="B25" s="28">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,23),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B25" s="28" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,23),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C25" s="29">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,23),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,23),"")</f>
         <v>0</v>
       </c>
       <c r="D25" s="30">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C25,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C25,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -4024,16 +4291,16 @@
       <c r="A26" s="23">
         <v>24</v>
       </c>
-      <c r="B26" s="24">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,24),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B26" s="24" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,24),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C26" s="25">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,24),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,24),"")</f>
         <v>0</v>
       </c>
       <c r="D26" s="26">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C26,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C26,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -4041,16 +4308,16 @@
       <c r="A27" s="27">
         <v>25</v>
       </c>
-      <c r="B27" s="28">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,25),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B27" s="28" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,25),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C27" s="29">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,25),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,25),"")</f>
         <v>0</v>
       </c>
       <c r="D27" s="30">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C27,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C27,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -4058,16 +4325,16 @@
       <c r="A28" s="23">
         <v>26</v>
       </c>
-      <c r="B28" s="24">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,26),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B28" s="24" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,26),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C28" s="25">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,26),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,26),"")</f>
         <v>0</v>
       </c>
       <c r="D28" s="26">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C28,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C28,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -4075,16 +4342,16 @@
       <c r="A29" s="27">
         <v>27</v>
       </c>
-      <c r="B29" s="28">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,27),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B29" s="28" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,27),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C29" s="29">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,27),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,27),"")</f>
         <v>0</v>
       </c>
       <c r="D29" s="30">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C29,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C29,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -4092,16 +4359,16 @@
       <c r="A30" s="23">
         <v>28</v>
       </c>
-      <c r="B30" s="24">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,28),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B30" s="24" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,28),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C30" s="25">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,28),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,28),"")</f>
         <v>0</v>
       </c>
       <c r="D30" s="26">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C30,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C30,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -4109,16 +4376,16 @@
       <c r="A31" s="27">
         <v>29</v>
       </c>
-      <c r="B31" s="28">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,29),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
+      <c r="B31" s="28" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,29),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v>Liz Bugler</v>
       </c>
       <c r="C31" s="29">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,29),"")</f>
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,29),"")</f>
         <v>0</v>
       </c>
       <c r="D31" s="30">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C31,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C31,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -4126,17 +4393,17 @@
       <c r="A32" s="23">
         <v>30</v>
       </c>
-      <c r="B32" s="24">
-        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$33,30),'Picks &amp; Scores'!$M$4:$M$33,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="C32" s="25">
-        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$33,30),"")</f>
-        <v>0</v>
-      </c>
-      <c r="D32" s="26">
-        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$33,MATCH(C32,'Picks &amp; Scores'!$M$4:$M$33,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+      <c r="B32" s="24" t="str">
+        <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,30),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="25" t="str">
+        <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,30),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="26" t="str">
+        <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C32,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="564" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DE502F1-73DA-4C34-BB7E-E5F0D80C7C4D}"/>
+  <xr:revisionPtr revIDLastSave="567" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70283B9F-187C-4826-9673-B8248E43E9C2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="183">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -1006,10 +1006,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2238,9 +2234,15 @@
       <c r="D4" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
@@ -2675,7 +2677,7 @@
       </c>
       <c r="D8" s="17">
         <f>IF(C8="","",IF(UPPER(C8)=UPPER('Race Results'!B4),10,IF(UPPER(C8)=UPPER('Race Results'!C4),6,IF(UPPER(C8)=UPPER('Race Results'!D4),4,IF(UPPER(C8)=UPPER('Race Results'!E4),3,IF(UPPER(C8)=UPPER('Race Results'!F4),2,IF(UPPER(C8)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>113</v>
@@ -2707,7 +2709,7 @@
       </c>
       <c r="M8" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2863,7 +2865,7 @@
       </c>
       <c r="D12" s="17">
         <f>IF(C12="","",IF(UPPER(C12)=UPPER('Race Results'!B4),10,IF(UPPER(C12)=UPPER('Race Results'!C4),6,IF(UPPER(C12)=UPPER('Race Results'!D4),4,IF(UPPER(C12)=UPPER('Race Results'!E4),3,IF(UPPER(C12)=UPPER('Race Results'!F4),2,IF(UPPER(C12)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>115</v>
@@ -2895,7 +2897,7 @@
       </c>
       <c r="M12" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3098,7 +3100,7 @@
       </c>
       <c r="D17" s="17">
         <f>IF(C17="","",IF(UPPER(C17)=UPPER('Race Results'!B4),10,IF(UPPER(C17)=UPPER('Race Results'!C4),6,IF(UPPER(C17)=UPPER('Race Results'!D4),4,IF(UPPER(C17)=UPPER('Race Results'!E4),3,IF(UPPER(C17)=UPPER('Race Results'!F4),2,IF(UPPER(C17)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>118</v>
@@ -3130,7 +3132,7 @@
       </c>
       <c r="M17" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
@@ -3239,7 +3241,7 @@
       </c>
       <c r="D20" s="17">
         <f>IF(C20="","",IF(UPPER(C20)=UPPER('Race Results'!B4),10,IF(UPPER(C20)=UPPER('Race Results'!C4),6,IF(UPPER(C20)=UPPER('Race Results'!D4),4,IF(UPPER(C20)=UPPER('Race Results'!E4),3,IF(UPPER(C20)=UPPER('Race Results'!F4),2,IF(UPPER(C20)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>121</v>
@@ -3271,7 +3273,7 @@
       </c>
       <c r="M20" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3568,7 +3570,7 @@
       </c>
       <c r="D27" s="17">
         <f>IF(C27="","",IF(UPPER(C27)=UPPER('Race Results'!B4),10,IF(UPPER(C27)=UPPER('Race Results'!C4),6,IF(UPPER(C27)=UPPER('Race Results'!D4),4,IF(UPPER(C27)=UPPER('Race Results'!E4),3,IF(UPPER(C27)=UPPER('Race Results'!F4),2,IF(UPPER(C27)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>112</v>
@@ -3600,7 +3602,7 @@
       </c>
       <c r="M27" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3970,11 +3972,11 @@
       </c>
       <c r="B7" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,5),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Jack Webb</v>
       </c>
       <c r="C7" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,5),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C7,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -3987,11 +3989,11 @@
       </c>
       <c r="B8" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,6),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Jack Webb</v>
       </c>
       <c r="C8" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,6),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D8" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C8,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4004,11 +4006,11 @@
       </c>
       <c r="B9" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,7),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Jack Webb</v>
       </c>
       <c r="C9" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,7),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C9,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4021,11 +4023,11 @@
       </c>
       <c r="B10" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,8),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Gemma Forsyth</v>
       </c>
       <c r="C10" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,8),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C10,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4038,11 +4040,11 @@
       </c>
       <c r="B11" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,9),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Denise White</v>
       </c>
       <c r="C11" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,9),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C11,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="567" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70283B9F-187C-4826-9673-B8248E43E9C2}"/>
+  <xr:revisionPtr revIDLastSave="576" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E369C077-0A98-4E47-8D2C-36EDEB5A8F49}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest List" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="183">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -2248,12 +2248,24 @@
       <c r="A5" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
@@ -2543,7 +2555,7 @@
       </c>
       <c r="F5" s="17">
         <f>IF(E5="","",IF(UPPER(E5)=UPPER('Race Results'!B5),10,IF(UPPER(E5)=UPPER('Race Results'!C5),6,IF(UPPER(E5)=UPPER('Race Results'!D5),4,IF(UPPER(E5)=UPPER('Race Results'!E5),3,IF(UPPER(E5)=UPPER('Race Results'!F5),2,IF(UPPER(E5)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>141</v>
@@ -2568,7 +2580,7 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
@@ -2590,7 +2602,7 @@
       </c>
       <c r="F6" s="17">
         <f>IF(E6="","",IF(UPPER(E6)=UPPER('Race Results'!B5),10,IF(UPPER(E6)=UPPER('Race Results'!C5),6,IF(UPPER(E6)=UPPER('Race Results'!D5),4,IF(UPPER(E6)=UPPER('Race Results'!E5),3,IF(UPPER(E6)=UPPER('Race Results'!F5),2,IF(UPPER(E6)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G6" s="15" t="s">
         <v>134</v>
@@ -2615,7 +2627,7 @@
       </c>
       <c r="M6" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2637,7 +2649,7 @@
       </c>
       <c r="F7" s="17">
         <f>IF(E7="","",IF(UPPER(E7)=UPPER('Race Results'!B5),10,IF(UPPER(E7)=UPPER('Race Results'!C5),6,IF(UPPER(E7)=UPPER('Race Results'!D5),4,IF(UPPER(E7)=UPPER('Race Results'!E5),3,IF(UPPER(E7)=UPPER('Race Results'!F5),2,IF(UPPER(E7)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>138</v>
@@ -2662,7 +2674,7 @@
       </c>
       <c r="M7" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2872,7 +2884,7 @@
       </c>
       <c r="F12" s="17">
         <f>IF(E12="","",IF(UPPER(E12)=UPPER('Race Results'!B5),10,IF(UPPER(E12)=UPPER('Race Results'!C5),6,IF(UPPER(E12)=UPPER('Race Results'!D5),4,IF(UPPER(E12)=UPPER('Race Results'!E5),3,IF(UPPER(E12)=UPPER('Race Results'!F5),2,IF(UPPER(E12)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G12" s="15" t="s">
         <v>131</v>
@@ -2897,7 +2909,7 @@
       </c>
       <c r="M12" s="18">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2919,7 +2931,7 @@
       </c>
       <c r="F13" s="17">
         <f>IF(E13="","",IF(UPPER(E13)=UPPER('Race Results'!B5),10,IF(UPPER(E13)=UPPER('Race Results'!C5),6,IF(UPPER(E13)=UPPER('Race Results'!D5),4,IF(UPPER(E13)=UPPER('Race Results'!E5),3,IF(UPPER(E13)=UPPER('Race Results'!F5),2,IF(UPPER(E13)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>138</v>
@@ -2944,7 +2956,7 @@
       </c>
       <c r="M13" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3060,7 +3072,7 @@
       </c>
       <c r="F16" s="17">
         <f>IF(E16="","",IF(UPPER(E16)=UPPER('Race Results'!B5),10,IF(UPPER(E16)=UPPER('Race Results'!C5),6,IF(UPPER(E16)=UPPER('Race Results'!D5),4,IF(UPPER(E16)=UPPER('Race Results'!E5),3,IF(UPPER(E16)=UPPER('Race Results'!F5),2,IF(UPPER(E16)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>138</v>
@@ -3085,7 +3097,7 @@
       </c>
       <c r="M16" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3248,7 +3260,7 @@
       </c>
       <c r="F20" s="17">
         <f>IF(E20="","",IF(UPPER(E20)=UPPER('Race Results'!B5),10,IF(UPPER(E20)=UPPER('Race Results'!C5),6,IF(UPPER(E20)=UPPER('Race Results'!D5),4,IF(UPPER(E20)=UPPER('Race Results'!E5),3,IF(UPPER(E20)=UPPER('Race Results'!F5),2,IF(UPPER(E20)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>138</v>
@@ -3273,7 +3285,7 @@
       </c>
       <c r="M20" s="18">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3389,7 +3401,7 @@
       </c>
       <c r="F23" s="17">
         <f>IF(E23="","",IF(UPPER(E23)=UPPER('Race Results'!B5),10,IF(UPPER(E23)=UPPER('Race Results'!C5),6,IF(UPPER(E23)=UPPER('Race Results'!D5),4,IF(UPPER(E23)=UPPER('Race Results'!E5),3,IF(UPPER(E23)=UPPER('Race Results'!F5),2,IF(UPPER(E23)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="15" t="s">
         <v>135</v>
@@ -3414,7 +3426,7 @@
       </c>
       <c r="M23" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3624,7 +3636,7 @@
       </c>
       <c r="F28" s="17">
         <f>IF(E28="","",IF(UPPER(E28)=UPPER('Race Results'!B5),10,IF(UPPER(E28)=UPPER('Race Results'!C5),6,IF(UPPER(E28)=UPPER('Race Results'!D5),4,IF(UPPER(E28)=UPPER('Race Results'!E5),3,IF(UPPER(E28)=UPPER('Race Results'!F5),2,IF(UPPER(E28)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>138</v>
@@ -3649,14 +3661,16 @@
       </c>
       <c r="M28" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="15">
         <v>27</v>
       </c>
-      <c r="B29" s="16"/>
+      <c r="B29" s="16" t="s">
+        <v>67</v>
+      </c>
       <c r="C29" s="15"/>
       <c r="D29" s="17" t="str">
         <f>IF(C29="","",IF(UPPER(C29)=UPPER('Race Results'!B4),10,IF(UPPER(C29)=UPPER('Race Results'!C4),6,IF(UPPER(C29)=UPPER('Race Results'!D4),4,IF(UPPER(C29)=UPPER('Race Results'!E4),3,IF(UPPER(C29)=UPPER('Race Results'!F4),2,IF(UPPER(C29)=UPPER('Race Results'!G4),1,0)))))))</f>
@@ -3904,7 +3918,7 @@
       </c>
       <c r="B3" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,1),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liam Bridgeman</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C3" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,1),"")</f>
@@ -3921,15 +3935,15 @@
       </c>
       <c r="B4" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,2),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Steve Burfitt</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C4" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,2),"")</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C4,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -3938,15 +3952,15 @@
       </c>
       <c r="B5" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,3),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Steve Burfitt</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C5" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,3),"")</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C5,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -3955,11 +3969,11 @@
       </c>
       <c r="B6" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,4),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Marianne Chardon</v>
+        <v>Jack Webb</v>
       </c>
       <c r="C6" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,4),"")</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D6" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C6,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -3972,11 +3986,11 @@
       </c>
       <c r="B7" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,5),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Jack Webb</v>
+        <v>Stephen Hughes</v>
       </c>
       <c r="C7" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,5),"")</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D7" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C7,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -3989,11 +4003,11 @@
       </c>
       <c r="B8" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,6),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Jack Webb</v>
+        <v>Marianne Chardon</v>
       </c>
       <c r="C8" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,6),"")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D8" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C8,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4006,11 +4020,11 @@
       </c>
       <c r="B9" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,7),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Jack Webb</v>
+        <v>Marianne Chardon</v>
       </c>
       <c r="C9" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,7),"")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D9" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C9,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4023,11 +4037,11 @@
       </c>
       <c r="B10" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,8),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Gemma Forsyth</v>
+        <v>Marianne Chardon</v>
       </c>
       <c r="C10" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,8),"")</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D10" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C10,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4040,11 +4054,11 @@
       </c>
       <c r="B11" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,9),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Denise White</v>
+        <v>Peter Goode</v>
       </c>
       <c r="C11" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,9),"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C11,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4057,11 +4071,11 @@
       </c>
       <c r="B12" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,10),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Peter Goode</v>
       </c>
       <c r="C12" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,10),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D12" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C12,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4074,11 +4088,11 @@
       </c>
       <c r="B13" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,11),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Peter Goode</v>
       </c>
       <c r="C13" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,11),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D13" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C13,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4091,11 +4105,11 @@
       </c>
       <c r="B14" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,12),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Peter Goode</v>
       </c>
       <c r="C14" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,12),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D14" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C14,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4108,11 +4122,11 @@
       </c>
       <c r="B15" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,13),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Gemma Forsyth</v>
       </c>
       <c r="C15" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,13),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C15,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4125,11 +4139,11 @@
       </c>
       <c r="B16" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,14),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Gemma Forsyth</v>
       </c>
       <c r="C16" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,14),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C16,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4142,11 +4156,11 @@
       </c>
       <c r="B17" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,15),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Denise White</v>
       </c>
       <c r="C17" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,15),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C17,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="576" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E369C077-0A98-4E47-8D2C-36EDEB5A8F49}"/>
+  <xr:revisionPtr revIDLastSave="580" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1873D743-2540-49AA-A0DC-3922C6EADD09}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest List" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="183">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -909,6 +909,7 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -916,7 +917,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1218,16 +1218,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35"/>
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1622,14 +1622,14 @@
       <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -2271,9 +2271,15 @@
       <c r="A6" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
+      <c r="B6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -2310,15 +2316,15 @@
       <c r="G9" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2609,7 +2615,7 @@
       </c>
       <c r="H6" s="17">
         <f>IF(G6="","",IF(UPPER(G6)=UPPER('Race Results'!B6),10,IF(UPPER(G6)=UPPER('Race Results'!C6),6,IF(UPPER(G6)=UPPER('Race Results'!D6),4,IF(UPPER(G6)=UPPER('Race Results'!E6),3,IF(UPPER(G6)=UPPER('Race Results'!F6),2,IF(UPPER(G6)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>147</v>
@@ -2627,7 +2633,7 @@
       </c>
       <c r="M6" s="18">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2703,7 +2709,7 @@
       </c>
       <c r="H8" s="17">
         <f>IF(G8="","",IF(UPPER(G8)=UPPER('Race Results'!B6),10,IF(UPPER(G8)=UPPER('Race Results'!C6),6,IF(UPPER(G8)=UPPER('Race Results'!D6),4,IF(UPPER(G8)=UPPER('Race Results'!E6),3,IF(UPPER(G8)=UPPER('Race Results'!F6),2,IF(UPPER(G8)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>145</v>
@@ -2721,7 +2727,7 @@
       </c>
       <c r="M8" s="18">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2750,7 +2756,7 @@
       </c>
       <c r="H9" s="17">
         <f>IF(G9="","",IF(UPPER(G9)=UPPER('Race Results'!B6),10,IF(UPPER(G9)=UPPER('Race Results'!C6),6,IF(UPPER(G9)=UPPER('Race Results'!D6),4,IF(UPPER(G9)=UPPER('Race Results'!E6),3,IF(UPPER(G9)=UPPER('Race Results'!F6),2,IF(UPPER(G9)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>143</v>
@@ -2768,7 +2774,7 @@
       </c>
       <c r="M9" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2797,7 +2803,7 @@
       </c>
       <c r="H10" s="17">
         <f>IF(G10="","",IF(UPPER(G10)=UPPER('Race Results'!B6),10,IF(UPPER(G10)=UPPER('Race Results'!C6),6,IF(UPPER(G10)=UPPER('Race Results'!D6),4,IF(UPPER(G10)=UPPER('Race Results'!E6),3,IF(UPPER(G10)=UPPER('Race Results'!F6),2,IF(UPPER(G10)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>144</v>
@@ -2815,7 +2821,7 @@
       </c>
       <c r="M10" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2985,7 +2991,7 @@
       </c>
       <c r="H14" s="17">
         <f>IF(G14="","",IF(UPPER(G14)=UPPER('Race Results'!B6),10,IF(UPPER(G14)=UPPER('Race Results'!C6),6,IF(UPPER(G14)=UPPER('Race Results'!D6),4,IF(UPPER(G14)=UPPER('Race Results'!E6),3,IF(UPPER(G14)=UPPER('Race Results'!F6),2,IF(UPPER(G14)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>147</v>
@@ -3003,7 +3009,7 @@
       </c>
       <c r="M14" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3502,7 +3508,7 @@
       </c>
       <c r="H25" s="17">
         <f>IF(G25="","",IF(UPPER(G25)=UPPER('Race Results'!B6),10,IF(UPPER(G25)=UPPER('Race Results'!C6),6,IF(UPPER(G25)=UPPER('Race Results'!D6),4,IF(UPPER(G25)=UPPER('Race Results'!E6),3,IF(UPPER(G25)=UPPER('Race Results'!F6),2,IF(UPPER(G25)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>151</v>
@@ -3520,7 +3526,7 @@
       </c>
       <c r="M25" s="18">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3549,7 +3555,7 @@
       </c>
       <c r="H26" s="17">
         <f>IF(G26="","",IF(UPPER(G26)=UPPER('Race Results'!B6),10,IF(UPPER(G26)=UPPER('Race Results'!C6),6,IF(UPPER(G26)=UPPER('Race Results'!D6),4,IF(UPPER(G26)=UPPER('Race Results'!E6),3,IF(UPPER(G26)=UPPER('Race Results'!F6),2,IF(UPPER(G26)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>146</v>
@@ -3567,7 +3573,7 @@
       </c>
       <c r="M26" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3681,10 +3687,12 @@
         <f>IF(E29="","",IF(UPPER(E29)=UPPER('Race Results'!B5),10,IF(UPPER(E29)=UPPER('Race Results'!C5),6,IF(UPPER(E29)=UPPER('Race Results'!D5),4,IF(UPPER(E29)=UPPER('Race Results'!E5),3,IF(UPPER(E29)=UPPER('Race Results'!F5),2,IF(UPPER(E29)=UPPER('Race Results'!G5),1,0)))))))</f>
         <v/>
       </c>
-      <c r="G29" s="15"/>
-      <c r="H29" s="17" t="str">
+      <c r="G29" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="H29" s="17">
         <f>IF(G29="","",IF(UPPER(G29)=UPPER('Race Results'!B6),10,IF(UPPER(G29)=UPPER('Race Results'!C6),6,IF(UPPER(G29)=UPPER('Race Results'!D6),4,IF(UPPER(G29)=UPPER('Race Results'!E6),3,IF(UPPER(G29)=UPPER('Race Results'!F6),2,IF(UPPER(G29)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="I29" s="15"/>
       <c r="J29" s="17" t="str">
@@ -3698,7 +3706,7 @@
       </c>
       <c r="M29" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3918,11 +3926,11 @@
       </c>
       <c r="B3" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,1),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Liam Bridgeman</v>
       </c>
       <c r="C3" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,1),"")</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D3" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C3,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -3939,11 +3947,11 @@
       </c>
       <c r="C4" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,2),"")</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C4,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -3952,15 +3960,15 @@
       </c>
       <c r="B5" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,3),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Gemma Forsyth</v>
       </c>
       <c r="C5" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,3),"")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C5,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -3969,15 +3977,15 @@
       </c>
       <c r="B6" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,4),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Jack Webb</v>
+        <v>Gemma Forsyth</v>
       </c>
       <c r="C6" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,4),"")</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C6,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -3986,15 +3994,15 @@
       </c>
       <c r="B7" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,5),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Stephen Hughes</v>
+        <v>Sean Horan</v>
       </c>
       <c r="C7" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,5),"")</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D7" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C7,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4003,15 +4011,15 @@
       </c>
       <c r="B8" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,6),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Marianne Chardon</v>
+        <v>Sean Horan</v>
       </c>
       <c r="C8" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,6),"")</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D8" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C8,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4020,11 +4028,11 @@
       </c>
       <c r="B9" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,7),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Marianne Chardon</v>
+        <v>Jack Webb</v>
       </c>
       <c r="C9" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,7),"")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D9" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C9,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4037,11 +4045,11 @@
       </c>
       <c r="B10" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,8),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Marianne Chardon</v>
+        <v>Stephen Hughes</v>
       </c>
       <c r="C10" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,8),"")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C10,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4054,11 +4062,11 @@
       </c>
       <c r="B11" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,9),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Peter Goode</v>
+        <v>Marianne Chardon</v>
       </c>
       <c r="C11" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,9),"")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D11" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C11,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4071,11 +4079,11 @@
       </c>
       <c r="B12" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,10),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Peter Goode</v>
+        <v>Marianne Chardon</v>
       </c>
       <c r="C12" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,10),"")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D12" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C12,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4088,11 +4096,11 @@
       </c>
       <c r="B13" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,11),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Peter Goode</v>
+        <v>Marianne Chardon</v>
       </c>
       <c r="C13" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,11),"")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D13" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C13,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4105,11 +4113,11 @@
       </c>
       <c r="B14" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,12),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Peter Goode</v>
+        <v>Mick Hogg</v>
       </c>
       <c r="C14" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,12),"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C14,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4122,11 +4130,11 @@
       </c>
       <c r="B15" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,13),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Gemma Forsyth</v>
+        <v>Mick Hogg</v>
       </c>
       <c r="C15" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,13),"")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C15,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4139,11 +4147,11 @@
       </c>
       <c r="B16" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,14),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Gemma Forsyth</v>
+        <v>Peter Goode</v>
       </c>
       <c r="C16" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,14),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C16,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4156,11 +4164,11 @@
       </c>
       <c r="B17" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,15),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Denise White</v>
+        <v>Peter Goode</v>
       </c>
       <c r="C17" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,15),"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C17,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4173,11 +4181,11 @@
       </c>
       <c r="B18" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,16),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Peter Goode</v>
       </c>
       <c r="C18" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,16),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D18" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C18,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4190,11 +4198,11 @@
       </c>
       <c r="B19" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,17),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Peter Goode</v>
       </c>
       <c r="C19" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,17),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D19" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C19,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4207,11 +4215,11 @@
       </c>
       <c r="B20" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,18),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Andy Bugler</v>
       </c>
       <c r="C20" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,18),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C20,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4224,11 +4232,11 @@
       </c>
       <c r="B21" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,19),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Denise White</v>
       </c>
       <c r="C21" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,19),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C21,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="580" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1873D743-2540-49AA-A0DC-3922C6EADD09}"/>
+  <xr:revisionPtr revIDLastSave="583" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{910FB32F-D1E1-4B31-B53D-AB0D0E534D83}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest List" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="183">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -909,7 +909,6 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -917,6 +916,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1218,16 +1218,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="36"/>
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37"/>
+      <c r="B2" s="36"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1622,14 +1622,14 @@
       <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -2280,9 +2280,15 @@
       <c r="D6" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
@@ -2316,15 +2322,15 @@
       <c r="G9" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2568,7 +2574,7 @@
       </c>
       <c r="H5" s="17">
         <f>IF(G5="","",IF(UPPER(G5)=UPPER('Race Results'!B6),10,IF(UPPER(G5)=UPPER('Race Results'!C6),6,IF(UPPER(G5)=UPPER('Race Results'!D6),4,IF(UPPER(G5)=UPPER('Race Results'!E6),3,IF(UPPER(G5)=UPPER('Race Results'!F6),2,IF(UPPER(G5)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>151</v>
@@ -2586,7 +2592,7 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
@@ -2897,7 +2903,7 @@
       </c>
       <c r="H12" s="17">
         <f>IF(G12="","",IF(UPPER(G12)=UPPER('Race Results'!B6),10,IF(UPPER(G12)=UPPER('Race Results'!C6),6,IF(UPPER(G12)=UPPER('Race Results'!D6),4,IF(UPPER(G12)=UPPER('Race Results'!E6),3,IF(UPPER(G12)=UPPER('Race Results'!F6),2,IF(UPPER(G12)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>143</v>
@@ -2915,7 +2921,7 @@
       </c>
       <c r="M12" s="18">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3038,7 +3044,7 @@
       </c>
       <c r="H15" s="17">
         <f>IF(G15="","",IF(UPPER(G15)=UPPER('Race Results'!B6),10,IF(UPPER(G15)=UPPER('Race Results'!C6),6,IF(UPPER(G15)=UPPER('Race Results'!D6),4,IF(UPPER(G15)=UPPER('Race Results'!E6),3,IF(UPPER(G15)=UPPER('Race Results'!F6),2,IF(UPPER(G15)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>146</v>
@@ -3056,7 +3062,7 @@
       </c>
       <c r="M15" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3179,7 +3185,7 @@
       </c>
       <c r="H18" s="17">
         <f>IF(G18="","",IF(UPPER(G18)=UPPER('Race Results'!B6),10,IF(UPPER(G18)=UPPER('Race Results'!C6),6,IF(UPPER(G18)=UPPER('Race Results'!D6),4,IF(UPPER(G18)=UPPER('Race Results'!E6),3,IF(UPPER(G18)=UPPER('Race Results'!F6),2,IF(UPPER(G18)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>151</v>
@@ -3197,7 +3203,7 @@
       </c>
       <c r="M18" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3226,7 +3232,7 @@
       </c>
       <c r="H19" s="17">
         <f>IF(G19="","",IF(UPPER(G19)=UPPER('Race Results'!B6),10,IF(UPPER(G19)=UPPER('Race Results'!C6),6,IF(UPPER(G19)=UPPER('Race Results'!D6),4,IF(UPPER(G19)=UPPER('Race Results'!E6),3,IF(UPPER(G19)=UPPER('Race Results'!F6),2,IF(UPPER(G19)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>151</v>
@@ -3244,7 +3250,7 @@
       </c>
       <c r="M19" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3320,7 +3326,7 @@
       </c>
       <c r="H21" s="17">
         <f>IF(G21="","",IF(UPPER(G21)=UPPER('Race Results'!B6),10,IF(UPPER(G21)=UPPER('Race Results'!C6),6,IF(UPPER(G21)=UPPER('Race Results'!D6),4,IF(UPPER(G21)=UPPER('Race Results'!E6),3,IF(UPPER(G21)=UPPER('Race Results'!F6),2,IF(UPPER(G21)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>145</v>
@@ -3338,7 +3344,7 @@
       </c>
       <c r="M21" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3461,7 +3467,7 @@
       </c>
       <c r="H24" s="17">
         <f>IF(G24="","",IF(UPPER(G24)=UPPER('Race Results'!B6),10,IF(UPPER(G24)=UPPER('Race Results'!C6),6,IF(UPPER(G24)=UPPER('Race Results'!D6),4,IF(UPPER(G24)=UPPER('Race Results'!E6),3,IF(UPPER(G24)=UPPER('Race Results'!F6),2,IF(UPPER(G24)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>151</v>
@@ -3479,7 +3485,7 @@
       </c>
       <c r="M24" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3994,15 +4000,15 @@
       </c>
       <c r="B7" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,5),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Sean Horan</v>
+        <v>Jack Webb</v>
       </c>
       <c r="C7" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,5),"")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C7,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4028,15 +4034,15 @@
       </c>
       <c r="B9" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,7),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Jack Webb</v>
+        <v>Sean Horan</v>
       </c>
       <c r="C9" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,7),"")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C9,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4045,11 +4051,11 @@
       </c>
       <c r="B10" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,8),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Stephen Hughes</v>
+        <v>Lynn Forsyth</v>
       </c>
       <c r="C10" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,8),"")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C10,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4066,7 +4072,7 @@
       </c>
       <c r="C11" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,9),"")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C11,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4083,7 +4089,7 @@
       </c>
       <c r="C12" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,10),"")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C12,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4096,7 +4102,7 @@
       </c>
       <c r="B13" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,11),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Marianne Chardon</v>
+        <v>Anthony Burke</v>
       </c>
       <c r="C13" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,11),"")</f>
@@ -4215,11 +4221,11 @@
       </c>
       <c r="B20" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,18),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Andy Bugler</v>
+        <v>Peter Goode</v>
       </c>
       <c r="C20" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,18),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C20,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4232,11 +4238,11 @@
       </c>
       <c r="B21" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,19),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Denise White</v>
+        <v>Darren Gill</v>
       </c>
       <c r="C21" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,19),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C21,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4249,11 +4255,11 @@
       </c>
       <c r="B22" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,20),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Darren Gill</v>
       </c>
       <c r="C22" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,20),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C22,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4266,11 +4272,11 @@
       </c>
       <c r="B23" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,21),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Darren Gill</v>
       </c>
       <c r="C23" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,21),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C23,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4283,11 +4289,11 @@
       </c>
       <c r="B24" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,22),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Darren Gill</v>
       </c>
       <c r="C24" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,22),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C24,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4300,11 +4306,11 @@
       </c>
       <c r="B25" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,23),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Denise White</v>
       </c>
       <c r="C25" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,23),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C25,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="583" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{910FB32F-D1E1-4B31-B53D-AB0D0E534D83}"/>
+  <xr:revisionPtr revIDLastSave="593" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{314C3167-AA66-4DD8-B8DA-CD7D29D066B0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest List" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="183">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -903,23 +903,23 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1218,16 +1218,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35"/>
+      <c r="A1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="34"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
+      <c r="B2" s="35"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1612,14 +1612,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="37" t="s">
@@ -2177,26 +2177,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
     </row>
     <row r="3" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
@@ -2294,12 +2294,24 @@
       <c r="A7" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
+      <c r="B7" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
@@ -2322,15 +2334,15 @@
       <c r="G9" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2427,38 +2439,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
     </row>
     <row r="3" spans="1:13" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -2534,7 +2546,7 @@
       </c>
       <c r="J4" s="17">
         <f>IF(I4="","",IF(UPPER(I4)=UPPER('Race Results'!B7),10,IF(UPPER(I4)=UPPER('Race Results'!C7),6,IF(UPPER(I4)=UPPER('Race Results'!D7),4,IF(UPPER(I4)=UPPER('Race Results'!E7),3,IF(UPPER(I4)=UPPER('Race Results'!F7),2,IF(UPPER(I4)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>160</v>
@@ -2545,7 +2557,7 @@
       </c>
       <c r="M4" s="18">
         <f t="shared" ref="M4:M32" si="0">IF(COUNTA(D4,F4,H4,J4,L4)=0,"",SUM(D4,F4,H4,J4,L4))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
@@ -2581,7 +2593,7 @@
       </c>
       <c r="J5" s="17">
         <f>IF(I5="","",IF(UPPER(I5)=UPPER('Race Results'!B7),10,IF(UPPER(I5)=UPPER('Race Results'!C7),6,IF(UPPER(I5)=UPPER('Race Results'!D7),4,IF(UPPER(I5)=UPPER('Race Results'!E7),3,IF(UPPER(I5)=UPPER('Race Results'!F7),2,IF(UPPER(I5)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>155</v>
@@ -2592,7 +2604,7 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
@@ -2628,7 +2640,7 @@
       </c>
       <c r="J6" s="17">
         <f>IF(I6="","",IF(UPPER(I6)=UPPER('Race Results'!B7),10,IF(UPPER(I6)=UPPER('Race Results'!C7),6,IF(UPPER(I6)=UPPER('Race Results'!D7),4,IF(UPPER(I6)=UPPER('Race Results'!E7),3,IF(UPPER(I6)=UPPER('Race Results'!F7),2,IF(UPPER(I6)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K6" s="15" t="s">
         <v>162</v>
@@ -2639,7 +2651,7 @@
       </c>
       <c r="M6" s="18">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2675,7 +2687,7 @@
       </c>
       <c r="J7" s="17">
         <f>IF(I7="","",IF(UPPER(I7)=UPPER('Race Results'!B7),10,IF(UPPER(I7)=UPPER('Race Results'!C7),6,IF(UPPER(I7)=UPPER('Race Results'!D7),4,IF(UPPER(I7)=UPPER('Race Results'!E7),3,IF(UPPER(I7)=UPPER('Race Results'!F7),2,IF(UPPER(I7)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>155</v>
@@ -2686,7 +2698,7 @@
       </c>
       <c r="M7" s="18">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2769,7 +2781,7 @@
       </c>
       <c r="J9" s="17">
         <f>IF(I9="","",IF(UPPER(I9)=UPPER('Race Results'!B7),10,IF(UPPER(I9)=UPPER('Race Results'!C7),6,IF(UPPER(I9)=UPPER('Race Results'!D7),4,IF(UPPER(I9)=UPPER('Race Results'!E7),3,IF(UPPER(I9)=UPPER('Race Results'!F7),2,IF(UPPER(I9)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>178</v>
@@ -2780,7 +2792,7 @@
       </c>
       <c r="M9" s="18">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2794,8 +2806,7 @@
         <v>96</v>
       </c>
       <c r="D10" s="17">
-        <f>IF(C10="","",IF(UPPER(C10)=UPPER('Race Results'!B4),10,IF(UPPER(C10)=UPPER('Race Results'!C4),6,IF(UPPER(C10)=UPPER('Race Results'!D4),4,IF(UPPER(C10)=UPPER('Race Results'!E4),3,IF(UPPER(C10)=UPPER('Race Results'!F4),2,IF(UPPER(C10)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>112</v>
@@ -2827,7 +2838,7 @@
       </c>
       <c r="M10" s="18">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2863,7 +2874,7 @@
       </c>
       <c r="J11" s="17">
         <f>IF(I11="","",IF(UPPER(I11)=UPPER('Race Results'!B7),10,IF(UPPER(I11)=UPPER('Race Results'!C7),6,IF(UPPER(I11)=UPPER('Race Results'!D7),4,IF(UPPER(I11)=UPPER('Race Results'!E7),3,IF(UPPER(I11)=UPPER('Race Results'!F7),2,IF(UPPER(I11)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>155</v>
@@ -2874,7 +2885,7 @@
       </c>
       <c r="M11" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2910,7 +2921,7 @@
       </c>
       <c r="J12" s="17">
         <f>IF(I12="","",IF(UPPER(I12)=UPPER('Race Results'!B7),10,IF(UPPER(I12)=UPPER('Race Results'!C7),6,IF(UPPER(I12)=UPPER('Race Results'!D7),4,IF(UPPER(I12)=UPPER('Race Results'!E7),3,IF(UPPER(I12)=UPPER('Race Results'!F7),2,IF(UPPER(I12)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>164</v>
@@ -2921,7 +2932,7 @@
       </c>
       <c r="M12" s="18">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2957,7 +2968,7 @@
       </c>
       <c r="J13" s="17">
         <f>IF(I13="","",IF(UPPER(I13)=UPPER('Race Results'!B7),10,IF(UPPER(I13)=UPPER('Race Results'!C7),6,IF(UPPER(I13)=UPPER('Race Results'!D7),4,IF(UPPER(I13)=UPPER('Race Results'!E7),3,IF(UPPER(I13)=UPPER('Race Results'!F7),2,IF(UPPER(I13)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>163</v>
@@ -2968,7 +2979,7 @@
       </c>
       <c r="M13" s="18">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3004,7 +3015,7 @@
       </c>
       <c r="J14" s="17">
         <f>IF(I14="","",IF(UPPER(I14)=UPPER('Race Results'!B7),10,IF(UPPER(I14)=UPPER('Race Results'!C7),6,IF(UPPER(I14)=UPPER('Race Results'!D7),4,IF(UPPER(I14)=UPPER('Race Results'!E7),3,IF(UPPER(I14)=UPPER('Race Results'!F7),2,IF(UPPER(I14)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K14" s="15" t="s">
         <v>163</v>
@@ -3015,7 +3026,7 @@
       </c>
       <c r="M14" s="18">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3051,7 +3062,7 @@
       </c>
       <c r="J15" s="17">
         <f>IF(I15="","",IF(UPPER(I15)=UPPER('Race Results'!B7),10,IF(UPPER(I15)=UPPER('Race Results'!C7),6,IF(UPPER(I15)=UPPER('Race Results'!D7),4,IF(UPPER(I15)=UPPER('Race Results'!E7),3,IF(UPPER(I15)=UPPER('Race Results'!F7),2,IF(UPPER(I15)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15" t="s">
         <v>155</v>
@@ -3062,7 +3073,7 @@
       </c>
       <c r="M15" s="18">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3098,7 +3109,7 @@
       </c>
       <c r="J16" s="17">
         <f>IF(I16="","",IF(UPPER(I16)=UPPER('Race Results'!B7),10,IF(UPPER(I16)=UPPER('Race Results'!C7),6,IF(UPPER(I16)=UPPER('Race Results'!D7),4,IF(UPPER(I16)=UPPER('Race Results'!E7),3,IF(UPPER(I16)=UPPER('Race Results'!F7),2,IF(UPPER(I16)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>159</v>
@@ -3109,7 +3120,7 @@
       </c>
       <c r="M16" s="18">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3170,8 +3181,7 @@
         <v>96</v>
       </c>
       <c r="D18" s="17">
-        <f>IF(C18="","",IF(UPPER(C18)=UPPER('Race Results'!B4),10,IF(UPPER(C18)=UPPER('Race Results'!C4),6,IF(UPPER(C18)=UPPER('Race Results'!D4),4,IF(UPPER(C18)=UPPER('Race Results'!E4),3,IF(UPPER(C18)=UPPER('Race Results'!F4),2,IF(UPPER(C18)=UPPER('Race Results'!G4),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>113</v>
@@ -3192,7 +3202,7 @@
       </c>
       <c r="J18" s="17">
         <f>IF(I18="","",IF(UPPER(I18)=UPPER('Race Results'!B7),10,IF(UPPER(I18)=UPPER('Race Results'!C7),6,IF(UPPER(I18)=UPPER('Race Results'!D7),4,IF(UPPER(I18)=UPPER('Race Results'!E7),3,IF(UPPER(I18)=UPPER('Race Results'!F7),2,IF(UPPER(I18)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>158</v>
@@ -3203,7 +3213,7 @@
       </c>
       <c r="M18" s="18">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3239,7 +3249,7 @@
       </c>
       <c r="J19" s="17">
         <f>IF(I19="","",IF(UPPER(I19)=UPPER('Race Results'!B7),10,IF(UPPER(I19)=UPPER('Race Results'!C7),6,IF(UPPER(I19)=UPPER('Race Results'!D7),4,IF(UPPER(I19)=UPPER('Race Results'!E7),3,IF(UPPER(I19)=UPPER('Race Results'!F7),2,IF(UPPER(I19)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K19" s="15" t="s">
         <v>162</v>
@@ -3250,7 +3260,7 @@
       </c>
       <c r="M19" s="18">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3286,7 +3296,7 @@
       </c>
       <c r="J20" s="17">
         <f>IF(I20="","",IF(UPPER(I20)=UPPER('Race Results'!B7),10,IF(UPPER(I20)=UPPER('Race Results'!C7),6,IF(UPPER(I20)=UPPER('Race Results'!D7),4,IF(UPPER(I20)=UPPER('Race Results'!E7),3,IF(UPPER(I20)=UPPER('Race Results'!F7),2,IF(UPPER(I20)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>166</v>
@@ -3297,7 +3307,7 @@
       </c>
       <c r="M20" s="18">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3380,7 +3390,7 @@
       </c>
       <c r="J22" s="17">
         <f>IF(I22="","",IF(UPPER(I22)=UPPER('Race Results'!B7),10,IF(UPPER(I22)=UPPER('Race Results'!C7),6,IF(UPPER(I22)=UPPER('Race Results'!D7),4,IF(UPPER(I22)=UPPER('Race Results'!E7),3,IF(UPPER(I22)=UPPER('Race Results'!F7),2,IF(UPPER(I22)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>162</v>
@@ -3391,7 +3401,7 @@
       </c>
       <c r="M22" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
@@ -3427,7 +3437,7 @@
       </c>
       <c r="J23" s="17">
         <f>IF(I23="","",IF(UPPER(I23)=UPPER('Race Results'!B7),10,IF(UPPER(I23)=UPPER('Race Results'!C7),6,IF(UPPER(I23)=UPPER('Race Results'!D7),4,IF(UPPER(I23)=UPPER('Race Results'!E7),3,IF(UPPER(I23)=UPPER('Race Results'!F7),2,IF(UPPER(I23)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K23" s="15" t="s">
         <v>178</v>
@@ -3438,7 +3448,7 @@
       </c>
       <c r="M23" s="18">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3474,7 +3484,7 @@
       </c>
       <c r="J24" s="17">
         <f>IF(I24="","",IF(UPPER(I24)=UPPER('Race Results'!B7),10,IF(UPPER(I24)=UPPER('Race Results'!C7),6,IF(UPPER(I24)=UPPER('Race Results'!D7),4,IF(UPPER(I24)=UPPER('Race Results'!E7),3,IF(UPPER(I24)=UPPER('Race Results'!F7),2,IF(UPPER(I24)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>164</v>
@@ -3485,7 +3495,7 @@
       </c>
       <c r="M24" s="18">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3521,7 +3531,7 @@
       </c>
       <c r="J25" s="17">
         <f>IF(I25="","",IF(UPPER(I25)=UPPER('Race Results'!B7),10,IF(UPPER(I25)=UPPER('Race Results'!C7),6,IF(UPPER(I25)=UPPER('Race Results'!D7),4,IF(UPPER(I25)=UPPER('Race Results'!E7),3,IF(UPPER(I25)=UPPER('Race Results'!F7),2,IF(UPPER(I25)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K25" s="15" t="s">
         <v>180</v>
@@ -3532,7 +3542,7 @@
       </c>
       <c r="M25" s="18">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3568,7 +3578,7 @@
       </c>
       <c r="J26" s="17">
         <f>IF(I26="","",IF(UPPER(I26)=UPPER('Race Results'!B7),10,IF(UPPER(I26)=UPPER('Race Results'!C7),6,IF(UPPER(I26)=UPPER('Race Results'!D7),4,IF(UPPER(I26)=UPPER('Race Results'!E7),3,IF(UPPER(I26)=UPPER('Race Results'!F7),2,IF(UPPER(I26)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>181</v>
@@ -3579,7 +3589,7 @@
       </c>
       <c r="M26" s="18">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3615,7 +3625,7 @@
       </c>
       <c r="J27" s="17">
         <f>IF(I27="","",IF(UPPER(I27)=UPPER('Race Results'!B7),10,IF(UPPER(I27)=UPPER('Race Results'!C7),6,IF(UPPER(I27)=UPPER('Race Results'!D7),4,IF(UPPER(I27)=UPPER('Race Results'!E7),3,IF(UPPER(I27)=UPPER('Race Results'!F7),2,IF(UPPER(I27)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15" t="s">
         <v>154</v>
@@ -3626,7 +3636,7 @@
       </c>
       <c r="M27" s="18">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3662,7 +3672,7 @@
       </c>
       <c r="J28" s="17">
         <f>IF(I28="","",IF(UPPER(I28)=UPPER('Race Results'!B7),10,IF(UPPER(I28)=UPPER('Race Results'!C7),6,IF(UPPER(I28)=UPPER('Race Results'!D7),4,IF(UPPER(I28)=UPPER('Race Results'!E7),3,IF(UPPER(I28)=UPPER('Race Results'!F7),2,IF(UPPER(I28)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>178</v>
@@ -3673,10 +3683,10 @@
       </c>
       <c r="M28" s="18">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A29" s="15">
         <v>27</v>
       </c>
@@ -3700,19 +3710,23 @@
         <f>IF(G29="","",IF(UPPER(G29)=UPPER('Race Results'!B6),10,IF(UPPER(G29)=UPPER('Race Results'!C6),6,IF(UPPER(G29)=UPPER('Race Results'!D6),4,IF(UPPER(G29)=UPPER('Race Results'!E6),3,IF(UPPER(G29)=UPPER('Race Results'!F6),2,IF(UPPER(G29)=UPPER('Race Results'!G6),1,0)))))))</f>
         <v>6</v>
       </c>
-      <c r="I29" s="15"/>
-      <c r="J29" s="17" t="str">
+      <c r="I29" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J29" s="17">
         <f>IF(I29="","",IF(UPPER(I29)=UPPER('Race Results'!B7),10,IF(UPPER(I29)=UPPER('Race Results'!C7),6,IF(UPPER(I29)=UPPER('Race Results'!D7),4,IF(UPPER(I29)=UPPER('Race Results'!E7),3,IF(UPPER(I29)=UPPER('Race Results'!F7),2,IF(UPPER(I29)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="K29" s="15"/>
-      <c r="L29" s="17" t="str">
+        <v>3</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="L29" s="17">
         <f>IF(K29="","",IF(UPPER(K29)=UPPER('Race Results'!B8),10,IF(UPPER(K29)=UPPER('Race Results'!C8),6,IF(UPPER(K29)=UPPER('Race Results'!D8),4,IF(UPPER(K29)=UPPER('Race Results'!E8),3,IF(UPPER(K29)=UPPER('Race Results'!F8),2,IF(UPPER(K29)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M29" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3905,12 +3919,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -3936,11 +3950,11 @@
       </c>
       <c r="C3" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,1),"")</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D3" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C3,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -3953,7 +3967,7 @@
       </c>
       <c r="C4" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,2),"")</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D4" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C4,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -3966,11 +3980,11 @@
       </c>
       <c r="B5" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,3),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Gemma Forsyth</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C5" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,3),"")</f>
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D5" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C5,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -3983,11 +3997,11 @@
       </c>
       <c r="B6" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,4),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Gemma Forsyth</v>
+        <v>Marianne Chardon</v>
       </c>
       <c r="C6" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,4),"")</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D6" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C6,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4000,15 +4014,15 @@
       </c>
       <c r="B7" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,5),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Jack Webb</v>
+        <v>Sean Horan</v>
       </c>
       <c r="C7" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,5),"")</f>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D7" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C7,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4017,15 +4031,15 @@
       </c>
       <c r="B8" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,6),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Sean Horan</v>
+        <v>Steve Burfitt</v>
       </c>
       <c r="C8" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,6),"")</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D8" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C8,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4034,15 +4048,15 @@
       </c>
       <c r="B9" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,7),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Sean Horan</v>
+        <v>Steve Burfitt</v>
       </c>
       <c r="C9" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,7),"")</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D9" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C9,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4051,11 +4065,11 @@
       </c>
       <c r="B10" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,8),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Lynn Forsyth</v>
+        <v>Jack Webb</v>
       </c>
       <c r="C10" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,8),"")</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D10" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C10,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4068,15 +4082,15 @@
       </c>
       <c r="B11" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,9),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Marianne Chardon</v>
+        <v>Peter Goode</v>
       </c>
       <c r="C11" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,9),"")</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D11" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C11,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4085,15 +4099,15 @@
       </c>
       <c r="B12" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,10),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Marianne Chardon</v>
+        <v>Peter Goode</v>
       </c>
       <c r="C12" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,10),"")</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D12" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C12,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4102,15 +4116,15 @@
       </c>
       <c r="B13" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,11),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Anthony Burke</v>
+        <v>Peter Goode</v>
       </c>
       <c r="C13" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,11),"")</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D13" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C13,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4119,15 +4133,15 @@
       </c>
       <c r="B14" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,12),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Mick Hogg</v>
+        <v>Peter Goode</v>
       </c>
       <c r="C14" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,12),"")</f>
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D14" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C14,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4136,15 +4150,15 @@
       </c>
       <c r="B15" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,13),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Mick Hogg</v>
+        <v>Gemma Forsyth</v>
       </c>
       <c r="C15" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,13),"")</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D15" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C15,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4153,15 +4167,15 @@
       </c>
       <c r="B16" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,14),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Peter Goode</v>
+        <v>Gemma Forsyth</v>
       </c>
       <c r="C16" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,14),"")</f>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D16" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C16,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4170,15 +4184,15 @@
       </c>
       <c r="B17" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,15),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Peter Goode</v>
+        <v>Gemma Forsyth</v>
       </c>
       <c r="C17" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,15),"")</f>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D17" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C17,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4187,15 +4201,15 @@
       </c>
       <c r="B18" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,16),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Peter Goode</v>
+        <v>Vahi Crowley</v>
       </c>
       <c r="C18" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,16),"")</f>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D18" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C18,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4204,15 +4218,15 @@
       </c>
       <c r="B19" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,17),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Peter Goode</v>
+        <v>Vahi Crowley</v>
       </c>
       <c r="C19" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,17),"")</f>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D19" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C19,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4221,11 +4235,11 @@
       </c>
       <c r="B20" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,18),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Peter Goode</v>
+        <v>David Owens</v>
       </c>
       <c r="C20" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,18),"")</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D20" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C20,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4238,11 +4252,11 @@
       </c>
       <c r="B21" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,19),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Darren Gill</v>
+        <v>David Owens</v>
       </c>
       <c r="C21" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,19),"")</f>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D21" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C21,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4255,11 +4269,11 @@
       </c>
       <c r="B22" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,20),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Darren Gill</v>
+        <v>Jade Dally</v>
       </c>
       <c r="C22" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,20),"")</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D22" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C22,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4272,11 +4286,11 @@
       </c>
       <c r="B23" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,21),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Darren Gill</v>
+        <v>Mick Hogg</v>
       </c>
       <c r="C23" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,21),"")</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D23" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C23,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4289,11 +4303,11 @@
       </c>
       <c r="B24" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,22),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Darren Gill</v>
+        <v>Mick Hogg</v>
       </c>
       <c r="C24" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,22),"")</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D24" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C24,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4306,11 +4320,11 @@
       </c>
       <c r="B25" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,23),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Denise White</v>
+        <v>Andy Bugler</v>
       </c>
       <c r="C25" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,23),"")</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D25" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C25,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4327,7 +4341,7 @@
       </c>
       <c r="C26" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,24),"")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D26" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C26,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4340,11 +4354,11 @@
       </c>
       <c r="B27" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,25),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Emily Sardo</v>
       </c>
       <c r="C27" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,25),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D27" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C27,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4357,11 +4371,11 @@
       </c>
       <c r="B28" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,26),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>Emily Sardo</v>
       </c>
       <c r="C28" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,26),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D28" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C28,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4372,9 +4386,9 @@
       <c r="A29" s="27">
         <v>27</v>
       </c>
-      <c r="B29" s="28" t="str">
+      <c r="B29" s="28">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,27),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>0</v>
       </c>
       <c r="C29" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,27),"")</f>
@@ -4389,9 +4403,9 @@
       <c r="A30" s="23">
         <v>28</v>
       </c>
-      <c r="B30" s="24" t="str">
+      <c r="B30" s="24">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,28),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>0</v>
       </c>
       <c r="C30" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,28),"")</f>
@@ -4406,9 +4420,9 @@
       <c r="A31" s="27">
         <v>29</v>
       </c>
-      <c r="B31" s="28" t="str">
+      <c r="B31" s="28">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,29),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Liz Bugler</v>
+        <v>0</v>
       </c>
       <c r="C31" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,29),"")</f>
@@ -4457,14 +4471,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="3" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A3" s="40" t="s">

--- a/ascot_tipping_scoresheet.xlsx
+++ b/ascot_tipping_scoresheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="593" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{314C3167-AA66-4DD8-B8DA-CD7D29D066B0}"/>
+  <xr:revisionPtr revIDLastSave="599" documentId="13_ncr:1_{D69588C9-C99A-444E-8716-C3CC7EB9F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA5D2BFC-29BD-49EE-9B37-10A9C69C3B45}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest List" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="183">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -2317,12 +2317,24 @@
       <c r="A8" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
@@ -2741,11 +2753,11 @@
       </c>
       <c r="L8" s="17">
         <f>IF(K8="","",IF(UPPER(K8)=UPPER('Race Results'!B8),10,IF(UPPER(K8)=UPPER('Race Results'!C8),6,IF(UPPER(K8)=UPPER('Race Results'!D8),4,IF(UPPER(K8)=UPPER('Race Results'!E8),3,IF(UPPER(K8)=UPPER('Race Results'!F8),2,IF(UPPER(K8)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" s="18">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2788,11 +2800,11 @@
       </c>
       <c r="L9" s="17">
         <f>IF(K9="","",IF(UPPER(K9)=UPPER('Race Results'!B8),10,IF(UPPER(K9)=UPPER('Race Results'!C8),6,IF(UPPER(K9)=UPPER('Race Results'!D8),4,IF(UPPER(K9)=UPPER('Race Results'!E8),3,IF(UPPER(K9)=UPPER('Race Results'!F8),2,IF(UPPER(K9)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M9" s="18">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3444,11 +3456,11 @@
       </c>
       <c r="L23" s="17">
         <f>IF(K23="","",IF(UPPER(K23)=UPPER('Race Results'!B8),10,IF(UPPER(K23)=UPPER('Race Results'!C8),6,IF(UPPER(K23)=UPPER('Race Results'!D8),4,IF(UPPER(K23)=UPPER('Race Results'!E8),3,IF(UPPER(K23)=UPPER('Race Results'!F8),2,IF(UPPER(K23)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M23" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3538,11 +3550,11 @@
       </c>
       <c r="L25" s="17">
         <f>IF(K25="","",IF(UPPER(K25)=UPPER('Race Results'!B8),10,IF(UPPER(K25)=UPPER('Race Results'!C8),6,IF(UPPER(K25)=UPPER('Race Results'!D8),4,IF(UPPER(K25)=UPPER('Race Results'!E8),3,IF(UPPER(K25)=UPPER('Race Results'!F8),2,IF(UPPER(K25)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M25" s="18">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3679,11 +3691,11 @@
       </c>
       <c r="L28" s="17">
         <f>IF(K28="","",IF(UPPER(K28)=UPPER('Race Results'!B8),10,IF(UPPER(K28)=UPPER('Race Results'!C8),6,IF(UPPER(K28)=UPPER('Race Results'!D8),4,IF(UPPER(K28)=UPPER('Race Results'!E8),3,IF(UPPER(K28)=UPPER('Race Results'!F8),2,IF(UPPER(K28)=UPPER('Race Results'!G8),1,0)))))))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M28" s="18">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
@@ -3950,7 +3962,7 @@
       </c>
       <c r="C3" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,1),"")</f>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D3" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C3,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -3963,15 +3975,15 @@
       </c>
       <c r="B4" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,2),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Bryan White</v>
       </c>
       <c r="C4" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,2),"")</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D4" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C4,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -3980,11 +3992,11 @@
       </c>
       <c r="B5" s="20" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,3),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Robb Topp</v>
+        <v>Steve Burfitt</v>
       </c>
       <c r="C5" s="21">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,3),"")</f>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D5" s="22">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C5,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -3997,11 +4009,11 @@
       </c>
       <c r="B6" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,4),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Marianne Chardon</v>
+        <v>Robb Topp</v>
       </c>
       <c r="C6" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,4),"")</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D6" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C6,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4014,11 +4026,11 @@
       </c>
       <c r="B7" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,5),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Sean Horan</v>
+        <v>Marianne Chardon</v>
       </c>
       <c r="C7" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,5),"")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C7,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4031,15 +4043,15 @@
       </c>
       <c r="B8" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,6),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Steve Burfitt</v>
+        <v>Sean Horan</v>
       </c>
       <c r="C8" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,6),"")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C8,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4048,15 +4060,15 @@
       </c>
       <c r="B9" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,7),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Steve Burfitt</v>
+        <v>Sean Horan</v>
       </c>
       <c r="C9" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,7),"")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C9,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4065,15 +4077,15 @@
       </c>
       <c r="B10" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,8),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Jack Webb</v>
+        <v>Gemma Forsyth</v>
       </c>
       <c r="C10" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,8),"")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C10,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4082,11 +4094,11 @@
       </c>
       <c r="B11" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,9),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Peter Goode</v>
+        <v>Gemma Forsyth</v>
       </c>
       <c r="C11" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,9),"")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D11" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C11,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4099,15 +4111,15 @@
       </c>
       <c r="B12" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,10),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Peter Goode</v>
+        <v>Jack Webb</v>
       </c>
       <c r="C12" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,10),"")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C12,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4150,11 +4162,11 @@
       </c>
       <c r="B15" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,13),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Gemma Forsyth</v>
+        <v>Peter Goode</v>
       </c>
       <c r="C15" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,13),"")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C15,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4167,11 +4179,11 @@
       </c>
       <c r="B16" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,14),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Gemma Forsyth</v>
+        <v>Peter Goode</v>
       </c>
       <c r="C16" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,14),"")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C16,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4184,7 +4196,7 @@
       </c>
       <c r="B17" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,15),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Gemma Forsyth</v>
+        <v>Jamie Jordan</v>
       </c>
       <c r="C17" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,15),"")</f>
@@ -4201,15 +4213,15 @@
       </c>
       <c r="B18" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,16),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Vahi Crowley</v>
+        <v>Jamie Jordan</v>
       </c>
       <c r="C18" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,16),"")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D18" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C18,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4235,15 +4247,15 @@
       </c>
       <c r="B20" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,18),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>David Owens</v>
+        <v>Vahi Crowley</v>
       </c>
       <c r="C20" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,18),"")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C20,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -4269,11 +4281,11 @@
       </c>
       <c r="B22" s="24" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,20),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Jade Dally</v>
+        <v>David Owens</v>
       </c>
       <c r="C22" s="25">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,20),"")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="26">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C22,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4286,11 +4298,11 @@
       </c>
       <c r="B23" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,21),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Mick Hogg</v>
+        <v>Jade Dally</v>
       </c>
       <c r="C23" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,21),"")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C23,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
@@ -4320,11 +4332,11 @@
       </c>
       <c r="B25" s="28" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$32,MATCH(LARGE('Picks &amp; Scores'!$M$4:$M$32,23),'Picks &amp; Scores'!$M$4:$M$32,0)),"")</f>
-        <v>Andy Bugler</v>
+        <v>Mick Hogg</v>
       </c>
       <c r="C25" s="29">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$M$4:$M$32,23),"")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" s="30">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$L$32,MATCH(C25,'Picks &amp; Scores'!$M$4:$M$32,0)-1,0,1,11),10),"")</f>
